--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -673,7 +673,9 @@
       <c r="Q5" s="8">
         <v>0.38</v>
       </c>
-      <c r="R5" s="9"/>
+      <c r="R5" s="8">
+        <v>0.1</v>
+      </c>
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -683,7 +685,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9">
         <f t="shared" si="2"/>
-        <v>0.262225</v>
+        <v>0.22978</v>
       </c>
     </row>
     <row r="8">
@@ -994,15 +996,17 @@
       <c r="Q12" s="8">
         <v>0.2373</v>
       </c>
-      <c r="R12" s="9"/>
+      <c r="R12" s="8">
+        <v>0.0244</v>
+      </c>
       <c r="S12" s="9"/>
       <c r="T12" s="11"/>
       <c r="W12" s="12"/>
       <c r="X12" s="9"/>
       <c r="Y12" s="9"/>
-      <c r="Z12" s="7" t="str">
+      <c r="Z12" s="9">
         <f>average(R12:Y12)</f>
-        <v>#DIV/0!</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="13">
@@ -2124,7 +2128,9 @@
       <c r="Q40" s="8">
         <v>0.1957</v>
       </c>
-      <c r="R40" s="9"/>
+      <c r="R40" s="8">
+        <v>0.1111</v>
+      </c>
       <c r="S40" s="9"/>
       <c r="T40" s="9"/>
       <c r="U40" s="9"/>
@@ -2132,9 +2138,9 @@
       <c r="W40" s="9"/>
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
-      <c r="Z40" s="7" t="str">
+      <c r="Z40" s="9">
         <f>average(R40:Y40)</f>
-        <v>#DIV/0!</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="43">
@@ -2299,7 +2305,9 @@
       <c r="Q47" s="8">
         <v>0.1818</v>
       </c>
-      <c r="R47" s="9"/>
+      <c r="R47" s="8">
+        <v>0.2059</v>
+      </c>
       <c r="S47" s="9"/>
       <c r="T47" s="9"/>
       <c r="U47" s="9"/>
@@ -2307,9 +2315,9 @@
       <c r="W47" s="9"/>
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
-      <c r="Z47" s="7" t="str">
+      <c r="Z47" s="9">
         <f>average(R47:Y47)</f>
-        <v>#DIV/0!</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="50">
@@ -2930,9 +2938,9 @@
         <f t="shared" si="14"/>
         <v>0.2484571429</v>
       </c>
-      <c r="R59" s="7" t="str">
+      <c r="R59" s="9">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.11035</v>
       </c>
       <c r="S59" s="7" t="str">
         <f t="shared" si="14"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="16">
   <si>
     <t>Jamie Jenkins</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>Mike Harr</t>
+  </si>
+  <si>
+    <t>Contract Total Average</t>
   </si>
   <si>
     <t>Closing Rate Monthly Average</t>
@@ -374,7 +377,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="13.88"/>
+    <col customWidth="1" min="1" max="1" width="17.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2559,71 +2562,71 @@
       <c r="A56" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="5">
         <f t="shared" ref="B56:Y56" si="10">sum(B51,B44,B37,B30,B23,B16,B9,B2)</f>
         <v>89497.5</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="5">
         <f t="shared" si="10"/>
         <v>96780.4</v>
       </c>
-      <c r="D56" s="14">
+      <c r="D56" s="5">
         <f t="shared" si="10"/>
         <v>266185.41</v>
       </c>
-      <c r="E56" s="14">
+      <c r="E56" s="5">
         <f t="shared" si="10"/>
         <v>191108.77</v>
       </c>
-      <c r="F56" s="14">
+      <c r="F56" s="5">
         <f t="shared" si="10"/>
         <v>478352.55</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="5">
         <f t="shared" si="10"/>
         <v>732280.47</v>
       </c>
-      <c r="H56" s="14">
+      <c r="H56" s="5">
         <f t="shared" si="10"/>
         <v>684300.08</v>
       </c>
-      <c r="I56" s="14">
+      <c r="I56" s="5">
         <f t="shared" si="10"/>
         <v>318537.92</v>
       </c>
-      <c r="J56" s="7">
+      <c r="J56" s="5">
         <f t="shared" si="10"/>
         <v>337890.59</v>
       </c>
-      <c r="K56" s="7">
+      <c r="K56" s="5">
         <f t="shared" si="10"/>
         <v>691198.5</v>
       </c>
-      <c r="L56" s="7">
+      <c r="L56" s="5">
         <f t="shared" si="10"/>
         <v>265364.49</v>
       </c>
-      <c r="M56" s="14">
+      <c r="M56" s="5">
         <f t="shared" si="10"/>
         <v>122687.55</v>
       </c>
-      <c r="N56" s="7">
+      <c r="N56" s="5">
         <f t="shared" si="10"/>
         <v>165703.1</v>
       </c>
-      <c r="O56" s="14">
+      <c r="O56" s="5">
         <f t="shared" si="10"/>
         <v>96916.54</v>
       </c>
-      <c r="P56" s="14">
+      <c r="P56" s="5">
         <f t="shared" si="10"/>
         <v>368073.39</v>
       </c>
-      <c r="Q56" s="14">
+      <c r="Q56" s="5">
         <f t="shared" si="10"/>
         <v>1347302.95</v>
       </c>
-      <c r="R56" s="14">
+      <c r="R56" s="5">
         <f t="shared" si="10"/>
         <v>1175433.54</v>
       </c>
@@ -2656,328 +2659,429 @@
         <v>0</v>
       </c>
       <c r="Z56" s="5">
-        <f t="shared" ref="Z56:Z57" si="12">sum(N56:Y56)</f>
+        <f>sum(N56:Y56)</f>
         <v>3153429.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="7">
-        <f t="shared" ref="B57:Y57" si="11">sum(B52,B45,B38,B31,B24,B17,B10,B3)</f>
-        <v>4</v>
-      </c>
-      <c r="C57" s="7">
+        <v>14</v>
+      </c>
+      <c r="B57" s="5">
+        <f t="shared" ref="B57:Z57" si="11">average(B51,B44,B37,B30,B23,B16,B9,B2)</f>
+        <v>44748.75</v>
+      </c>
+      <c r="C57" s="5">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="D57" s="7">
+        <v>24195.1</v>
+      </c>
+      <c r="D57" s="5">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="E57" s="7">
+        <v>53237.082</v>
+      </c>
+      <c r="E57" s="5">
         <f t="shared" si="11"/>
-        <v>24</v>
-      </c>
-      <c r="F57" s="7">
+        <v>31851.46167</v>
+      </c>
+      <c r="F57" s="5">
         <f t="shared" si="11"/>
-        <v>39</v>
-      </c>
-      <c r="G57" s="7">
+        <v>79725.425</v>
+      </c>
+      <c r="G57" s="5">
         <f t="shared" si="11"/>
-        <v>60</v>
-      </c>
-      <c r="H57" s="7">
+        <v>146456.094</v>
+      </c>
+      <c r="H57" s="5">
         <f t="shared" si="11"/>
-        <v>44</v>
-      </c>
-      <c r="I57" s="7">
+        <v>114050.0133</v>
+      </c>
+      <c r="I57" s="5">
         <f t="shared" si="11"/>
-        <v>33</v>
-      </c>
-      <c r="J57" s="7">
+        <v>53089.65333</v>
+      </c>
+      <c r="J57" s="5">
         <f t="shared" si="11"/>
-        <v>36</v>
-      </c>
-      <c r="K57" s="7">
+        <v>67578.118</v>
+      </c>
+      <c r="K57" s="5">
         <f t="shared" si="11"/>
-        <v>71</v>
-      </c>
-      <c r="L57" s="7">
+        <v>138239.7</v>
+      </c>
+      <c r="L57" s="5">
         <f t="shared" si="11"/>
-        <v>35</v>
-      </c>
-      <c r="M57" s="7">
+        <v>53072.898</v>
+      </c>
+      <c r="M57" s="5">
         <f t="shared" si="11"/>
-        <v>21</v>
-      </c>
-      <c r="N57" s="7">
+        <v>20447.925</v>
+      </c>
+      <c r="N57" s="5">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="O57" s="7">
+        <v>55234.36667</v>
+      </c>
+      <c r="O57" s="5">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="P57" s="7">
+        <v>19383.308</v>
+      </c>
+      <c r="P57" s="5">
         <f t="shared" si="11"/>
-        <v>57</v>
-      </c>
-      <c r="Q57" s="7">
+        <v>46009.17375</v>
+      </c>
+      <c r="Q57" s="5">
         <f t="shared" si="11"/>
-        <v>127</v>
-      </c>
-      <c r="R57" s="7">
+        <v>168412.8688</v>
+      </c>
+      <c r="R57" s="5">
         <f t="shared" si="11"/>
-        <v>89</v>
-      </c>
-      <c r="S57" s="7">
+        <v>146929.1925</v>
+      </c>
+      <c r="S57" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="T57" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T57" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U57" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U57" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V57" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V57" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W57" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W57" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="X57" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X57" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Y57" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y57" s="7" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Z57" s="7">
-        <f t="shared" si="12"/>
-        <v>307</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z57" s="5">
+        <f t="shared" si="11"/>
+        <v>394178.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="7">
+        <f t="shared" ref="B58:Y58" si="12">sum(B52,B45,B38,B31,B24,B17,B10,B3)</f>
+        <v>4</v>
+      </c>
+      <c r="C58" s="7">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="D58" s="7">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="E58" s="7">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="F58" s="7">
+        <f t="shared" si="12"/>
+        <v>39</v>
+      </c>
+      <c r="G58" s="7">
+        <f t="shared" si="12"/>
+        <v>60</v>
+      </c>
+      <c r="H58" s="7">
+        <f t="shared" si="12"/>
+        <v>44</v>
+      </c>
+      <c r="I58" s="7">
+        <f t="shared" si="12"/>
+        <v>33</v>
+      </c>
+      <c r="J58" s="7">
+        <f t="shared" si="12"/>
+        <v>36</v>
+      </c>
+      <c r="K58" s="7">
+        <f t="shared" si="12"/>
+        <v>71</v>
+      </c>
+      <c r="L58" s="7">
+        <f t="shared" si="12"/>
+        <v>35</v>
+      </c>
+      <c r="M58" s="7">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="N58" s="7">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="O58" s="7">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="P58" s="7">
+        <f t="shared" si="12"/>
+        <v>57</v>
+      </c>
+      <c r="Q58" s="7">
+        <f t="shared" si="12"/>
+        <v>127</v>
+      </c>
+      <c r="R58" s="7">
+        <f t="shared" si="12"/>
+        <v>89</v>
+      </c>
+      <c r="S58" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="U58" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V58" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W58" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X58" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Y58" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Z58" s="7">
+        <f>sum(N58:Y58)</f>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B58" s="7">
-        <f t="shared" ref="B58:Y58" si="13">AVERAGE(B53,B46,B39,B32,B25,B18,B11,B4)</f>
+      <c r="B59" s="5">
+        <f t="shared" ref="B59:Y59" si="13">AVERAGE(B53,B46,B39,B32,B25,B18,B11,B4)</f>
         <v>22374.375</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C59" s="5">
         <f t="shared" si="13"/>
         <v>14428.8725</v>
       </c>
-      <c r="D58" s="14">
+      <c r="D59" s="5">
         <f t="shared" si="13"/>
         <v>16038.198</v>
       </c>
-      <c r="E58" s="14">
+      <c r="E59" s="5">
         <f t="shared" si="13"/>
         <v>13527.67</v>
       </c>
-      <c r="F58" s="14">
+      <c r="F59" s="5">
         <f t="shared" si="13"/>
         <v>10810.03167</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G59" s="5">
         <f t="shared" si="13"/>
         <v>14472.008</v>
       </c>
-      <c r="H58" s="14">
+      <c r="H59" s="5">
         <f t="shared" si="13"/>
         <v>20600.915</v>
       </c>
-      <c r="I58" s="14">
+      <c r="I59" s="5">
         <f t="shared" si="13"/>
         <v>14129.13167</v>
       </c>
-      <c r="J58" s="7">
+      <c r="J59" s="5">
         <f t="shared" si="13"/>
         <v>10893.582</v>
       </c>
-      <c r="K58" s="7">
+      <c r="K59" s="5">
         <f t="shared" si="13"/>
         <v>10478.64</v>
       </c>
-      <c r="L58" s="7">
+      <c r="L59" s="5">
         <f t="shared" si="13"/>
         <v>7528.564</v>
       </c>
-      <c r="M58" s="14">
+      <c r="M59" s="5">
         <f t="shared" si="13"/>
         <v>5842.406667</v>
       </c>
-      <c r="N58" s="7">
+      <c r="N59" s="5">
         <f t="shared" si="13"/>
         <v>10965.62667</v>
       </c>
-      <c r="O58" s="14">
+      <c r="O59" s="5">
         <f t="shared" si="13"/>
         <v>9192.024</v>
       </c>
-      <c r="P58" s="14">
+      <c r="P59" s="5">
         <f t="shared" si="13"/>
         <v>5427.795</v>
       </c>
-      <c r="Q58" s="14">
+      <c r="Q59" s="5">
         <f t="shared" si="13"/>
         <v>10327.15375</v>
       </c>
-      <c r="R58" s="14">
+      <c r="R59" s="5">
         <f t="shared" si="13"/>
         <v>14002.4825</v>
       </c>
-      <c r="S58" s="7" t="str">
+      <c r="S59" s="7" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T58" s="7" t="str">
+      <c r="T59" s="7" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U58" s="7" t="str">
+      <c r="U59" s="7" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V58" s="7" t="str">
+      <c r="V59" s="7" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W58" s="7" t="str">
+      <c r="W59" s="7" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X58" s="7" t="str">
+      <c r="X59" s="7" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y58" s="7" t="str">
+      <c r="Y59" s="7" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z58" s="5" t="str">
-        <f>average(N58:Y58)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
+      <c r="Z59" s="5" t="str">
+        <f>average(N59:Y59)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B59" s="9">
-        <f t="shared" ref="B59:Y59" si="14">AVERAGE(B54,B47,B40,B33,B26,B19,B12,B5)</f>
+      <c r="B60" s="9">
+        <f t="shared" ref="B60:Y60" si="14">AVERAGE(B54,B47,B40,B33,B26,B19,B12,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C60" s="9">
         <f t="shared" si="14"/>
         <v>0.309525</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D60" s="9">
         <f t="shared" si="14"/>
         <v>0.42125</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E60" s="9">
         <f t="shared" si="14"/>
         <v>0.42478</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F60" s="9">
         <f t="shared" si="14"/>
         <v>0.40488</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G60" s="9">
         <f t="shared" si="14"/>
         <v>0.45414</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H60" s="9">
         <f t="shared" si="14"/>
         <v>0.40556</v>
       </c>
-      <c r="I59" s="9">
+      <c r="I60" s="9">
         <f t="shared" si="14"/>
         <v>0.31688</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J60" s="9">
         <f t="shared" si="14"/>
         <v>0.41248</v>
       </c>
-      <c r="K59" s="9">
+      <c r="K60" s="9">
         <f t="shared" si="14"/>
         <v>0.29162</v>
       </c>
-      <c r="L59" s="9">
+      <c r="L60" s="9">
         <f t="shared" si="14"/>
         <v>0.36604</v>
       </c>
-      <c r="M59" s="9">
+      <c r="M60" s="9">
         <f t="shared" si="14"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N59" s="9">
+      <c r="N60" s="9">
         <f t="shared" si="14"/>
         <v>0.26642</v>
       </c>
-      <c r="O59" s="9">
+      <c r="O60" s="9">
         <f t="shared" si="14"/>
         <v>0.2047833333</v>
       </c>
-      <c r="P59" s="9">
+      <c r="P60" s="9">
         <f t="shared" si="14"/>
         <v>0.3297714286</v>
       </c>
-      <c r="Q59" s="9">
+      <c r="Q60" s="9">
         <f t="shared" si="14"/>
         <v>0.2484571429</v>
       </c>
-      <c r="R59" s="9">
+      <c r="R60" s="9">
         <f t="shared" si="14"/>
         <v>0.11035</v>
       </c>
-      <c r="S59" s="7" t="str">
+      <c r="S60" s="7" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T59" s="7" t="str">
+      <c r="T60" s="7" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U59" s="7" t="str">
+      <c r="U60" s="7" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V59" s="7" t="str">
+      <c r="V60" s="7" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W59" s="7" t="str">
+      <c r="W60" s="7" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X59" s="7" t="str">
+      <c r="X60" s="7" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y59" s="7" t="str">
+      <c r="Y60" s="7" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z59" s="7" t="str">
-        <f>average(R59:Y59)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="1"/>
-      <c r="S69" s="9"/>
+      <c r="Z60" s="7" t="str">
+        <f>average(R60:Y60)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="1"/>
@@ -3000,73 +3104,77 @@
       <c r="S74" s="9"/>
     </row>
     <row r="75">
+      <c r="B75" s="1"/>
       <c r="S75" s="9"/>
     </row>
-    <row r="99">
-      <c r="B99" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C99" s="9" t="str">
-        <f t="shared" ref="C99:R99" si="15">average(C69:C74)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D99" s="9" t="str">
+    <row r="76">
+      <c r="S76" s="9"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="9" t="str">
+        <f t="shared" ref="C100:R100" si="15">average(C70:C75)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E99" s="9" t="str">
+      <c r="E100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F99" s="9" t="str">
+      <c r="F100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G99" s="9" t="str">
+      <c r="G100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H99" s="9" t="str">
+      <c r="H100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I99" s="9" t="str">
+      <c r="I100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J99" s="9" t="str">
+      <c r="J100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K99" s="9" t="str">
+      <c r="K100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L99" s="9" t="str">
+      <c r="L100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M99" s="9" t="str">
+      <c r="M100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N99" s="9" t="str">
+      <c r="N100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O99" s="9" t="str">
+      <c r="O100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P99" s="9" t="str">
+      <c r="P100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q99" s="9" t="str">
+      <c r="Q100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R99" s="9" t="str">
+      <c r="R100" s="9" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="16">
   <si>
     <t>Jamie Jenkins</t>
   </si>
@@ -2558,6 +2558,83 @@
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="55">
+      <c r="B55" s="2">
+        <v>45658.0</v>
+      </c>
+      <c r="C55" s="2">
+        <v>45689.0</v>
+      </c>
+      <c r="D55" s="2">
+        <v>45717.0</v>
+      </c>
+      <c r="E55" s="2">
+        <v>45748.0</v>
+      </c>
+      <c r="F55" s="2">
+        <v>45778.0</v>
+      </c>
+      <c r="G55" s="2">
+        <v>45809.0</v>
+      </c>
+      <c r="H55" s="2">
+        <v>45839.0</v>
+      </c>
+      <c r="I55" s="2">
+        <v>45870.0</v>
+      </c>
+      <c r="J55" s="2">
+        <v>45901.0</v>
+      </c>
+      <c r="K55" s="2">
+        <v>45931.0</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M55" s="2">
+        <v>45992.0</v>
+      </c>
+      <c r="N55" s="2">
+        <v>46023.0</v>
+      </c>
+      <c r="O55" s="2">
+        <v>46054.0</v>
+      </c>
+      <c r="P55" s="2">
+        <v>46082.0</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>46113.0</v>
+      </c>
+      <c r="R55" s="2">
+        <v>46143.0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>46174.0</v>
+      </c>
+      <c r="T55" s="2">
+        <v>46204.0</v>
+      </c>
+      <c r="U55" s="2">
+        <v>46235.0</v>
+      </c>
+      <c r="V55" s="2">
+        <v>46266.0</v>
+      </c>
+      <c r="W55" s="2">
+        <v>46296.0</v>
+      </c>
+      <c r="X55" s="2">
+        <v>46327.0</v>
+      </c>
+      <c r="Y55" s="2">
+        <v>46357.0</v>
+      </c>
+      <c r="Z55" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" s="3" t="s">
         <v>3</v>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -2850,7 +2850,7 @@
         <v>4</v>
       </c>
       <c r="B58" s="7">
-        <f t="shared" ref="B58:Y58" si="12">sum(B52,B45,B38,B31,B24,B17,B10,B3)</f>
+        <f t="shared" ref="B58:Q58" si="12">sum(B52,B45,B38,B31,B24,B17,B10,B3)</f>
         <v>4</v>
       </c>
       <c r="C58" s="7">
@@ -2914,40 +2914,40 @@
         <v>127</v>
       </c>
       <c r="R58" s="7">
-        <f t="shared" si="12"/>
-        <v>89</v>
+        <f>AVERAGE(R52,R45,R38,R31,R24,R17,R10,R3)</f>
+        <v>11.125</v>
       </c>
       <c r="S58" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="S58:Y58" si="13">sum(S52,S45,S38,S31,S24,S17,S10,S3)</f>
         <v>0</v>
       </c>
       <c r="T58" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U58" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="V58" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="W58" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X58" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Y58" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Z58" s="7">
         <f>sum(N58:Y58)</f>
-        <v>307</v>
+        <v>229.125</v>
       </c>
     </row>
     <row r="59">
@@ -2955,99 +2955,99 @@
         <v>5</v>
       </c>
       <c r="B59" s="5">
-        <f t="shared" ref="B59:Y59" si="13">AVERAGE(B53,B46,B39,B32,B25,B18,B11,B4)</f>
+        <f t="shared" ref="B59:Y59" si="14">AVERAGE(B53,B46,B39,B32,B25,B18,B11,B4)</f>
         <v>22374.375</v>
       </c>
       <c r="C59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14428.8725</v>
       </c>
       <c r="D59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16038.198</v>
       </c>
       <c r="E59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13527.67</v>
       </c>
       <c r="F59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10810.03167</v>
       </c>
       <c r="G59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14472.008</v>
       </c>
       <c r="H59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20600.915</v>
       </c>
       <c r="I59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14129.13167</v>
       </c>
       <c r="J59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10893.582</v>
       </c>
       <c r="K59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10478.64</v>
       </c>
       <c r="L59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7528.564</v>
       </c>
       <c r="M59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5842.406667</v>
       </c>
       <c r="N59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10965.62667</v>
       </c>
       <c r="O59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9192.024</v>
       </c>
       <c r="P59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5427.795</v>
       </c>
       <c r="Q59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10327.15375</v>
       </c>
       <c r="R59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14002.4825</v>
       </c>
       <c r="S59" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T59" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U59" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V59" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W59" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X59" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y59" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z59" s="5" t="str">
@@ -3060,99 +3060,99 @@
         <v>6</v>
       </c>
       <c r="B60" s="9">
-        <f t="shared" ref="B60:Y60" si="14">AVERAGE(B54,B47,B40,B33,B26,B19,B12,B5)</f>
+        <f t="shared" ref="B60:Y60" si="15">AVERAGE(B54,B47,B40,B33,B26,B19,B12,B5)</f>
         <v>0.3444333333</v>
       </c>
       <c r="C60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.309525</v>
       </c>
       <c r="D60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.42125</v>
       </c>
       <c r="E60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.42478</v>
       </c>
       <c r="F60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.40488</v>
       </c>
       <c r="G60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.45414</v>
       </c>
       <c r="H60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.40556</v>
       </c>
       <c r="I60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.31688</v>
       </c>
       <c r="J60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.41248</v>
       </c>
       <c r="K60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.29162</v>
       </c>
       <c r="L60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.36604</v>
       </c>
       <c r="M60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.3687333333</v>
       </c>
       <c r="N60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.26642</v>
       </c>
       <c r="O60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2047833333</v>
       </c>
       <c r="P60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.3297714286</v>
       </c>
       <c r="Q60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2484571429</v>
       </c>
       <c r="R60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.11035</v>
       </c>
       <c r="S60" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T60" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U60" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V60" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W60" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X60" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y60" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z60" s="7" t="str">
@@ -3192,67 +3192,67 @@
         <v>15</v>
       </c>
       <c r="C100" s="9" t="str">
-        <f t="shared" ref="C100:R100" si="15">average(C70:C75)</f>
+        <f t="shared" ref="C100:R100" si="16">average(C70:C75)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R100" s="9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -160,6 +160,7 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2849,72 +2850,72 @@
       <c r="A58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B58" s="7">
-        <f t="shared" ref="B58:Q58" si="12">sum(B52,B45,B38,B31,B24,B17,B10,B3)</f>
+      <c r="B58" s="15">
+        <f t="shared" ref="B58:R58" si="12">AVERAGE(B52,B45,B38,B31,B24,B17,B10,B3)</f>
+        <v>2</v>
+      </c>
+      <c r="C58" s="15">
+        <f t="shared" si="12"/>
+        <v>1.75</v>
+      </c>
+      <c r="D58" s="15">
+        <f t="shared" si="12"/>
+        <v>3.4</v>
+      </c>
+      <c r="E58" s="15">
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="C58" s="7">
+      <c r="F58" s="15">
+        <f t="shared" si="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="G58" s="15">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="H58" s="15">
+        <f t="shared" si="12"/>
+        <v>7.333333333</v>
+      </c>
+      <c r="I58" s="15">
+        <f t="shared" si="12"/>
+        <v>5.5</v>
+      </c>
+      <c r="J58" s="15">
+        <f t="shared" si="12"/>
+        <v>7.2</v>
+      </c>
+      <c r="K58" s="15">
+        <f t="shared" si="12"/>
+        <v>14.2</v>
+      </c>
+      <c r="L58" s="15">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="D58" s="7">
+      <c r="M58" s="15">
         <f t="shared" si="12"/>
-        <v>17</v>
-      </c>
-      <c r="E58" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="N58" s="15">
         <f t="shared" si="12"/>
-        <v>24</v>
-      </c>
-      <c r="F58" s="7">
+        <v>5.666666667</v>
+      </c>
+      <c r="O58" s="15">
         <f t="shared" si="12"/>
-        <v>39</v>
-      </c>
-      <c r="G58" s="7">
+        <v>3.4</v>
+      </c>
+      <c r="P58" s="15">
         <f t="shared" si="12"/>
-        <v>60</v>
-      </c>
-      <c r="H58" s="7">
+        <v>7.125</v>
+      </c>
+      <c r="Q58" s="15">
         <f t="shared" si="12"/>
-        <v>44</v>
-      </c>
-      <c r="I58" s="7">
+        <v>15.875</v>
+      </c>
+      <c r="R58" s="15">
         <f t="shared" si="12"/>
-        <v>33</v>
-      </c>
-      <c r="J58" s="7">
-        <f t="shared" si="12"/>
-        <v>36</v>
-      </c>
-      <c r="K58" s="7">
-        <f t="shared" si="12"/>
-        <v>71</v>
-      </c>
-      <c r="L58" s="7">
-        <f t="shared" si="12"/>
-        <v>35</v>
-      </c>
-      <c r="M58" s="7">
-        <f t="shared" si="12"/>
-        <v>21</v>
-      </c>
-      <c r="N58" s="7">
-        <f t="shared" si="12"/>
-        <v>17</v>
-      </c>
-      <c r="O58" s="7">
-        <f t="shared" si="12"/>
-        <v>17</v>
-      </c>
-      <c r="P58" s="7">
-        <f t="shared" si="12"/>
-        <v>57</v>
-      </c>
-      <c r="Q58" s="7">
-        <f t="shared" si="12"/>
-        <v>127</v>
-      </c>
-      <c r="R58" s="7">
-        <f>AVERAGE(R52,R45,R38,R31,R24,R17,R10,R3)</f>
         <v>11.125</v>
       </c>
       <c r="S58" s="7">
@@ -2945,9 +2946,9 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z58" s="7">
+      <c r="Z58" s="15">
         <f>sum(N58:Y58)</f>
-        <v>229.125</v>
+        <v>43.19166667</v>
       </c>
     </row>
     <row r="59">

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -85,7 +85,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -126,31 +125,26 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
@@ -376,12 +370,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="17.88"/>
+    <col customWidth="1" min="2" max="6" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,7 +456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -517,7 +512,7 @@
         <v>644158.88</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -568,12 +563,12 @@
       </c>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
-      <c r="Z3" s="7">
+      <c r="Z3" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -627,72 +622,76 @@
         <v>13175.23</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>0.3333</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>0.3571</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>0.3333</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>0.375</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>0.52</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>0.3333</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>0.1111</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>0.28</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="7">
         <v>0.2353</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>0.24</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="7">
         <v>0.3333</v>
       </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="8">
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
         <v>0.1818</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="7">
         <v>0.1538</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="7">
         <v>0.3333</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="7">
         <v>0.38</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="7">
         <v>0.1</v>
       </c>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9">
+      <c r="S5" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7">
         <f t="shared" si="2"/>
-        <v>0.22978</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>0.1914833333</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1"/>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -772,7 +771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
@@ -825,13 +824,13 @@
         <v>118400.53</v>
       </c>
       <c r="S9" s="4"/>
-      <c r="W9" s="10"/>
+      <c r="W9" s="9"/>
       <c r="Z9" s="5">
         <f t="shared" ref="Z9:Z10" si="3">sum(N9:Y9)</f>
         <v>658167.27</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -884,13 +883,13 @@
         <v>9.0</v>
       </c>
       <c r="S10" s="6"/>
-      <c r="W10" s="10"/>
-      <c r="Z10" s="7">
+      <c r="W10" s="9"/>
+      <c r="Z10" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
@@ -942,98 +941,100 @@
       <c r="R11" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W11" s="10"/>
+      <c r="W11" s="9"/>
       <c r="Z11" s="5">
         <f>average(N11:Y11)</f>
         <v>9918.804</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>0.5</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>0.2381</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>0.375</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>0.4231</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>0.4333</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>0.4231</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>0.25</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>0.2632</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="7">
         <v>0.4211</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="7">
         <v>0.2973</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="7">
         <v>0.3182</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="7">
         <v>0.6429</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="7">
         <v>0.5385</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="7">
         <v>0.2759</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="7">
         <v>0.3</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="Q12" s="7">
         <v>0.2373</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="7">
         <v>0.0244</v>
       </c>
-      <c r="S12" s="9"/>
-      <c r="T12" s="11"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9">
+      <c r="S12" s="8">
+        <v>0.0714</v>
+      </c>
+      <c r="T12" s="10"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7">
         <f>average(R12:Y12)</f>
-        <v>0.0244</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="S13" s="9"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-    </row>
-    <row r="14">
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-    </row>
-    <row r="15">
+        <v>0.0479</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="S13" s="7"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
@@ -1113,7 +1114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>3</v>
       </c>
@@ -1166,7 +1167,7 @@
         <v>566987.93</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1213,12 +1214,12 @@
         <v>7.0</v>
       </c>
       <c r="S17" s="6"/>
-      <c r="Z17" s="7">
+      <c r="Z17" s="3">
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1269,66 +1270,70 @@
         <v>15074.612</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7">
         <v>0.6667</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="7">
         <v>0.4286</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <v>0.4286</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>0.5</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="7">
         <v>0.5333</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="7">
         <v>0.381</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="7">
         <v>0.2963</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="7">
         <v>0.3571</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="7">
         <v>0.33</v>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="7">
         <v>0.2308</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="7">
         <v>0.129</v>
       </c>
-      <c r="P19" s="8">
+      <c r="P19" s="7">
         <v>0.3469</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q19" s="7">
         <v>0.2</v>
       </c>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="7" t="str">
+      <c r="R19" s="7"/>
+      <c r="S19" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7">
         <f>average(R19:Y19)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
@@ -1408,7 +1413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,7 +1472,7 @@
         <v>172532.09</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1520,13 +1525,13 @@
         <v>10.0</v>
       </c>
       <c r="S24" s="6"/>
-      <c r="W24" s="10"/>
-      <c r="Z24" s="7">
+      <c r="W24" s="9"/>
+      <c r="Z24" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>5</v>
       </c>
@@ -1578,77 +1583,81 @@
       <c r="R25" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T25" s="11"/>
-      <c r="W25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="W25" s="9"/>
       <c r="Z25" s="5">
         <f>average(N25:Y25)</f>
         <v>3625.05</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="8">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7">
         <v>0.2143</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>0.5556</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="7">
         <v>0.25</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="7">
         <v>0.2632</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="7">
         <v>0.3714</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="7">
         <v>0.6667</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="7">
         <v>0.2222</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="7">
         <v>0.4</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="7">
         <v>0.3636</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="7">
         <v>0.1852</v>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="7">
         <v>0.1333</v>
       </c>
-      <c r="N26" s="8">
+      <c r="N26" s="7">
         <v>0.2381</v>
       </c>
-      <c r="O26" s="8">
+      <c r="O26" s="7">
         <v>0.2308</v>
       </c>
-      <c r="P26" s="8">
+      <c r="P26" s="7">
         <v>0.3636</v>
       </c>
-      <c r="Q26" s="8">
+      <c r="Q26" s="7">
         <v>0.2414</v>
       </c>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="13"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="7" t="str">
+      <c r="R26" s="7"/>
+      <c r="S26" s="8">
+        <v>0.125</v>
+      </c>
+      <c r="T26" s="12"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="7">
         <f>average(R26:Y26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -1728,7 +1737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>3</v>
       </c>
@@ -1768,7 +1777,7 @@
       <c r="M30" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N30" s="10"/>
+      <c r="N30" s="9"/>
       <c r="O30" s="4">
         <v>8067.86</v>
       </c>
@@ -1788,7 +1797,7 @@
         <v>424826.95</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>4</v>
       </c>
@@ -1842,12 +1851,12 @@
       </c>
       <c r="S31" s="6"/>
       <c r="T31" s="6"/>
-      <c r="Z31" s="7">
+      <c r="Z31" s="3">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1904,70 +1913,74 @@
         <v>11771.765</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="7">
         <v>0.2</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <v>0.4286</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>0.4211</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="7">
         <v>0.4091</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="7">
         <v>0.3793</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="7">
         <v>0.7143</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="7">
         <v>0.5</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="7">
         <v>0.2857</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="7">
         <v>0.625</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="7">
         <v>0.2609</v>
       </c>
-      <c r="L33" s="8">
+      <c r="L33" s="7">
         <v>0.6364</v>
       </c>
-      <c r="M33" s="9"/>
-      <c r="N33" s="8">
+      <c r="M33" s="7"/>
+      <c r="N33" s="7">
         <v>0.1429</v>
       </c>
-      <c r="O33" s="8">
+      <c r="O33" s="7">
         <v>0.2963</v>
       </c>
-      <c r="P33" s="8">
+      <c r="P33" s="7">
         <v>0.2909</v>
       </c>
-      <c r="Q33" s="8">
+      <c r="Q33" s="7">
         <v>0.303</v>
       </c>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="7" t="str">
+      <c r="R33" s="7"/>
+      <c r="S33" s="8">
+        <v>0.3333</v>
+      </c>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="7">
         <f>average(R33:Y33)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
@@ -2047,7 +2060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>3</v>
       </c>
@@ -2067,7 +2080,7 @@
         <v>285109.85</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>4</v>
       </c>
@@ -2082,16 +2095,16 @@
       </c>
       <c r="S38" s="6"/>
       <c r="T38" s="6"/>
-      <c r="Z38" s="7">
+      <c r="Z38" s="3">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L39" s="10"/>
+      <c r="L39" s="9"/>
       <c r="P39" s="4">
         <v>1874.92</v>
       </c>
@@ -2106,48 +2119,52 @@
         <v>8284.286667</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="8">
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7">
         <v>0.1429</v>
       </c>
-      <c r="P40" s="8">
+      <c r="P40" s="7">
         <v>0.3404</v>
       </c>
-      <c r="Q40" s="8">
+      <c r="Q40" s="7">
         <v>0.1957</v>
       </c>
-      <c r="R40" s="8">
+      <c r="R40" s="7">
         <v>0.1111</v>
       </c>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
-      <c r="X40" s="9"/>
-      <c r="Y40" s="9"/>
-      <c r="Z40" s="9">
+      <c r="S40" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7">
         <f>average(R40:Y40)</f>
-        <v>0.1111</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>0.05555</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
@@ -2227,7 +2244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2247,7 +2264,7 @@
         <v>204565.15</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2262,12 +2279,12 @@
       </c>
       <c r="S45" s="6"/>
       <c r="T45" s="6"/>
-      <c r="Z45" s="7">
+      <c r="Z45" s="3">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2285,46 +2302,50 @@
         <v>5090.413333</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7">
         <v>0.3333</v>
       </c>
-      <c r="Q47" s="8">
+      <c r="Q47" s="7">
         <v>0.1818</v>
       </c>
-      <c r="R47" s="8">
+      <c r="R47" s="7">
         <v>0.2059</v>
       </c>
-      <c r="S47" s="9"/>
-      <c r="T47" s="9"/>
-      <c r="U47" s="9"/>
-      <c r="V47" s="9"/>
-      <c r="W47" s="9"/>
-      <c r="X47" s="9"/>
-      <c r="Y47" s="9"/>
-      <c r="Z47" s="9">
+      <c r="S47" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="7">
         <f>average(R47:Y47)</f>
-        <v>0.2059</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>0.10295</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>13</v>
       </c>
@@ -2404,7 +2425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
         <v>3</v>
       </c>
@@ -2423,7 +2444,7 @@
       <c r="I51" s="4">
         <v>3769.0</v>
       </c>
-      <c r="L51" s="10"/>
+      <c r="L51" s="9"/>
       <c r="M51" s="4">
         <v>2632.6</v>
       </c>
@@ -2446,7 +2467,7 @@
         <v>197081.4</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2482,12 +2503,12 @@
       </c>
       <c r="S52" s="6"/>
       <c r="T52" s="6"/>
-      <c r="Z52" s="7">
+      <c r="Z52" s="3">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="s">
         <v>5</v>
       </c>
@@ -2526,40 +2547,40 @@
         <v>11771.8175</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
-      <c r="N54" s="9"/>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="9"/>
-      <c r="S54" s="9"/>
-      <c r="T54" s="9"/>
-      <c r="U54" s="9"/>
-      <c r="V54" s="9"/>
-      <c r="W54" s="9"/>
-      <c r="X54" s="9"/>
-      <c r="Y54" s="9"/>
-      <c r="Z54" s="7" t="str">
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7"/>
+      <c r="O54" s="7"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="3" t="str">
         <f>average(R54:Y54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="B55" s="2">
         <v>45658.0</v>
       </c>
@@ -2636,7 +2657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
         <v>3</v>
       </c>
@@ -2708,31 +2729,31 @@
         <f t="shared" si="10"/>
         <v>1175433.54</v>
       </c>
-      <c r="S56" s="14">
+      <c r="S56" s="13">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T56" s="14">
+      <c r="T56" s="13">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U56" s="7">
+      <c r="U56" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="V56" s="7">
+      <c r="V56" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="W56" s="7">
+      <c r="W56" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X56" s="7">
+      <c r="X56" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Y56" s="7">
+      <c r="Y56" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -2741,7 +2762,7 @@
         <v>3153429.52</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
         <v>14</v>
       </c>
@@ -2813,31 +2834,31 @@
         <f t="shared" si="11"/>
         <v>146929.1925</v>
       </c>
-      <c r="S57" s="7" t="str">
+      <c r="S57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T57" s="7" t="str">
+      <c r="T57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U57" s="7" t="str">
+      <c r="U57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V57" s="7" t="str">
+      <c r="V57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W57" s="7" t="str">
+      <c r="W57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X57" s="7" t="str">
+      <c r="X57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y57" s="7" t="str">
+      <c r="Y57" s="3" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
@@ -2846,112 +2867,112 @@
         <v>394178.69</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B58" s="15">
+      <c r="B58" s="14">
         <f t="shared" ref="B58:R58" si="12">AVERAGE(B52,B45,B38,B31,B24,B17,B10,B3)</f>
         <v>2</v>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="14">
         <f t="shared" si="12"/>
         <v>1.75</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="14">
         <f t="shared" si="12"/>
         <v>3.4</v>
       </c>
-      <c r="E58" s="15">
+      <c r="E58" s="14">
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="F58" s="15">
+      <c r="F58" s="14">
         <f t="shared" si="12"/>
         <v>6.5</v>
       </c>
-      <c r="G58" s="15">
+      <c r="G58" s="14">
         <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="H58" s="15">
+      <c r="H58" s="14">
         <f t="shared" si="12"/>
         <v>7.333333333</v>
       </c>
-      <c r="I58" s="15">
+      <c r="I58" s="14">
         <f t="shared" si="12"/>
         <v>5.5</v>
       </c>
-      <c r="J58" s="15">
+      <c r="J58" s="14">
         <f t="shared" si="12"/>
         <v>7.2</v>
       </c>
-      <c r="K58" s="15">
+      <c r="K58" s="14">
         <f t="shared" si="12"/>
         <v>14.2</v>
       </c>
-      <c r="L58" s="15">
+      <c r="L58" s="14">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="M58" s="15">
+      <c r="M58" s="14">
         <f t="shared" si="12"/>
         <v>3.5</v>
       </c>
-      <c r="N58" s="15">
+      <c r="N58" s="14">
         <f t="shared" si="12"/>
         <v>5.666666667</v>
       </c>
-      <c r="O58" s="15">
+      <c r="O58" s="14">
         <f t="shared" si="12"/>
         <v>3.4</v>
       </c>
-      <c r="P58" s="15">
+      <c r="P58" s="14">
         <f t="shared" si="12"/>
         <v>7.125</v>
       </c>
-      <c r="Q58" s="15">
+      <c r="Q58" s="14">
         <f t="shared" si="12"/>
         <v>15.875</v>
       </c>
-      <c r="R58" s="15">
+      <c r="R58" s="14">
         <f t="shared" si="12"/>
         <v>11.125</v>
       </c>
-      <c r="S58" s="7">
+      <c r="S58" s="3">
         <f t="shared" ref="S58:Y58" si="13">sum(S52,S45,S38,S31,S24,S17,S10,S3)</f>
         <v>0</v>
       </c>
-      <c r="T58" s="7">
+      <c r="T58" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U58" s="7">
+      <c r="U58" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V58" s="7">
+      <c r="V58" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="W58" s="7">
+      <c r="W58" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X58" s="7">
+      <c r="X58" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Y58" s="7">
+      <c r="Y58" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z58" s="15">
+      <c r="Z58" s="14">
         <f>sum(N58:Y58)</f>
         <v>43.19166667</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3023,31 +3044,31 @@
         <f t="shared" si="14"/>
         <v>14002.4825</v>
       </c>
-      <c r="S59" s="7" t="str">
+      <c r="S59" s="3" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T59" s="7" t="str">
+      <c r="T59" s="3" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U59" s="7" t="str">
+      <c r="U59" s="3" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V59" s="7" t="str">
+      <c r="V59" s="3" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W59" s="7" t="str">
+      <c r="W59" s="3" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X59" s="7" t="str">
+      <c r="X59" s="3" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y59" s="7" t="str">
+      <c r="Y59" s="3" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
@@ -3056,207 +3077,1139 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="7">
         <f t="shared" ref="B60:Y60" si="15">AVERAGE(B54,B47,B40,B33,B26,B19,B12,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="7">
         <f t="shared" si="15"/>
         <v>0.309525</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="7">
         <f t="shared" si="15"/>
         <v>0.42125</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="7">
         <f t="shared" si="15"/>
         <v>0.42478</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="7">
         <f t="shared" si="15"/>
         <v>0.40488</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="7">
         <f t="shared" si="15"/>
         <v>0.45414</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="7">
         <f t="shared" si="15"/>
         <v>0.40556</v>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="7">
         <f t="shared" si="15"/>
         <v>0.31688</v>
       </c>
-      <c r="J60" s="9">
+      <c r="J60" s="7">
         <f t="shared" si="15"/>
         <v>0.41248</v>
       </c>
-      <c r="K60" s="9">
+      <c r="K60" s="7">
         <f t="shared" si="15"/>
         <v>0.29162</v>
       </c>
-      <c r="L60" s="9">
+      <c r="L60" s="7">
         <f t="shared" si="15"/>
         <v>0.36604</v>
       </c>
-      <c r="M60" s="9">
+      <c r="M60" s="7">
         <f t="shared" si="15"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N60" s="9">
+      <c r="N60" s="7">
         <f t="shared" si="15"/>
         <v>0.26642</v>
       </c>
-      <c r="O60" s="9">
+      <c r="O60" s="7">
         <f t="shared" si="15"/>
         <v>0.2047833333</v>
       </c>
-      <c r="P60" s="9">
+      <c r="P60" s="7">
         <f t="shared" si="15"/>
         <v>0.3297714286</v>
       </c>
-      <c r="Q60" s="9">
+      <c r="Q60" s="7">
         <f t="shared" si="15"/>
         <v>0.2484571429</v>
       </c>
-      <c r="R60" s="9">
+      <c r="R60" s="7">
         <f t="shared" si="15"/>
         <v>0.11035</v>
       </c>
-      <c r="S60" s="7" t="str">
+      <c r="S60" s="7">
+        <f t="shared" si="15"/>
+        <v>0.07567142857</v>
+      </c>
+      <c r="T60" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T60" s="7" t="str">
+      <c r="U60" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U60" s="7" t="str">
+      <c r="V60" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V60" s="7" t="str">
+      <c r="W60" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W60" s="7" t="str">
+      <c r="X60" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X60" s="7" t="str">
+      <c r="Y60" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y60" s="7" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z60" s="7" t="str">
+      <c r="Z60" s="3" t="str">
         <f>average(R60:Y60)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="70">
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1">
       <c r="B70" s="1"/>
-      <c r="S70" s="9"/>
-    </row>
-    <row r="71">
+      <c r="S70" s="7"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
       <c r="B71" s="1"/>
-      <c r="S71" s="9"/>
-    </row>
-    <row r="72">
+      <c r="S71" s="7"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="1"/>
-      <c r="S72" s="9"/>
-    </row>
-    <row r="73">
+      <c r="S72" s="7"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
       <c r="B73" s="1"/>
-      <c r="S73" s="9"/>
-    </row>
-    <row r="74">
+      <c r="S73" s="7"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
       <c r="B74" s="1"/>
-      <c r="S74" s="9"/>
-    </row>
-    <row r="75">
+      <c r="S74" s="7"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="1"/>
-      <c r="S75" s="9"/>
-    </row>
-    <row r="76">
-      <c r="S76" s="9"/>
-    </row>
-    <row r="100">
+      <c r="S75" s="7"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="S76" s="7"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C100" s="9" t="str">
+      <c r="C100" s="7" t="str">
         <f t="shared" ref="C100:R100" si="16">average(C70:C75)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D100" s="9" t="str">
+      <c r="D100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E100" s="9" t="str">
+      <c r="E100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F100" s="9" t="str">
+      <c r="F100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G100" s="9" t="str">
+      <c r="G100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H100" s="9" t="str">
+      <c r="H100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I100" s="9" t="str">
+      <c r="I100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J100" s="9" t="str">
+      <c r="J100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K100" s="9" t="str">
+      <c r="K100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L100" s="9" t="str">
+      <c r="L100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M100" s="9" t="str">
+      <c r="M100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N100" s="9" t="str">
+      <c r="N100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O100" s="9" t="str">
+      <c r="O100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P100" s="9" t="str">
+      <c r="P100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q100" s="9" t="str">
+      <c r="Q100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R100" s="9" t="str">
+      <c r="R100" s="7" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -659,24 +659,24 @@
       <c r="L5" s="7">
         <v>0.3333</v>
       </c>
-      <c r="M5" s="7"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="7">
         <v>0.1818</v>
       </c>
-      <c r="O5" s="7">
-        <v>0.1538</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0.3333</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0.38</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0.1</v>
+      <c r="O5" s="8">
+        <v>0.2308</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0.3529</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0.4167</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0.1923</v>
       </c>
       <c r="S5" s="8">
-        <v>0.0</v>
+        <v>0.292</v>
       </c>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
@@ -686,7 +686,7 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="7">
         <f t="shared" si="2"/>
-        <v>0.1914833333</v>
+        <v>0.27775</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1"/>
@@ -981,8 +981,8 @@
       <c r="K12" s="7">
         <v>0.2973</v>
       </c>
-      <c r="L12" s="7">
-        <v>0.3182</v>
+      <c r="L12" s="8">
+        <v>0.2727</v>
       </c>
       <c r="M12" s="7">
         <v>0.6429</v>
@@ -993,14 +993,14 @@
       <c r="O12" s="7">
         <v>0.2759</v>
       </c>
-      <c r="P12" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0.2373</v>
-      </c>
-      <c r="R12" s="7">
-        <v>0.0244</v>
+      <c r="P12" s="8">
+        <v>0.3429</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0.3276</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0.0513</v>
       </c>
       <c r="S12" s="8">
         <v>0.0714</v>
@@ -1011,7 +1011,7 @@
       <c r="Y12" s="7"/>
       <c r="Z12" s="7">
         <f>average(R12:Y12)</f>
-        <v>0.0479</v>
+        <v>0.06135</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -1307,28 +1307,26 @@
       <c r="N19" s="7">
         <v>0.2308</v>
       </c>
-      <c r="O19" s="7">
-        <v>0.129</v>
-      </c>
-      <c r="P19" s="7">
-        <v>0.3469</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R19" s="7"/>
-      <c r="S19" s="8">
-        <v>0.0</v>
-      </c>
+      <c r="O19" s="8">
+        <v>0.1613</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0.3673</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0.22</v>
+      </c>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="7">
+      <c r="Z19" s="3" t="str">
         <f>average(R19:Y19)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -1634,13 +1632,13 @@
       <c r="O26" s="7">
         <v>0.2308</v>
       </c>
-      <c r="P26" s="7">
-        <v>0.3636</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>0.2414</v>
-      </c>
-      <c r="R26" s="7"/>
+      <c r="P26" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>0.2759</v>
+      </c>
+      <c r="R26" s="8"/>
       <c r="S26" s="8">
         <v>0.125</v>
       </c>
@@ -1954,16 +1952,18 @@
       <c r="N33" s="7">
         <v>0.1429</v>
       </c>
-      <c r="O33" s="7">
-        <v>0.2963</v>
-      </c>
-      <c r="P33" s="7">
-        <v>0.2909</v>
+      <c r="O33" s="8">
+        <v>0.3333</v>
+      </c>
+      <c r="P33" s="8">
+        <v>0.3333</v>
       </c>
       <c r="Q33" s="7">
         <v>0.303</v>
       </c>
-      <c r="R33" s="7"/>
+      <c r="R33" s="8">
+        <v>0.0606</v>
+      </c>
       <c r="S33" s="8">
         <v>0.3333</v>
       </c>
@@ -1975,7 +1975,7 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7">
         <f>average(R33:Y33)</f>
-        <v>0.3333</v>
+        <v>0.19695</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -2139,18 +2139,16 @@
       <c r="O40" s="7">
         <v>0.1429</v>
       </c>
-      <c r="P40" s="7">
-        <v>0.3404</v>
-      </c>
-      <c r="Q40" s="7">
-        <v>0.1957</v>
-      </c>
-      <c r="R40" s="7">
-        <v>0.1111</v>
-      </c>
-      <c r="S40" s="8">
-        <v>0.0</v>
-      </c>
+      <c r="P40" s="8">
+        <v>0.3696</v>
+      </c>
+      <c r="Q40" s="8">
+        <v>0.2222</v>
+      </c>
+      <c r="R40" s="8">
+        <v>0.1724</v>
+      </c>
+      <c r="S40" s="8"/>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
       <c r="V40" s="7"/>
@@ -2159,7 +2157,7 @@
       <c r="Y40" s="7"/>
       <c r="Z40" s="7">
         <f>average(R40:Y40)</f>
-        <v>0.05555</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -2319,19 +2317,19 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7">
-        <v>0.3333</v>
-      </c>
-      <c r="Q47" s="7">
-        <v>0.1818</v>
-      </c>
-      <c r="R47" s="7">
-        <v>0.2059</v>
-      </c>
-      <c r="S47" s="8">
+      <c r="O47" s="8">
         <v>0.0</v>
       </c>
+      <c r="P47" s="8">
+        <v>0.3778</v>
+      </c>
+      <c r="Q47" s="8">
+        <v>0.2273</v>
+      </c>
+      <c r="R47" s="8">
+        <v>0.2857</v>
+      </c>
+      <c r="S47" s="8"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
@@ -2340,7 +2338,7 @@
       <c r="Y47" s="7"/>
       <c r="Z47" s="7">
         <f>average(R47:Y47)</f>
-        <v>0.10295</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
@@ -2564,10 +2562,14 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
+      <c r="O54" s="8">
+        <v>0.6667</v>
+      </c>
+      <c r="P54" s="8">
+        <v>0.3913</v>
+      </c>
       <c r="Q54" s="7"/>
-      <c r="R54" s="7"/>
+      <c r="R54" s="8"/>
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
       <c r="U54" s="7"/>
@@ -3123,7 +3125,7 @@
       </c>
       <c r="L60" s="7">
         <f t="shared" si="15"/>
-        <v>0.36604</v>
+        <v>0.35694</v>
       </c>
       <c r="M60" s="7">
         <f t="shared" si="15"/>
@@ -3135,23 +3137,23 @@
       </c>
       <c r="O60" s="7">
         <f t="shared" si="15"/>
-        <v>0.2047833333</v>
+        <v>0.2552125</v>
       </c>
       <c r="P60" s="7">
         <f t="shared" si="15"/>
-        <v>0.3297714286</v>
+        <v>0.3668875</v>
       </c>
       <c r="Q60" s="7">
         <f t="shared" si="15"/>
-        <v>0.2484571429</v>
+        <v>0.2846714286</v>
       </c>
       <c r="R60" s="7">
         <f t="shared" si="15"/>
-        <v>0.11035</v>
+        <v>0.15246</v>
       </c>
       <c r="S60" s="7">
         <f t="shared" si="15"/>
-        <v>0.07567142857</v>
+        <v>0.205425</v>
       </c>
       <c r="T60" s="3" t="str">
         <f t="shared" si="15"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -675,9 +675,7 @@
       <c r="R5" s="8">
         <v>0.1923</v>
       </c>
-      <c r="S5" s="8">
-        <v>0.292</v>
-      </c>
+      <c r="S5" s="8"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -686,7 +684,7 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="7">
         <f t="shared" si="2"/>
-        <v>0.27775</v>
+        <v>0.2749</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1"/>
@@ -3153,7 +3151,7 @@
       </c>
       <c r="S60" s="7">
         <f t="shared" si="15"/>
-        <v>0.205425</v>
+        <v>0.1765666667</v>
       </c>
       <c r="T60" s="3" t="str">
         <f t="shared" si="15"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -11,12 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="16">
   <si>
     <t>Jamie Jenkins</t>
-  </si>
-  <si>
-    <t>November 205</t>
   </si>
   <si>
     <t>YTD</t>
@@ -31,10 +28,13 @@
     <t>Average Contract</t>
   </si>
   <si>
-    <t>Closing Rate</t>
+    <t>Rolling 90-Day Closing Rate</t>
   </si>
   <si>
     <t>John Fincher</t>
+  </si>
+  <si>
+    <t>November 205</t>
   </si>
   <si>
     <t>Andrew Painter</t>
@@ -70,7 +70,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -85,6 +85,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -125,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -133,6 +138,9 @@
       <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
@@ -141,18 +149,21 @@
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -410,8 +421,8 @@
       <c r="K1" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>1</v>
+      <c r="L1" s="3">
+        <v>45962.0</v>
       </c>
       <c r="M1" s="2">
         <v>45992.0</v>
@@ -452,246 +463,248 @@
       <c r="Y1" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>33624.74</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>49353.38</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <v>150019.57</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <v>35596.98</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
         <v>121861.65</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>217702.66</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="5">
         <v>80860.65</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="5">
         <v>56753.76</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>97057.61</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="5">
         <v>117013.22</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="5">
         <v>39130.08</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="5">
         <v>24475.43</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="5">
         <v>50427.08</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="5">
         <v>215081.52</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="5">
         <v>378650.28</v>
       </c>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="Z2" s="5">
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="Z2" s="6">
         <f t="shared" ref="Z2:Z3" si="1">sum(N2:Y2)</f>
         <v>644158.88</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7">
         <v>2.0</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="7">
         <v>2.0</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="7">
         <v>5.0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>2.0</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="7">
         <v>9.0</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="7">
         <v>12.0</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="7">
         <v>5.0</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="7">
         <v>4.0</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="7">
         <v>5.0</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="7">
         <v>7.0</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="7">
         <v>7.0</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="7">
         <v>3.0</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="7">
         <v>7.0</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="7">
         <v>13.0</v>
       </c>
-      <c r="R3" s="6">
+      <c r="R3" s="7">
         <v>24.0</v>
       </c>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="Z3" s="3">
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="Z3" s="4">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5">
         <v>16812.37</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>24676.69</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>30003.91</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>17798.49</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>13540.18</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>18141.89</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>16172.13</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>14188.44</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>19411.52</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="5">
         <v>16716.17</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="5">
         <v>5590.01</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="5">
         <v>8158.48</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="5">
         <v>7203.87</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="5">
         <v>16544.73</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4" s="5">
         <v>15777.09</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4" s="6">
         <f t="shared" ref="Z4:Z5" si="2">average(N4:Y4)</f>
         <v>13175.23</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="7">
+      <c r="A5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.5714</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.4167</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.3182</v>
+      </c>
+      <c r="E5" s="9">
         <v>0.3333</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.3571</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.3333</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0.52</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0.3333</v>
-      </c>
-      <c r="H5" s="7">
-        <v>0.1111</v>
-      </c>
-      <c r="I5" s="7">
-        <v>0.28</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0.2353</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0.24</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0.3333</v>
-      </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="7">
-        <v>0.1818</v>
-      </c>
-      <c r="O5" s="8">
+      <c r="F5" s="9">
+        <v>0.3429</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.4348</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0.4468</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0.3462</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0.2456</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0.2203</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0.2537</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0.2593</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0.2368</v>
+      </c>
+      <c r="O5" s="9">
         <v>0.2308</v>
       </c>
-      <c r="P5" s="8">
-        <v>0.3529</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0.4167</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0.1923</v>
-      </c>
-      <c r="S5" s="8"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7">
+      <c r="P5" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0.3393</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0.3426</v>
+      </c>
+      <c r="S5" s="9"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10">
         <f t="shared" si="2"/>
-        <v>0.2749</v>
+        <v>0.2699</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1"/>
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
         <v>45658.0</v>
@@ -723,8 +736,8 @@
       <c r="K8" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>1</v>
+      <c r="L8" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="M8" s="2">
         <v>45992.0</v>
@@ -765,272 +778,268 @@
       <c r="Y8" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z8" s="3" t="s">
+      <c r="Z8" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>26439.71</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>51542.87</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>75885.54</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>103291.98</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <v>153828.56</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <v>142652.92</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="5">
         <v>63419.5</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>131500.17</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="5">
         <v>131200.28</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="5">
         <v>28825.49</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="5">
         <v>10448.87</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="5">
         <v>90672.39</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="5">
         <v>34294.16</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="5">
         <v>65730.26</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="5">
         <v>349069.93</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9" s="5">
         <v>118400.53</v>
       </c>
-      <c r="S9" s="4"/>
-      <c r="W9" s="9"/>
-      <c r="Z9" s="5">
+      <c r="S9" s="5"/>
+      <c r="W9" s="11"/>
+      <c r="Z9" s="6">
         <f t="shared" ref="Z9:Z10" si="3">sum(N9:Y9)</f>
         <v>658167.27</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="6">
+      <c r="A10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7">
         <v>2.0</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>5.0</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>10.0</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>11.0</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <v>20.0</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <v>8.0</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <v>8.0</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="7">
         <v>8.0</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="7">
         <v>15.0</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="7">
         <v>9.0</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="7">
         <v>3.0</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="7">
         <v>6.0</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="7">
         <v>11.0</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="7">
         <v>10.0</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="7">
         <v>30.0</v>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="7">
         <v>9.0</v>
       </c>
-      <c r="S10" s="6"/>
-      <c r="W10" s="9"/>
-      <c r="Z10" s="3">
+      <c r="S10" s="7"/>
+      <c r="W10" s="11"/>
+      <c r="Z10" s="4">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="A11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5">
         <v>13219.86</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>10308.57</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>7588.55</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>9390.18</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>7691.43</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <v>17831.62</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="5">
         <v>7927.44</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>16437.52</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="5">
         <v>8746.69</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="5">
         <v>3202.83</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M11" s="5">
         <v>3482.96</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="5">
         <v>15112.07</v>
       </c>
-      <c r="O11" s="4">
+      <c r="O11" s="5">
         <v>3117.65</v>
       </c>
-      <c r="P11" s="4">
+      <c r="P11" s="5">
         <v>6573.03</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="Q11" s="5">
         <v>11635.66</v>
       </c>
-      <c r="R11" s="4">
+      <c r="R11" s="5">
         <v>13155.61</v>
       </c>
-      <c r="W11" s="9"/>
-      <c r="Z11" s="5">
+      <c r="W11" s="11"/>
+      <c r="Z11" s="6">
         <f>average(N11:Y11)</f>
         <v>9918.804</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.2381</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.4231</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0.4333</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0.4231</v>
-      </c>
-      <c r="H12" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="I12" s="7">
-        <v>0.2632</v>
-      </c>
-      <c r="J12" s="7">
-        <v>0.4211</v>
-      </c>
-      <c r="K12" s="7">
-        <v>0.2973</v>
-      </c>
-      <c r="L12" s="8">
-        <v>0.2727</v>
-      </c>
-      <c r="M12" s="7">
-        <v>0.6429</v>
-      </c>
-      <c r="N12" s="7">
-        <v>0.5385</v>
-      </c>
-      <c r="O12" s="7">
-        <v>0.2759</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0.3429</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0.3276</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0.0513</v>
-      </c>
-      <c r="S12" s="8">
-        <v>0.0714</v>
-      </c>
-      <c r="T12" s="10"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7">
+      <c r="A12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9">
+        <v>0.5161</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0.3333</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.34</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0.3521</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0.4125</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0.4321</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0.369</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0.3194</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0.2969</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0.32</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0.3205</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0.3571</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0.449</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0.4182</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0.3269</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0.2711</v>
+      </c>
+      <c r="S12" s="9"/>
+      <c r="T12" s="12"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10">
         <f>average(R12:Y12)</f>
-        <v>0.06135</v>
+        <v>0.2711</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="S13" s="7"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
@@ -1066,8 +1075,8 @@
       <c r="K15" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>1</v>
+      <c r="L15" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="M15" s="2">
         <v>45992.0</v>
@@ -1108,223 +1117,225 @@
       <c r="Y15" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z15" s="3" t="s">
+      <c r="Z15" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>31222.74</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>1972.5</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>165667.1</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <v>200911.27</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>46590.51</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="5">
         <v>13253.11</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="5">
         <v>182255.48</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="5">
         <v>128036.34</v>
       </c>
-      <c r="M16" s="4">
+      <c r="M16" s="5">
         <v>64847.69</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N16" s="5">
         <v>65950.63</v>
       </c>
-      <c r="O16" s="4">
+      <c r="O16" s="5">
         <v>14994.71</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P16" s="5">
         <v>76787.72</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="Q16" s="5">
         <v>262251.4</v>
       </c>
-      <c r="R16" s="4">
+      <c r="R16" s="5">
         <v>147003.47</v>
       </c>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="Z16" s="5">
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="Z16" s="6">
         <f t="shared" ref="Z16:Z17" si="4">sum(N16:Y16)</f>
         <v>566987.93</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="A17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7">
         <v>1.0</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <v>1.0</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="7">
         <v>7.0</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="7">
         <v>5.0</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="7">
         <v>8.0</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="7">
         <v>6.0</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="7">
         <v>16.0</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="7">
         <v>8.0</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="7">
         <v>4.0</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="7">
         <v>4.0</v>
       </c>
-      <c r="O17" s="6">
+      <c r="O17" s="7">
         <v>1.0</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="7">
         <v>7.0</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q17" s="7">
         <v>22.0</v>
       </c>
-      <c r="R17" s="6">
+      <c r="R17" s="7">
         <v>7.0</v>
       </c>
-      <c r="S17" s="6"/>
-      <c r="Z17" s="3">
+      <c r="S17" s="7"/>
+      <c r="Z17" s="4">
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="A18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="5">
         <v>31222.74</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <v>1972.5</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <v>23666.73</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="5">
         <v>40182.25</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="5">
         <v>5823.81</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="5">
         <v>2208.85</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="5">
         <v>11390.97</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18" s="5">
         <v>16004.54</v>
       </c>
-      <c r="M18" s="4">
+      <c r="M18" s="5">
         <v>16211.92</v>
       </c>
-      <c r="N18" s="4">
+      <c r="N18" s="5">
         <v>16487.66</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O18" s="5">
         <v>14994.71</v>
       </c>
-      <c r="P18" s="4">
+      <c r="P18" s="5">
         <v>10969.67</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="Q18" s="5">
         <v>11920.52</v>
       </c>
-      <c r="R18" s="4">
+      <c r="R18" s="5">
         <v>21000.5</v>
       </c>
-      <c r="Z18" s="5">
+      <c r="Z18" s="6">
         <f>average(N18:Y18)</f>
         <v>15074.612</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7">
-        <v>0.6667</v>
-      </c>
-      <c r="F19" s="7">
-        <v>0.4286</v>
-      </c>
-      <c r="G19" s="7">
-        <v>0.4286</v>
-      </c>
-      <c r="H19" s="7">
+      <c r="A19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="9">
         <v>0.5</v>
       </c>
-      <c r="I19" s="7">
-        <v>0.5333</v>
-      </c>
-      <c r="J19" s="7">
-        <v>0.381</v>
-      </c>
-      <c r="K19" s="7">
-        <v>0.2963</v>
-      </c>
-      <c r="L19" s="7">
-        <v>0.3571</v>
-      </c>
-      <c r="M19" s="7">
-        <v>0.33</v>
-      </c>
-      <c r="N19" s="7">
-        <v>0.2308</v>
-      </c>
-      <c r="O19" s="8">
-        <v>0.1613</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0.3673</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0.22</v>
-      </c>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="3" t="str">
+      <c r="F19" s="9">
+        <v>0.5625</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0.5714</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0.4815</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0.4634</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0.4898</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0.463</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0.377</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0.3387</v>
+      </c>
+      <c r="N19" s="9">
+        <v>0.3265</v>
+      </c>
+      <c r="O19" s="9">
+        <v>0.3056</v>
+      </c>
+      <c r="P19" s="9">
+        <v>0.2075</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>0.2615</v>
+      </c>
+      <c r="R19" s="9">
+        <v>0.232</v>
+      </c>
+      <c r="S19" s="9"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10">
         <f>average(R19:Y19)</f>
-        <v>#DIV/0!</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -1363,8 +1374,8 @@
       <c r="K22" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>1</v>
+      <c r="L22" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="M22" s="2">
         <v>45992.0</v>
@@ -1405,250 +1416,250 @@
       <c r="Y22" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z22" s="3" t="s">
+      <c r="Z22" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>18650.58</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>30930.58</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>10220.61</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="5">
         <v>40940.34</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="5">
         <v>31725.85</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="5">
         <v>59653.44</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="5">
         <v>52341.19</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="5">
         <v>43968.35</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="5">
         <v>55035.51</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="5">
         <v>30872.18</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M23" s="5">
         <v>5421.62</v>
       </c>
-      <c r="N23" s="4">
+      <c r="N23" s="5">
         <v>9080.08</v>
       </c>
-      <c r="O23" s="4">
+      <c r="O23" s="5">
         <v>5713.65</v>
       </c>
-      <c r="P23" s="4">
+      <c r="P23" s="5">
         <v>55012.85</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="Q23" s="5">
         <v>13845.3</v>
       </c>
-      <c r="R23" s="4">
+      <c r="R23" s="5">
         <v>88880.21</v>
       </c>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="Z23" s="5">
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="Z23" s="6">
         <f t="shared" ref="Z23:Z24" si="5">sum(N23:Y23)</f>
         <v>172532.09</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="6">
+      <c r="A24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="7">
         <v>1.0</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="7">
         <v>5.0</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="7">
         <v>2.0</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="7">
         <v>3.0</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="7">
         <v>13.0</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="7">
         <v>13.0</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="7">
         <v>10.0</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="7">
         <v>13.0</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="7">
         <v>16.0</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="7">
         <v>6.0</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="7">
         <v>2.0</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24" s="7">
         <v>7.0</v>
       </c>
-      <c r="O24" s="6">
+      <c r="O24" s="7">
         <v>2.0</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="7">
         <v>14.0</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="Q24" s="7">
         <v>12.0</v>
       </c>
-      <c r="R24" s="6">
+      <c r="R24" s="7">
         <v>10.0</v>
       </c>
-      <c r="S24" s="6"/>
-      <c r="W24" s="9"/>
-      <c r="Z24" s="3">
+      <c r="S24" s="7"/>
+      <c r="W24" s="11"/>
+      <c r="Z24" s="4">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="4">
+      <c r="A25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="5">
         <v>18650.58</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <v>6186.12</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <v>5110.3</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="5">
         <v>13646.78</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="5">
         <v>2440.45</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="5">
         <v>4588.73</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="5">
         <v>5234.12</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J25" s="5">
         <v>3382.18</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25" s="5">
         <v>3439.72</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="5">
         <v>5145.36</v>
       </c>
-      <c r="M25" s="4">
+      <c r="M25" s="5">
         <v>2710.81</v>
       </c>
-      <c r="N25" s="4">
+      <c r="N25" s="5">
         <v>1297.15</v>
       </c>
-      <c r="O25" s="4">
+      <c r="O25" s="5">
         <v>2856.82</v>
       </c>
-      <c r="P25" s="4">
+      <c r="P25" s="5">
         <v>3929.49</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="Q25" s="5">
         <v>1153.77</v>
       </c>
-      <c r="R25" s="4">
+      <c r="R25" s="5">
         <v>8888.02</v>
       </c>
-      <c r="T25" s="10"/>
-      <c r="W25" s="9"/>
-      <c r="Z25" s="5">
+      <c r="T25" s="12"/>
+      <c r="W25" s="11"/>
+      <c r="Z25" s="6">
         <f>average(N25:Y25)</f>
         <v>3625.05</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7">
-        <v>0.2143</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0.5556</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="F26" s="7">
-        <v>0.2632</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0.3714</v>
-      </c>
-      <c r="H26" s="7">
-        <v>0.6667</v>
-      </c>
-      <c r="I26" s="7">
-        <v>0.2222</v>
-      </c>
-      <c r="J26" s="7">
-        <v>0.4</v>
-      </c>
-      <c r="K26" s="7">
-        <v>0.3636</v>
-      </c>
-      <c r="L26" s="7">
-        <v>0.1852</v>
-      </c>
-      <c r="M26" s="7">
+      <c r="A26" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="9">
         <v>0.1333</v>
       </c>
-      <c r="N26" s="7">
-        <v>0.2381</v>
-      </c>
-      <c r="O26" s="7">
-        <v>0.2308</v>
-      </c>
-      <c r="P26" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="Q26" s="8">
-        <v>0.2759</v>
-      </c>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="T26" s="12"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="7">
+      <c r="D26" s="9">
+        <v>0.1667</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.3514</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0.3778</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0.3226</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0.4359</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0.4286</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0.4366</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0.3457</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0.3222</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0.2568</v>
+      </c>
+      <c r="O26" s="9">
+        <v>0.1905</v>
+      </c>
+      <c r="P26" s="9">
+        <v>0.2281</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>0.3243</v>
+      </c>
+      <c r="R26" s="9">
+        <v>0.3297</v>
+      </c>
+      <c r="S26" s="9"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="10"/>
+      <c r="Z26" s="10">
         <f>average(R26:Y26)</f>
-        <v>0.125</v>
+        <v>0.3297</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -1687,8 +1698,8 @@
       <c r="K29" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>1</v>
+      <c r="L29" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="M29" s="2">
         <v>45992.0</v>
@@ -1729,251 +1740,251 @@
       <c r="Y29" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Z29" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>55872.76</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>2336.73</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="5">
         <v>33592.39</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="5">
         <v>21413.67</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="5">
         <v>186331.34</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="5">
         <v>163356.3</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="5">
         <v>93899.31</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="5">
         <v>95663.96</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="5">
         <v>52111.35</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K30" s="5">
         <v>205694.01</v>
       </c>
-      <c r="L30" s="4">
+      <c r="L30" s="5">
         <v>38500.4</v>
       </c>
-      <c r="M30" s="4">
+      <c r="M30" s="5">
         <v>14861.34</v>
       </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="4">
+      <c r="N30" s="11"/>
+      <c r="O30" s="5">
         <v>8067.86</v>
       </c>
-      <c r="P30" s="4">
+      <c r="P30" s="5">
         <v>108802.59</v>
       </c>
-      <c r="Q30" s="4">
+      <c r="Q30" s="5">
         <v>149911.53</v>
       </c>
-      <c r="R30" s="4">
+      <c r="R30" s="5">
         <v>158044.97</v>
       </c>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="Z30" s="5">
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="Z30" s="6">
         <f t="shared" ref="Z30:Z31" si="6">sum(N30:Y30)</f>
         <v>424826.95</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="6">
+      <c r="A31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="7">
         <v>2.0</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="7">
         <v>2.0</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="7">
         <v>1.0</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="7">
         <v>8.0</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="7">
         <v>13.0</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="7">
         <v>8.0</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="7">
         <v>10.0</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I31" s="7">
         <v>2.0</v>
       </c>
-      <c r="J31" s="6">
+      <c r="J31" s="7">
         <v>4.0</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="7">
         <v>17.0</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="7">
         <v>5.0</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="7">
         <v>8.0</v>
       </c>
-      <c r="O31" s="6">
+      <c r="O31" s="7">
         <v>1.0</v>
       </c>
-      <c r="P31" s="6">
+      <c r="P31" s="7">
         <v>9.0</v>
       </c>
-      <c r="Q31" s="6">
+      <c r="Q31" s="7">
         <v>16.0</v>
       </c>
-      <c r="R31" s="6">
+      <c r="R31" s="7">
         <v>9.0</v>
       </c>
-      <c r="S31" s="6"/>
-      <c r="T31" s="6"/>
-      <c r="Z31" s="3">
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="Z31" s="4">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="4">
+      <c r="A32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="5">
         <v>27936.38</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <v>1168.36</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="5">
         <v>33592.39</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="5">
         <v>2676.71</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="5">
         <v>14333.18</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="5">
         <v>20419.54</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="5">
         <v>9389.93</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="5">
         <v>47831.98</v>
       </c>
-      <c r="J32" s="4">
+      <c r="J32" s="5">
         <v>13027.84</v>
       </c>
-      <c r="K32" s="4">
+      <c r="K32" s="5">
         <v>12099.65</v>
       </c>
-      <c r="L32" s="4">
+      <c r="L32" s="5">
         <v>7700.08</v>
       </c>
-      <c r="M32" s="4">
+      <c r="M32" s="5">
         <v>1857.67</v>
       </c>
-      <c r="O32" s="4">
+      <c r="O32" s="5">
         <v>8067.86</v>
       </c>
-      <c r="P32" s="4">
+      <c r="P32" s="5">
         <v>12089.18</v>
       </c>
-      <c r="Q32" s="4">
+      <c r="Q32" s="5">
         <v>9369.47</v>
       </c>
-      <c r="R32" s="4">
+      <c r="R32" s="5">
         <v>17560.55</v>
       </c>
-      <c r="Z32" s="5">
+      <c r="Z32" s="6">
         <f>average(N32:Y32)</f>
         <v>11771.765</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="C33" s="7">
-        <v>0.4286</v>
-      </c>
-      <c r="D33" s="7">
+      <c r="A33" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0.4167</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H33" s="9">
         <v>0.4211</v>
       </c>
-      <c r="E33" s="7">
-        <v>0.4091</v>
-      </c>
-      <c r="F33" s="7">
-        <v>0.3793</v>
-      </c>
-      <c r="G33" s="7">
-        <v>0.7143</v>
-      </c>
-      <c r="H33" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="I33" s="7">
-        <v>0.2857</v>
-      </c>
-      <c r="J33" s="7">
-        <v>0.625</v>
-      </c>
-      <c r="K33" s="7">
-        <v>0.2609</v>
-      </c>
-      <c r="L33" s="7">
-        <v>0.6364</v>
-      </c>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7">
-        <v>0.1429</v>
-      </c>
-      <c r="O33" s="8">
+      <c r="I33" s="9">
+        <v>0.451</v>
+      </c>
+      <c r="J33" s="9">
+        <v>0.5161</v>
+      </c>
+      <c r="K33" s="9">
+        <v>0.5128</v>
+      </c>
+      <c r="L33" s="9">
+        <v>0.3913</v>
+      </c>
+      <c r="M33" s="9">
+        <v>0.46</v>
+      </c>
+      <c r="N33" s="9">
+        <v>0.325</v>
+      </c>
+      <c r="O33" s="9">
         <v>0.3333</v>
       </c>
-      <c r="P33" s="8">
-        <v>0.3333</v>
-      </c>
-      <c r="Q33" s="7">
-        <v>0.303</v>
-      </c>
-      <c r="R33" s="8">
-        <v>0.0606</v>
-      </c>
-      <c r="S33" s="8">
-        <v>0.3333</v>
-      </c>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
-      <c r="Y33" s="7"/>
-      <c r="Z33" s="7">
+      <c r="P33" s="9">
+        <v>0.2564</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>0.3238</v>
+      </c>
+      <c r="R33" s="9">
+        <v>0.2432</v>
+      </c>
+      <c r="S33" s="9"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10">
         <f>average(R33:Y33)</f>
-        <v>0.19695</v>
+        <v>0.2432</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -2012,8 +2023,8 @@
       <c r="K36" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>1</v>
+      <c r="L36" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="M36" s="2">
         <v>45992.0</v>
@@ -2054,111 +2065,112 @@
       <c r="Y36" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z36" s="3" t="s">
+      <c r="Z36" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P37" s="4">
+      <c r="P37" s="5">
         <v>9374.61</v>
       </c>
-      <c r="Q37" s="4">
+      <c r="Q37" s="5">
         <v>123258.92</v>
       </c>
-      <c r="R37" s="4">
+      <c r="R37" s="5">
         <v>152476.32</v>
       </c>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="Z37" s="5">
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="Z37" s="6">
         <f t="shared" ref="Z37:Z38" si="7">sum(N37:Y37)</f>
         <v>285109.85</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P38" s="6">
+      <c r="A38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="7">
         <v>5.0</v>
       </c>
-      <c r="Q38" s="6">
+      <c r="Q38" s="7">
         <v>12.0</v>
       </c>
-      <c r="R38" s="6">
+      <c r="R38" s="7">
         <v>12.0</v>
       </c>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="Z38" s="3">
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="Z38" s="4">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L39" s="9"/>
-      <c r="P39" s="4">
+      <c r="A39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L39" s="11"/>
+      <c r="P39" s="5">
         <v>1874.92</v>
       </c>
-      <c r="Q39" s="4">
+      <c r="Q39" s="5">
         <v>10271.58</v>
       </c>
-      <c r="R39" s="4">
+      <c r="R39" s="5">
         <v>12706.36</v>
       </c>
-      <c r="Z39" s="5">
+      <c r="Z39" s="6">
         <f>average(N39:Y39)</f>
         <v>8284.286667</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7">
-        <v>0.1429</v>
-      </c>
-      <c r="P40" s="8">
-        <v>0.3696</v>
-      </c>
-      <c r="Q40" s="8">
-        <v>0.2222</v>
-      </c>
-      <c r="R40" s="8">
-        <v>0.1724</v>
-      </c>
-      <c r="S40" s="8"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
-      <c r="X40" s="7"/>
-      <c r="Y40" s="7"/>
-      <c r="Z40" s="7">
+      <c r="A40" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9">
+        <v>0.1111</v>
+      </c>
+      <c r="Q40" s="9">
+        <v>0.2828</v>
+      </c>
+      <c r="R40" s="9">
+        <v>0.2667</v>
+      </c>
+      <c r="S40" s="9"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="10"/>
+      <c r="X40" s="10"/>
+      <c r="Y40" s="10"/>
+      <c r="Z40" s="10">
         <f>average(R40:Y40)</f>
-        <v>0.1724</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1"/>
+        <v>0.2667</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+    </row>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
@@ -2194,8 +2206,8 @@
       <c r="K43" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>1</v>
+      <c r="L43" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="M43" s="2">
         <v>45992.0</v>
@@ -2236,107 +2248,103 @@
       <c r="Y43" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z43" s="3" t="s">
+      <c r="Z43" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="4">
+      <c r="P44" s="5">
         <v>816.62</v>
       </c>
-      <c r="Q44" s="4">
+      <c r="Q44" s="5">
         <v>124770.34</v>
       </c>
-      <c r="R44" s="4">
+      <c r="R44" s="5">
         <v>78978.19</v>
       </c>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="Z44" s="5">
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="Z44" s="6">
         <f t="shared" ref="Z44:Z45" si="8">sum(N44:Y44)</f>
         <v>204565.15</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="6">
+      <c r="A45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="7">
         <v>2.0</v>
       </c>
-      <c r="Q45" s="6">
+      <c r="Q45" s="7">
         <v>13.0</v>
       </c>
-      <c r="R45" s="6">
+      <c r="R45" s="7">
         <v>15.0</v>
       </c>
-      <c r="S45" s="6"/>
-      <c r="T45" s="6"/>
-      <c r="Z45" s="3">
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="Z45" s="4">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P46" s="4">
+      <c r="A46" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="5">
         <v>408.31</v>
       </c>
-      <c r="Q46" s="4">
+      <c r="Q46" s="5">
         <v>9597.72</v>
       </c>
-      <c r="R46" s="4">
+      <c r="R46" s="5">
         <v>5265.21</v>
       </c>
-      <c r="Z46" s="5">
+      <c r="Z46" s="6">
         <f>average(N46:Y46)</f>
         <v>5090.413333</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="P47" s="8">
-        <v>0.3778</v>
-      </c>
-      <c r="Q47" s="8">
-        <v>0.2273</v>
-      </c>
-      <c r="R47" s="8">
-        <v>0.2857</v>
-      </c>
-      <c r="S47" s="8"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="7"/>
-      <c r="X47" s="7"/>
-      <c r="Y47" s="7"/>
-      <c r="Z47" s="7">
+      <c r="A47" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9">
+        <v>0.2727</v>
+      </c>
+      <c r="R47" s="9">
+        <v>0.296</v>
+      </c>
+      <c r="S47" s="9"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
+      <c r="V47" s="10"/>
+      <c r="W47" s="10"/>
+      <c r="X47" s="10"/>
+      <c r="Y47" s="10"/>
+      <c r="Z47" s="10">
         <f>average(R47:Y47)</f>
-        <v>0.2857</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
@@ -2375,8 +2383,8 @@
       <c r="K50" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L50" s="3" t="s">
-        <v>1</v>
+      <c r="L50" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="M50" s="2">
         <v>45992.0</v>
@@ -2417,772 +2425,806 @@
       <c r="Y50" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z50" s="3" t="s">
+      <c r="Z50" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="4">
+      <c r="D51" s="5">
         <v>100.0</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="5">
         <v>16769.23</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="5">
         <v>23954.74</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51" s="5">
         <v>106322.49</v>
       </c>
-      <c r="I51" s="4">
+      <c r="I51" s="5">
         <v>3769.0</v>
       </c>
-      <c r="L51" s="9"/>
-      <c r="M51" s="4">
+      <c r="L51" s="11"/>
+      <c r="M51" s="5">
         <v>2632.6</v>
       </c>
-      <c r="O51" s="4">
+      <c r="O51" s="5">
         <v>33846.16</v>
       </c>
-      <c r="P51" s="4">
+      <c r="P51" s="5">
         <v>1121.66</v>
       </c>
-      <c r="Q51" s="4">
+      <c r="Q51" s="5">
         <v>109114.01</v>
       </c>
-      <c r="R51" s="4">
+      <c r="R51" s="5">
         <v>52999.57</v>
       </c>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="Z51" s="5">
+      <c r="S51" s="5"/>
+      <c r="T51" s="5"/>
+      <c r="Z51" s="6">
         <f t="shared" ref="Z51:Z52" si="9">sum(N51:Y51)</f>
         <v>197081.4</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="6">
+      <c r="A52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="7">
         <v>1.0</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="7">
         <v>1.0</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="7">
         <v>2.0</v>
       </c>
-      <c r="H52" s="6">
+      <c r="H52" s="7">
         <v>3.0</v>
       </c>
-      <c r="I52" s="6">
+      <c r="I52" s="7">
         <v>1.0</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52" s="7">
         <v>1.0</v>
       </c>
-      <c r="O52" s="6">
+      <c r="O52" s="7">
         <v>2.0</v>
       </c>
-      <c r="P52" s="6">
+      <c r="P52" s="7">
         <v>3.0</v>
       </c>
-      <c r="Q52" s="6">
+      <c r="Q52" s="7">
         <v>9.0</v>
       </c>
-      <c r="R52" s="6">
+      <c r="R52" s="7">
         <v>3.0</v>
       </c>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="Z52" s="3">
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="Z52" s="4">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="4">
+      <c r="A53" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="5">
         <v>100.0</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="5">
         <v>16769.23</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="5">
         <v>11977.37</v>
       </c>
-      <c r="H53" s="4">
+      <c r="H53" s="5">
         <v>35440.83</v>
       </c>
-      <c r="I53" s="4">
+      <c r="I53" s="5">
         <v>3769.0</v>
       </c>
-      <c r="M53" s="4">
+      <c r="M53" s="5">
         <v>2632.6</v>
       </c>
-      <c r="O53" s="4">
+      <c r="O53" s="5">
         <v>16923.08</v>
       </c>
-      <c r="P53" s="4">
+      <c r="P53" s="5">
         <v>373.89</v>
       </c>
-      <c r="Q53" s="4">
+      <c r="Q53" s="5">
         <v>12123.78</v>
       </c>
-      <c r="R53" s="4">
+      <c r="R53" s="5">
         <v>17666.52</v>
       </c>
-      <c r="Z53" s="5">
+      <c r="Z53" s="6">
         <f>average(N53:Y53)</f>
         <v>11771.8175</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-      <c r="O54" s="8">
-        <v>0.6667</v>
-      </c>
-      <c r="P54" s="8">
-        <v>0.3913</v>
-      </c>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="8"/>
-      <c r="S54" s="7"/>
-      <c r="T54" s="7"/>
-      <c r="U54" s="7"/>
-      <c r="V54" s="7"/>
-      <c r="W54" s="7"/>
-      <c r="X54" s="7"/>
-      <c r="Y54" s="7"/>
-      <c r="Z54" s="3" t="str">
+      <c r="A54" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="N54" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="O54" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="P54" s="9">
+        <v>0.4286</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>0.4848</v>
+      </c>
+      <c r="R54" s="9">
+        <v>0.4118</v>
+      </c>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="10"/>
+      <c r="V54" s="10"/>
+      <c r="W54" s="10"/>
+      <c r="X54" s="10"/>
+      <c r="Y54" s="10"/>
+      <c r="Z54" s="10">
         <f>average(R54:Y54)</f>
-        <v>#DIV/0!</v>
+        <v>0.4118</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="B55" s="2">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+      <c r="T55" s="2"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="2"/>
+      <c r="X55" s="2"/>
+      <c r="Y55" s="2"/>
+      <c r="Z55" s="4"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="B56" s="2">
         <v>45658.0</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C56" s="2">
         <v>45689.0</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D56" s="2">
         <v>45717.0</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E56" s="2">
         <v>45748.0</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F56" s="2">
         <v>45778.0</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G56" s="2">
         <v>45809.0</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H56" s="2">
         <v>45839.0</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I56" s="2">
         <v>45870.0</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J56" s="2">
         <v>45901.0</v>
       </c>
-      <c r="K55" s="2">
+      <c r="K56" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L55" s="3" t="s">
+      <c r="L56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M56" s="2">
+        <v>45992.0</v>
+      </c>
+      <c r="N56" s="2">
+        <v>46023.0</v>
+      </c>
+      <c r="O56" s="2">
+        <v>46054.0</v>
+      </c>
+      <c r="P56" s="2">
+        <v>46082.0</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>46113.0</v>
+      </c>
+      <c r="R56" s="2">
+        <v>46143.0</v>
+      </c>
+      <c r="S56" s="2">
+        <v>46174.0</v>
+      </c>
+      <c r="T56" s="2">
+        <v>46204.0</v>
+      </c>
+      <c r="U56" s="2">
+        <v>46235.0</v>
+      </c>
+      <c r="V56" s="2">
+        <v>46266.0</v>
+      </c>
+      <c r="W56" s="2">
+        <v>46296.0</v>
+      </c>
+      <c r="X56" s="2">
+        <v>46327.0</v>
+      </c>
+      <c r="Y56" s="2">
+        <v>46357.0</v>
+      </c>
+      <c r="Z56" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="M55" s="2">
-        <v>45992.0</v>
-      </c>
-      <c r="N55" s="2">
-        <v>46023.0</v>
-      </c>
-      <c r="O55" s="2">
-        <v>46054.0</v>
-      </c>
-      <c r="P55" s="2">
-        <v>46082.0</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>46113.0</v>
-      </c>
-      <c r="R55" s="2">
-        <v>46143.0</v>
-      </c>
-      <c r="S55" s="2">
-        <v>46174.0</v>
-      </c>
-      <c r="T55" s="2">
-        <v>46204.0</v>
-      </c>
-      <c r="U55" s="2">
-        <v>46235.0</v>
-      </c>
-      <c r="V55" s="2">
-        <v>46266.0</v>
-      </c>
-      <c r="W55" s="2">
-        <v>46296.0</v>
-      </c>
-      <c r="X55" s="2">
-        <v>46327.0</v>
-      </c>
-      <c r="Y55" s="2">
-        <v>46357.0</v>
-      </c>
-      <c r="Z55" s="3" t="s">
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56" s="5">
-        <f t="shared" ref="B56:Y56" si="10">sum(B51,B44,B37,B30,B23,B16,B9,B2)</f>
+      <c r="B57" s="6">
+        <f t="shared" ref="B57:Y57" si="10">sum(B51,B44,B37,B30,B23,B16,B9,B2)</f>
         <v>89497.5</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C57" s="6">
         <f t="shared" si="10"/>
         <v>96780.4</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D57" s="6">
         <f t="shared" si="10"/>
         <v>266185.41</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E57" s="6">
         <f t="shared" si="10"/>
         <v>191108.77</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F57" s="6">
         <f t="shared" si="10"/>
         <v>478352.55</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G57" s="6">
         <f t="shared" si="10"/>
         <v>732280.47</v>
       </c>
-      <c r="H56" s="5">
+      <c r="H57" s="6">
         <f t="shared" si="10"/>
         <v>684300.08</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I57" s="6">
         <f t="shared" si="10"/>
         <v>318537.92</v>
       </c>
-      <c r="J56" s="5">
+      <c r="J57" s="6">
         <f t="shared" si="10"/>
         <v>337890.59</v>
       </c>
-      <c r="K56" s="5">
+      <c r="K57" s="6">
         <f t="shared" si="10"/>
         <v>691198.5</v>
       </c>
-      <c r="L56" s="5">
+      <c r="L57" s="6">
         <f t="shared" si="10"/>
         <v>265364.49</v>
       </c>
-      <c r="M56" s="5">
+      <c r="M57" s="6">
         <f t="shared" si="10"/>
         <v>122687.55</v>
       </c>
-      <c r="N56" s="5">
+      <c r="N57" s="6">
         <f t="shared" si="10"/>
         <v>165703.1</v>
       </c>
-      <c r="O56" s="5">
+      <c r="O57" s="6">
         <f t="shared" si="10"/>
         <v>96916.54</v>
       </c>
-      <c r="P56" s="5">
+      <c r="P57" s="6">
         <f t="shared" si="10"/>
         <v>368073.39</v>
       </c>
-      <c r="Q56" s="5">
+      <c r="Q57" s="6">
         <f t="shared" si="10"/>
         <v>1347302.95</v>
       </c>
-      <c r="R56" s="5">
+      <c r="R57" s="6">
         <f t="shared" si="10"/>
         <v>1175433.54</v>
       </c>
-      <c r="S56" s="13">
+      <c r="S57" s="15">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T56" s="13">
+      <c r="T57" s="15">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U56" s="3">
+      <c r="U57" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="V56" s="3">
+      <c r="V57" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="W56" s="3">
+      <c r="W57" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X56" s="3">
+      <c r="X57" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Y56" s="3">
+      <c r="Y57" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Z56" s="5">
-        <f>sum(N56:Y56)</f>
+      <c r="Z57" s="6">
+        <f>sum(N57:Y57)</f>
         <v>3153429.52</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3" t="s">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B57" s="5">
-        <f t="shared" ref="B57:Z57" si="11">average(B51,B44,B37,B30,B23,B16,B9,B2)</f>
+      <c r="B58" s="6">
+        <f t="shared" ref="B58:Z58" si="11">average(B51,B44,B37,B30,B23,B16,B9,B2)</f>
         <v>44748.75</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C58" s="6">
         <f t="shared" si="11"/>
         <v>24195.1</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D58" s="6">
         <f t="shared" si="11"/>
         <v>53237.082</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E58" s="6">
         <f t="shared" si="11"/>
         <v>31851.46167</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F58" s="6">
         <f t="shared" si="11"/>
         <v>79725.425</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G58" s="6">
         <f t="shared" si="11"/>
         <v>146456.094</v>
       </c>
-      <c r="H57" s="5">
+      <c r="H58" s="6">
         <f t="shared" si="11"/>
         <v>114050.0133</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I58" s="6">
         <f t="shared" si="11"/>
         <v>53089.65333</v>
       </c>
-      <c r="J57" s="5">
+      <c r="J58" s="6">
         <f t="shared" si="11"/>
         <v>67578.118</v>
       </c>
-      <c r="K57" s="5">
+      <c r="K58" s="6">
         <f t="shared" si="11"/>
         <v>138239.7</v>
       </c>
-      <c r="L57" s="5">
+      <c r="L58" s="6">
         <f t="shared" si="11"/>
         <v>53072.898</v>
       </c>
-      <c r="M57" s="5">
+      <c r="M58" s="6">
         <f t="shared" si="11"/>
         <v>20447.925</v>
       </c>
-      <c r="N57" s="5">
+      <c r="N58" s="6">
         <f t="shared" si="11"/>
         <v>55234.36667</v>
       </c>
-      <c r="O57" s="5">
+      <c r="O58" s="6">
         <f t="shared" si="11"/>
         <v>19383.308</v>
       </c>
-      <c r="P57" s="5">
+      <c r="P58" s="6">
         <f t="shared" si="11"/>
         <v>46009.17375</v>
       </c>
-      <c r="Q57" s="5">
+      <c r="Q58" s="6">
         <f t="shared" si="11"/>
         <v>168412.8688</v>
       </c>
-      <c r="R57" s="5">
+      <c r="R58" s="6">
         <f t="shared" si="11"/>
         <v>146929.1925</v>
       </c>
-      <c r="S57" s="3" t="str">
+      <c r="S58" s="4" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T57" s="3" t="str">
+      <c r="T58" s="4" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U57" s="3" t="str">
+      <c r="U58" s="4" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V57" s="3" t="str">
+      <c r="V58" s="4" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W57" s="3" t="str">
+      <c r="W58" s="4" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X57" s="3" t="str">
+      <c r="X58" s="4" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y57" s="3" t="str">
+      <c r="Y58" s="4" t="str">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z57" s="5">
+      <c r="Z58" s="6">
         <f t="shared" si="11"/>
         <v>394178.69</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="14">
-        <f t="shared" ref="B58:R58" si="12">AVERAGE(B52,B45,B38,B31,B24,B17,B10,B3)</f>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="16">
+        <f t="shared" ref="B59:R59" si="12">AVERAGE(B52,B45,B38,B31,B24,B17,B10,B3)</f>
         <v>2</v>
       </c>
-      <c r="C58" s="14">
+      <c r="C59" s="16">
         <f t="shared" si="12"/>
         <v>1.75</v>
       </c>
-      <c r="D58" s="14">
+      <c r="D59" s="16">
         <f t="shared" si="12"/>
         <v>3.4</v>
       </c>
-      <c r="E58" s="14">
+      <c r="E59" s="16">
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="F58" s="14">
+      <c r="F59" s="16">
         <f t="shared" si="12"/>
         <v>6.5</v>
       </c>
-      <c r="G58" s="14">
+      <c r="G59" s="16">
         <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="H58" s="14">
+      <c r="H59" s="16">
         <f t="shared" si="12"/>
         <v>7.333333333</v>
       </c>
-      <c r="I58" s="14">
+      <c r="I59" s="16">
         <f t="shared" si="12"/>
         <v>5.5</v>
       </c>
-      <c r="J58" s="14">
+      <c r="J59" s="16">
         <f t="shared" si="12"/>
         <v>7.2</v>
       </c>
-      <c r="K58" s="14">
+      <c r="K59" s="16">
         <f t="shared" si="12"/>
         <v>14.2</v>
       </c>
-      <c r="L58" s="14">
+      <c r="L59" s="16">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="M58" s="14">
+      <c r="M59" s="16">
         <f t="shared" si="12"/>
         <v>3.5</v>
       </c>
-      <c r="N58" s="14">
+      <c r="N59" s="16">
         <f t="shared" si="12"/>
         <v>5.666666667</v>
       </c>
-      <c r="O58" s="14">
+      <c r="O59" s="16">
         <f t="shared" si="12"/>
         <v>3.4</v>
       </c>
-      <c r="P58" s="14">
+      <c r="P59" s="16">
         <f t="shared" si="12"/>
         <v>7.125</v>
       </c>
-      <c r="Q58" s="14">
+      <c r="Q59" s="16">
         <f t="shared" si="12"/>
         <v>15.875</v>
       </c>
-      <c r="R58" s="14">
+      <c r="R59" s="16">
         <f t="shared" si="12"/>
         <v>11.125</v>
       </c>
-      <c r="S58" s="3">
-        <f t="shared" ref="S58:Y58" si="13">sum(S52,S45,S38,S31,S24,S17,S10,S3)</f>
+      <c r="S59" s="4">
+        <f t="shared" ref="S59:Y59" si="13">sum(S52,S45,S38,S31,S24,S17,S10,S3)</f>
         <v>0</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T59" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U59" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V59" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W59" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X58" s="3">
+      <c r="X59" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y59" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z58" s="14">
-        <f>sum(N58:Y58)</f>
+      <c r="Z59" s="16">
+        <f>sum(N59:Y59)</f>
         <v>43.19166667</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B59" s="5">
-        <f t="shared" ref="B59:Y59" si="14">AVERAGE(B53,B46,B39,B32,B25,B18,B11,B4)</f>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="6">
+        <f t="shared" ref="B60:Y60" si="14">AVERAGE(B53,B46,B39,B32,B25,B18,B11,B4)</f>
         <v>22374.375</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C60" s="6">
         <f t="shared" si="14"/>
         <v>14428.8725</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D60" s="6">
         <f t="shared" si="14"/>
         <v>16038.198</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E60" s="6">
         <f t="shared" si="14"/>
         <v>13527.67</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F60" s="6">
         <f t="shared" si="14"/>
         <v>10810.03167</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G60" s="6">
         <f t="shared" si="14"/>
         <v>14472.008</v>
       </c>
-      <c r="H59" s="5">
+      <c r="H60" s="6">
         <f t="shared" si="14"/>
         <v>20600.915</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I60" s="6">
         <f t="shared" si="14"/>
         <v>14129.13167</v>
       </c>
-      <c r="J59" s="5">
+      <c r="J60" s="6">
         <f t="shared" si="14"/>
         <v>10893.582</v>
       </c>
-      <c r="K59" s="5">
+      <c r="K60" s="6">
         <f t="shared" si="14"/>
         <v>10478.64</v>
       </c>
-      <c r="L59" s="5">
+      <c r="L60" s="6">
         <f t="shared" si="14"/>
         <v>7528.564</v>
       </c>
-      <c r="M59" s="5">
+      <c r="M60" s="6">
         <f t="shared" si="14"/>
         <v>5842.406667</v>
       </c>
-      <c r="N59" s="5">
+      <c r="N60" s="6">
         <f t="shared" si="14"/>
         <v>10965.62667</v>
       </c>
-      <c r="O59" s="5">
+      <c r="O60" s="6">
         <f t="shared" si="14"/>
         <v>9192.024</v>
       </c>
-      <c r="P59" s="5">
+      <c r="P60" s="6">
         <f t="shared" si="14"/>
         <v>5427.795</v>
       </c>
-      <c r="Q59" s="5">
+      <c r="Q60" s="6">
         <f t="shared" si="14"/>
         <v>10327.15375</v>
       </c>
-      <c r="R59" s="5">
+      <c r="R60" s="6">
         <f t="shared" si="14"/>
         <v>14002.4825</v>
       </c>
-      <c r="S59" s="3" t="str">
+      <c r="S60" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T59" s="3" t="str">
+      <c r="T60" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U59" s="3" t="str">
+      <c r="U60" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V59" s="3" t="str">
+      <c r="V60" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W59" s="3" t="str">
+      <c r="W60" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X59" s="3" t="str">
+      <c r="X60" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y59" s="3" t="str">
+      <c r="Y60" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z59" s="5" t="str">
-        <f>average(N59:Y59)</f>
+      <c r="Z60" s="6" t="str">
+        <f>average(N60:Y60)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="7">
-        <f t="shared" ref="B60:Y60" si="15">AVERAGE(B54,B47,B40,B33,B26,B19,B12,B5)</f>
-        <v>0.3444333333</v>
-      </c>
-      <c r="C60" s="7">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="10">
+        <f t="shared" ref="B61:Y61" si="15">AVERAGE(B54,B47,B40,B33,B26,B19,B12,B5)</f>
+        <v>0.50445</v>
+      </c>
+      <c r="C61" s="10">
         <f t="shared" si="15"/>
-        <v>0.309525</v>
-      </c>
-      <c r="D60" s="7">
+        <v>0.366525</v>
+      </c>
+      <c r="D61" s="10">
         <f t="shared" si="15"/>
-        <v>0.42125</v>
-      </c>
-      <c r="E60" s="7">
+        <v>0.30455</v>
+      </c>
+      <c r="E61" s="10">
         <f t="shared" si="15"/>
-        <v>0.42478</v>
-      </c>
-      <c r="F60" s="7">
+        <v>0.38494</v>
+      </c>
+      <c r="F61" s="10">
         <f t="shared" si="15"/>
-        <v>0.40488</v>
-      </c>
-      <c r="G60" s="7">
+        <v>0.40984</v>
+      </c>
+      <c r="G61" s="10">
         <f t="shared" si="15"/>
-        <v>0.45414</v>
-      </c>
-      <c r="H60" s="7">
+        <v>0.4393</v>
+      </c>
+      <c r="H61" s="10">
         <f t="shared" si="15"/>
-        <v>0.40556</v>
-      </c>
-      <c r="I60" s="7">
+        <v>0.42082</v>
+      </c>
+      <c r="I61" s="10">
         <f t="shared" si="15"/>
-        <v>0.31688</v>
-      </c>
-      <c r="J60" s="7">
+        <v>0.4131</v>
+      </c>
+      <c r="J61" s="10">
         <f t="shared" si="15"/>
-        <v>0.41248</v>
-      </c>
-      <c r="K60" s="7">
+        <v>0.3999</v>
+      </c>
+      <c r="K61" s="10">
         <f t="shared" si="15"/>
-        <v>0.29162</v>
-      </c>
-      <c r="L60" s="7">
+        <v>0.38592</v>
+      </c>
+      <c r="L61" s="10">
         <f t="shared" si="15"/>
-        <v>0.35694</v>
-      </c>
-      <c r="M60" s="7">
+        <v>0.33754</v>
+      </c>
+      <c r="M61" s="10">
         <f t="shared" si="15"/>
-        <v>0.3687333333</v>
-      </c>
-      <c r="N60" s="7">
+        <v>0.4501166667</v>
+      </c>
+      <c r="N61" s="10">
         <f t="shared" si="15"/>
-        <v>0.26642</v>
-      </c>
-      <c r="O60" s="7">
+        <v>0.4170333333</v>
+      </c>
+      <c r="O61" s="10">
         <f t="shared" si="15"/>
-        <v>0.2552125</v>
-      </c>
-      <c r="P60" s="7">
+        <v>0.3348666667</v>
+      </c>
+      <c r="P61" s="10">
         <f t="shared" si="15"/>
-        <v>0.3668875</v>
-      </c>
-      <c r="Q60" s="7">
+        <v>0.2642714286</v>
+      </c>
+      <c r="Q61" s="10">
         <f t="shared" si="15"/>
-        <v>0.2846714286</v>
-      </c>
-      <c r="R60" s="7">
+        <v>0.3270125</v>
+      </c>
+      <c r="R61" s="10">
         <f t="shared" si="15"/>
-        <v>0.15246</v>
-      </c>
-      <c r="S60" s="7">
-        <f t="shared" si="15"/>
-        <v>0.1765666667</v>
-      </c>
-      <c r="T60" s="3" t="str">
+        <v>0.2991375</v>
+      </c>
+      <c r="S61" s="4" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U60" s="3" t="str">
+      <c r="T61" s="4" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V60" s="3" t="str">
+      <c r="U61" s="4" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W60" s="3" t="str">
+      <c r="V61" s="4" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X60" s="3" t="str">
+      <c r="W61" s="4" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y60" s="3" t="str">
+      <c r="X61" s="4" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z60" s="3" t="str">
-        <f>average(R60:Y60)</f>
+      <c r="Y61" s="4" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1"/>
+      <c r="Z61" s="4" t="str">
+        <f>average(R61:Y61)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
     <row r="62" ht="15.75" customHeight="1"/>
     <row r="63" ht="15.75" customHeight="1"/>
     <row r="64" ht="15.75" customHeight="1"/>
@@ -3191,34 +3233,34 @@
     <row r="67" ht="15.75" customHeight="1"/>
     <row r="68" ht="15.75" customHeight="1"/>
     <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="B70" s="1"/>
-      <c r="S70" s="7"/>
-    </row>
+    <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1">
       <c r="B71" s="1"/>
-      <c r="S71" s="7"/>
+      <c r="S71" s="10"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="1"/>
-      <c r="S72" s="7"/>
+      <c r="S72" s="10"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="B73" s="1"/>
-      <c r="S73" s="7"/>
+      <c r="S73" s="10"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="B74" s="1"/>
-      <c r="S74" s="7"/>
+      <c r="S74" s="10"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="1"/>
-      <c r="S75" s="7"/>
+      <c r="S75" s="10"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="S76" s="7"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1"/>
+      <c r="B76" s="1"/>
+      <c r="S76" s="10"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="S77" s="10"/>
+    </row>
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1"/>
     <row r="80" ht="15.75" customHeight="1"/>
@@ -3241,76 +3283,76 @@
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="B100" s="3" t="s">
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="B101" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C100" s="7" t="str">
-        <f t="shared" ref="C100:R100" si="16">average(C70:C75)</f>
+      <c r="C101" s="10" t="str">
+        <f t="shared" ref="C101:R101" si="16">average(C71:C76)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D100" s="7" t="str">
+      <c r="D101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E100" s="7" t="str">
+      <c r="E101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F100" s="7" t="str">
+      <c r="F101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G100" s="7" t="str">
+      <c r="G101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H100" s="7" t="str">
+      <c r="H101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I100" s="7" t="str">
+      <c r="I101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J100" s="7" t="str">
+      <c r="J101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K100" s="7" t="str">
+      <c r="K101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L100" s="7" t="str">
+      <c r="L101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M100" s="7" t="str">
+      <c r="M101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N100" s="7" t="str">
+      <c r="N101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O100" s="7" t="str">
+      <c r="O101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P100" s="7" t="str">
+      <c r="P101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q100" s="7" t="str">
+      <c r="Q101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R100" s="7" t="str">
+      <c r="R101" s="10" t="str">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="101" ht="15.75" customHeight="1"/>
     <row r="102" ht="15.75" customHeight="1"/>
     <row r="103" ht="15.75" customHeight="1"/>
     <row r="104" ht="15.75" customHeight="1"/>
@@ -4210,6 +4252,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
   <si>
     <t>Jamie Jenkins</t>
   </si>
@@ -28,13 +28,13 @@
     <t>Average Contract</t>
   </si>
   <si>
+    <t>Monthly Closing Rate</t>
+  </si>
+  <si>
     <t>Rolling 90-Day Closing Rate</t>
   </si>
   <si>
     <t>John Fincher</t>
-  </si>
-  <si>
-    <t>November 205</t>
   </si>
   <si>
     <t>Andrew Painter</t>
@@ -49,10 +49,10 @@
     <t>Dani Cole</t>
   </si>
   <si>
-    <t>Megan Rice</t>
+    <t>November 205</t>
   </si>
   <si>
-    <t>Mike Harr</t>
+    <t>Megan Rice</t>
   </si>
   <si>
     <t>Contract Total Average</t>
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -149,6 +149,18 @@
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -164,6 +176,9 @@
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -629,7 +644,7 @@
         <v>15777.09</v>
       </c>
       <c r="Z4" s="6">
-        <f t="shared" ref="Z4:Z5" si="2">average(N4:Y4)</f>
+        <f t="shared" ref="Z4:Z6" si="2">average(N4:Y4)</f>
         <v>13175.23</v>
       </c>
     </row>
@@ -638,55 +653,53 @@
         <v>5</v>
       </c>
       <c r="B5" s="9">
-        <v>0.5714</v>
+        <v>0.3333</v>
       </c>
       <c r="C5" s="9">
+        <v>0.3571</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.3333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.52</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.3333</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0.1111</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0.28</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0.2353</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0.24</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0.3333</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="9">
+        <v>0.1818</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0.2308</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0.3529</v>
+      </c>
+      <c r="Q5" s="11">
         <v>0.4167</v>
       </c>
-      <c r="D5" s="9">
-        <v>0.3182</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.3333</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.3429</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0.4348</v>
-      </c>
-      <c r="H5" s="9">
-        <v>0.4468</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0.3462</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0.2456</v>
-      </c>
-      <c r="K5" s="9">
-        <v>0.2203</v>
-      </c>
-      <c r="L5" s="9">
-        <v>0.2537</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0.2593</v>
-      </c>
-      <c r="N5" s="9">
-        <v>0.2368</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0.2308</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0.3393</v>
-      </c>
-      <c r="R5" s="9">
-        <v>0.3426</v>
+      <c r="R5" s="11">
+        <v>0.1923</v>
       </c>
       <c r="S5" s="9"/>
       <c r="T5" s="10"/>
@@ -695,2580 +708,2836 @@
       <c r="W5" s="10"/>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
-      <c r="Z5" s="10">
+      <c r="Z5" s="9">
+        <f t="shared" si="2"/>
+        <v>0.2749</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0.5714</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0.4167</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0.3182</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0.3333</v>
+      </c>
+      <c r="F6" s="13">
+        <v>0.3429</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0.4348</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0.4468</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0.3462</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0.2456</v>
+      </c>
+      <c r="K6" s="13">
+        <v>0.2203</v>
+      </c>
+      <c r="L6" s="13">
+        <v>0.2537</v>
+      </c>
+      <c r="M6" s="13">
+        <v>0.2593</v>
+      </c>
+      <c r="N6" s="13">
+        <v>0.2368</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0.2308</v>
+      </c>
+      <c r="P6" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>0.3393</v>
+      </c>
+      <c r="R6" s="13">
+        <v>0.3426</v>
+      </c>
+      <c r="S6" s="13"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14">
         <f t="shared" si="2"/>
         <v>0.2699</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1"/>
     <row r="7" ht="15.75" customHeight="1"/>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2">
+    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
         <v>45658.0</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C9" s="2">
         <v>45689.0</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <v>45717.0</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E9" s="2">
         <v>45748.0</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F9" s="2">
         <v>45778.0</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G9" s="2">
         <v>45809.0</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H9" s="2">
         <v>45839.0</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I9" s="2">
         <v>45870.0</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J9" s="2">
         <v>45901.0</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K9" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M8" s="2">
+      <c r="L9" s="3">
+        <v>45962.0</v>
+      </c>
+      <c r="M9" s="2">
         <v>45992.0</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N9" s="2">
         <v>46023.0</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O9" s="2">
         <v>46054.0</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P9" s="2">
         <v>46082.0</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q9" s="2">
         <v>46113.0</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R9" s="2">
         <v>46143.0</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S9" s="2">
         <v>46174.0</v>
       </c>
-      <c r="T8" s="2">
+      <c r="T9" s="2">
         <v>46204.0</v>
       </c>
-      <c r="U8" s="2">
+      <c r="U9" s="2">
         <v>46235.0</v>
       </c>
-      <c r="V8" s="2">
+      <c r="V9" s="2">
         <v>46266.0</v>
       </c>
-      <c r="W8" s="2">
+      <c r="W9" s="2">
         <v>46296.0</v>
       </c>
-      <c r="X8" s="2">
+      <c r="X9" s="2">
         <v>46327.0</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y9" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z8" s="4" t="s">
+      <c r="Z9" s="4" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="5">
-        <v>26439.71</v>
-      </c>
-      <c r="D9" s="5">
-        <v>51542.87</v>
-      </c>
-      <c r="E9" s="5">
-        <v>75885.54</v>
-      </c>
-      <c r="F9" s="5">
-        <v>103291.98</v>
-      </c>
-      <c r="G9" s="5">
-        <v>153828.56</v>
-      </c>
-      <c r="H9" s="5">
-        <v>142652.92</v>
-      </c>
-      <c r="I9" s="5">
-        <v>63419.5</v>
-      </c>
-      <c r="J9" s="5">
-        <v>131500.17</v>
-      </c>
-      <c r="K9" s="5">
-        <v>131200.28</v>
-      </c>
-      <c r="L9" s="5">
-        <v>28825.49</v>
-      </c>
-      <c r="M9" s="5">
-        <v>10448.87</v>
-      </c>
-      <c r="N9" s="5">
-        <v>90672.39</v>
-      </c>
-      <c r="O9" s="5">
-        <v>34294.16</v>
-      </c>
-      <c r="P9" s="5">
-        <v>65730.26</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>349069.93</v>
-      </c>
-      <c r="R9" s="5">
-        <v>118400.53</v>
-      </c>
-      <c r="S9" s="5"/>
-      <c r="W9" s="11"/>
-      <c r="Z9" s="6">
-        <f t="shared" ref="Z9:Z10" si="3">sum(N9:Y9)</f>
-        <v>658167.27</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5">
+        <v>26439.71</v>
+      </c>
+      <c r="D10" s="5">
+        <v>51542.87</v>
+      </c>
+      <c r="E10" s="5">
+        <v>75885.54</v>
+      </c>
+      <c r="F10" s="5">
+        <v>103291.98</v>
+      </c>
+      <c r="G10" s="5">
+        <v>153828.56</v>
+      </c>
+      <c r="H10" s="5">
+        <v>142652.92</v>
+      </c>
+      <c r="I10" s="5">
+        <v>63419.5</v>
+      </c>
+      <c r="J10" s="5">
+        <v>131500.17</v>
+      </c>
+      <c r="K10" s="5">
+        <v>131200.28</v>
+      </c>
+      <c r="L10" s="5">
+        <v>28825.49</v>
+      </c>
+      <c r="M10" s="5">
+        <v>10448.87</v>
+      </c>
+      <c r="N10" s="5">
+        <v>90672.39</v>
+      </c>
+      <c r="O10" s="5">
+        <v>34294.16</v>
+      </c>
+      <c r="P10" s="5">
+        <v>65730.26</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>349069.93</v>
+      </c>
+      <c r="R10" s="5">
+        <v>118400.53</v>
+      </c>
+      <c r="S10" s="5"/>
+      <c r="W10" s="15"/>
+      <c r="Z10" s="6">
+        <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
+        <v>658167.27</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C11" s="7">
         <v>2.0</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D11" s="7">
         <v>5.0</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E11" s="7">
         <v>10.0</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F11" s="7">
         <v>11.0</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G11" s="7">
         <v>20.0</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H11" s="7">
         <v>8.0</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I11" s="7">
         <v>8.0</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J11" s="7">
         <v>8.0</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K11" s="7">
         <v>15.0</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L11" s="7">
         <v>9.0</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M11" s="7">
         <v>3.0</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N11" s="7">
         <v>6.0</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O11" s="7">
         <v>11.0</v>
       </c>
-      <c r="P10" s="7">
+      <c r="P11" s="7">
         <v>10.0</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q11" s="7">
         <v>30.0</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R11" s="7">
         <v>9.0</v>
       </c>
-      <c r="S10" s="7"/>
-      <c r="W10" s="11"/>
-      <c r="Z10" s="4">
+      <c r="S11" s="7"/>
+      <c r="W11" s="15"/>
+      <c r="Z11" s="4">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C12" s="5">
         <v>13219.86</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D12" s="5">
         <v>10308.57</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E12" s="5">
         <v>7588.55</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F12" s="5">
         <v>9390.18</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G12" s="5">
         <v>7691.43</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H12" s="5">
         <v>17831.62</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I12" s="5">
         <v>7927.44</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J12" s="5">
         <v>16437.52</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K12" s="5">
         <v>8746.69</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L12" s="5">
         <v>3202.83</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M12" s="5">
         <v>3482.96</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N12" s="5">
         <v>15112.07</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O12" s="5">
         <v>3117.65</v>
       </c>
-      <c r="P11" s="5">
+      <c r="P12" s="5">
         <v>6573.03</v>
       </c>
-      <c r="Q11" s="5">
+      <c r="Q12" s="5">
         <v>11635.66</v>
       </c>
-      <c r="R11" s="5">
+      <c r="R12" s="5">
         <v>13155.61</v>
       </c>
-      <c r="W11" s="11"/>
-      <c r="Z11" s="6">
-        <f>average(N11:Y11)</f>
+      <c r="W12" s="15"/>
+      <c r="Z12" s="6">
+        <f>average(N12:Y12)</f>
         <v>9918.804</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="8" t="s">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9">
+      <c r="B13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.2381</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.4231</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0.4333</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0.4231</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0.2632</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0.4211</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0.2973</v>
+      </c>
+      <c r="L13" s="11">
+        <v>0.2727</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0.6429</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0.5385</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.2759</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0.3429</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>0.3333</v>
+      </c>
+      <c r="R13" s="11">
+        <v>0.0513</v>
+      </c>
+      <c r="S13" s="13"/>
+      <c r="T13" s="16"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13">
         <v>0.5161</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D14" s="13">
         <v>0.3333</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E14" s="13">
         <v>0.34</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F14" s="13">
         <v>0.3521</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G14" s="13">
         <v>0.4125</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H14" s="13">
         <v>0.4321</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I14" s="13">
         <v>0.369</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J14" s="13">
         <v>0.3194</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K14" s="13">
         <v>0.2969</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L14" s="13">
         <v>0.32</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M14" s="13">
         <v>0.3205</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N14" s="13">
         <v>0.3571</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O14" s="13">
         <v>0.449</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P14" s="13">
         <v>0.4182</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q14" s="13">
         <v>0.3269</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R14" s="13">
         <v>0.2711</v>
       </c>
-      <c r="S12" s="9"/>
-      <c r="T12" s="12"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10">
-        <f>average(R12:Y12)</f>
+      <c r="S14" s="13"/>
+      <c r="T14" s="16"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14">
+        <f>average(R14:Y14)</f>
         <v>0.2711</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="S13" s="10"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-    </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
+      <c r="S15" s="14"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B17" s="2">
         <v>45658.0</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C17" s="2">
         <v>45689.0</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D17" s="2">
         <v>45717.0</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E17" s="2">
         <v>45748.0</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F17" s="2">
         <v>45778.0</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G17" s="2">
         <v>45809.0</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H17" s="2">
         <v>45839.0</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I17" s="2">
         <v>45870.0</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J17" s="2">
         <v>45901.0</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K17" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M15" s="2">
+      <c r="L17" s="3">
+        <v>45962.0</v>
+      </c>
+      <c r="M17" s="2">
         <v>45992.0</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N17" s="2">
         <v>46023.0</v>
       </c>
-      <c r="O15" s="2">
+      <c r="O17" s="2">
         <v>46054.0</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P17" s="2">
         <v>46082.0</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q17" s="2">
         <v>46113.0</v>
       </c>
-      <c r="R15" s="2">
+      <c r="R17" s="2">
         <v>46143.0</v>
       </c>
-      <c r="S15" s="2">
+      <c r="S17" s="2">
         <v>46174.0</v>
       </c>
-      <c r="T15" s="2">
+      <c r="T17" s="2">
         <v>46204.0</v>
       </c>
-      <c r="U15" s="2">
+      <c r="U17" s="2">
         <v>46235.0</v>
       </c>
-      <c r="V15" s="2">
+      <c r="V17" s="2">
         <v>46266.0</v>
       </c>
-      <c r="W15" s="2">
+      <c r="W17" s="2">
         <v>46296.0</v>
       </c>
-      <c r="X15" s="2">
+      <c r="X17" s="2">
         <v>46327.0</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y17" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z15" s="4" t="s">
+      <c r="Z17" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="4" t="s">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E18" s="5">
         <v>31222.74</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F18" s="5">
         <v>1972.5</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G18" s="5">
         <v>165667.1</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H18" s="5">
         <v>200911.27</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I18" s="5">
         <v>46590.51</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J18" s="5">
         <v>13253.11</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K18" s="5">
         <v>182255.48</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L18" s="5">
         <v>128036.34</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M18" s="5">
         <v>64847.69</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N18" s="5">
         <v>65950.63</v>
       </c>
-      <c r="O16" s="5">
+      <c r="O18" s="5">
         <v>14994.71</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P18" s="5">
         <v>76787.72</v>
       </c>
-      <c r="Q16" s="5">
+      <c r="Q18" s="5">
         <v>262251.4</v>
       </c>
-      <c r="R16" s="5">
+      <c r="R18" s="5">
         <v>147003.47</v>
       </c>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="Z16" s="6">
-        <f t="shared" ref="Z16:Z17" si="4">sum(N16:Y16)</f>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="Z18" s="6">
+        <f t="shared" ref="Z18:Z19" si="4">sum(N18:Y18)</f>
         <v>566987.93</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="4" t="s">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E19" s="7">
         <v>1.0</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F19" s="7">
         <v>1.0</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G19" s="7">
         <v>7.0</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H19" s="7">
         <v>5.0</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I19" s="7">
         <v>8.0</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J19" s="7">
         <v>6.0</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K19" s="7">
         <v>16.0</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L19" s="7">
         <v>8.0</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M19" s="7">
         <v>4.0</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N19" s="7">
         <v>4.0</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O19" s="7">
         <v>1.0</v>
       </c>
-      <c r="P17" s="7">
+      <c r="P19" s="7">
         <v>7.0</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="Q19" s="7">
         <v>22.0</v>
       </c>
-      <c r="R17" s="7">
+      <c r="R19" s="7">
         <v>7.0</v>
       </c>
-      <c r="S17" s="7"/>
-      <c r="Z17" s="4">
+      <c r="S19" s="7"/>
+      <c r="Z19" s="4">
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="4" t="s">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E20" s="5">
         <v>31222.74</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F20" s="5">
         <v>1972.5</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G20" s="5">
         <v>23666.73</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H20" s="5">
         <v>40182.25</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I20" s="5">
         <v>5823.81</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J20" s="5">
         <v>2208.85</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K20" s="5">
         <v>11390.97</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L20" s="5">
         <v>16004.54</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M20" s="5">
         <v>16211.92</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N20" s="5">
         <v>16487.66</v>
       </c>
-      <c r="O18" s="5">
+      <c r="O20" s="5">
         <v>14994.71</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P20" s="5">
         <v>10969.67</v>
       </c>
-      <c r="Q18" s="5">
+      <c r="Q20" s="5">
         <v>11920.52</v>
       </c>
-      <c r="R18" s="5">
+      <c r="R20" s="5">
         <v>21000.5</v>
       </c>
-      <c r="Z18" s="6">
-        <f>average(N18:Y18)</f>
+      <c r="Z20" s="6">
+        <f>average(N20:Y20)</f>
         <v>15074.612</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="8" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="9">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="9">
+        <v>0.6667</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0.4286</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0.4286</v>
+      </c>
+      <c r="H21" s="9">
         <v>0.5</v>
       </c>
-      <c r="F19" s="9">
+      <c r="I21" s="9">
+        <v>0.5333</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0.381</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0.2963</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0.3571</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0.33</v>
+      </c>
+      <c r="N21" s="9">
+        <v>0.2308</v>
+      </c>
+      <c r="O21" s="11">
+        <v>0.1613</v>
+      </c>
+      <c r="P21" s="11">
+        <v>0.3673</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="4"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="13">
         <v>0.5625</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G22" s="13">
         <v>0.5714</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H22" s="13">
         <v>0.4815</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I22" s="13">
         <v>0.4634</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J22" s="13">
         <v>0.4898</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K22" s="13">
         <v>0.463</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L22" s="13">
         <v>0.377</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M22" s="13">
         <v>0.3387</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N22" s="13">
         <v>0.3265</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O22" s="13">
         <v>0.3056</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P22" s="13">
         <v>0.2075</v>
       </c>
-      <c r="Q19" s="9">
+      <c r="Q22" s="13">
         <v>0.2615</v>
       </c>
-      <c r="R19" s="9">
+      <c r="R22" s="13">
         <v>0.232</v>
       </c>
-      <c r="S19" s="9"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10">
-        <f>average(R19:Y19)</f>
+      <c r="S22" s="13"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14">
+        <f>average(R22:Y22)</f>
         <v>0.232</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1" t="s">
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B25" s="2">
         <v>45658.0</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C25" s="2">
         <v>45689.0</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D25" s="2">
         <v>45717.0</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E25" s="2">
         <v>45748.0</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F25" s="2">
         <v>45778.0</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G25" s="2">
         <v>45809.0</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H25" s="2">
         <v>45839.0</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I25" s="2">
         <v>45870.0</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J25" s="2">
         <v>45901.0</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K25" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M22" s="2">
+      <c r="L25" s="3">
+        <v>45962.0</v>
+      </c>
+      <c r="M25" s="2">
         <v>45992.0</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N25" s="2">
         <v>46023.0</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O25" s="2">
         <v>46054.0</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P25" s="2">
         <v>46082.0</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q25" s="2">
         <v>46113.0</v>
       </c>
-      <c r="R22" s="2">
+      <c r="R25" s="2">
         <v>46143.0</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S25" s="2">
         <v>46174.0</v>
       </c>
-      <c r="T22" s="2">
+      <c r="T25" s="2">
         <v>46204.0</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U25" s="2">
         <v>46235.0</v>
       </c>
-      <c r="V22" s="2">
+      <c r="V25" s="2">
         <v>46266.0</v>
       </c>
-      <c r="W22" s="2">
+      <c r="W25" s="2">
         <v>46296.0</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X25" s="2">
         <v>46327.0</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y25" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z22" s="4" t="s">
+      <c r="Z25" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C26" s="5">
         <v>18650.58</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D26" s="5">
         <v>30930.58</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E26" s="5">
         <v>10220.61</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F26" s="5">
         <v>40940.34</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G26" s="5">
         <v>31725.85</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H26" s="5">
         <v>59653.44</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I26" s="5">
         <v>52341.19</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J26" s="5">
         <v>43968.35</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K26" s="5">
         <v>55035.51</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L26" s="5">
         <v>30872.18</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M26" s="5">
         <v>5421.62</v>
       </c>
-      <c r="N23" s="5">
+      <c r="N26" s="5">
         <v>9080.08</v>
       </c>
-      <c r="O23" s="5">
+      <c r="O26" s="5">
         <v>5713.65</v>
       </c>
-      <c r="P23" s="5">
+      <c r="P26" s="5">
         <v>55012.85</v>
       </c>
-      <c r="Q23" s="5">
+      <c r="Q26" s="5">
         <v>13845.3</v>
       </c>
-      <c r="R23" s="5">
+      <c r="R26" s="5">
         <v>88880.21</v>
       </c>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="Z23" s="6">
-        <f t="shared" ref="Z23:Z24" si="5">sum(N23:Y23)</f>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="Z26" s="6">
+        <f t="shared" ref="Z26:Z27" si="5">sum(N26:Y26)</f>
         <v>172532.09</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C27" s="7">
         <v>1.0</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D27" s="7">
         <v>5.0</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E27" s="7">
         <v>2.0</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F27" s="7">
         <v>3.0</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G27" s="7">
         <v>13.0</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H27" s="7">
         <v>13.0</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I27" s="7">
         <v>10.0</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J27" s="7">
         <v>13.0</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K27" s="7">
         <v>16.0</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L27" s="7">
         <v>6.0</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M27" s="7">
         <v>2.0</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N27" s="7">
         <v>7.0</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O27" s="7">
         <v>2.0</v>
       </c>
-      <c r="P24" s="7">
+      <c r="P27" s="7">
         <v>14.0</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="Q27" s="7">
         <v>12.0</v>
       </c>
-      <c r="R24" s="7">
+      <c r="R27" s="7">
         <v>10.0</v>
       </c>
-      <c r="S24" s="7"/>
-      <c r="W24" s="11"/>
-      <c r="Z24" s="4">
+      <c r="S27" s="7"/>
+      <c r="W27" s="15"/>
+      <c r="Z27" s="4">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C28" s="5">
         <v>18650.58</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D28" s="5">
         <v>6186.12</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E28" s="5">
         <v>5110.3</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F28" s="5">
         <v>13646.78</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G28" s="5">
         <v>2440.45</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H28" s="5">
         <v>4588.73</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I28" s="5">
         <v>5234.12</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J28" s="5">
         <v>3382.18</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K28" s="5">
         <v>3439.72</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L28" s="5">
         <v>5145.36</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M28" s="5">
         <v>2710.81</v>
       </c>
-      <c r="N25" s="5">
+      <c r="N28" s="5">
         <v>1297.15</v>
       </c>
-      <c r="O25" s="5">
+      <c r="O28" s="5">
         <v>2856.82</v>
       </c>
-      <c r="P25" s="5">
+      <c r="P28" s="5">
         <v>3929.49</v>
       </c>
-      <c r="Q25" s="5">
+      <c r="Q28" s="5">
         <v>1153.77</v>
       </c>
-      <c r="R25" s="5">
+      <c r="R28" s="5">
         <v>8888.02</v>
       </c>
-      <c r="T25" s="12"/>
-      <c r="W25" s="11"/>
-      <c r="Z25" s="6">
-        <f>average(N25:Y25)</f>
+      <c r="T28" s="16"/>
+      <c r="W28" s="15"/>
+      <c r="Z28" s="6">
+        <f>average(N28:Y28)</f>
         <v>3625.05</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="8" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="9">
+      <c r="B29" s="10"/>
+      <c r="C29" s="9">
+        <v>0.2143</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0.5556</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0.2632</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0.3714</v>
+      </c>
+      <c r="H29" s="9">
+        <v>0.6667</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0.2222</v>
+      </c>
+      <c r="J29" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="K29" s="9">
+        <v>0.3636</v>
+      </c>
+      <c r="L29" s="9">
+        <v>0.1852</v>
+      </c>
+      <c r="M29" s="9">
         <v>0.1333</v>
       </c>
-      <c r="D26" s="9">
+      <c r="N29" s="9">
+        <v>0.2381</v>
+      </c>
+      <c r="O29" s="9">
+        <v>0.2308</v>
+      </c>
+      <c r="P29" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>0.2759</v>
+      </c>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="4"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="13">
+        <v>0.1333</v>
+      </c>
+      <c r="D30" s="13">
         <v>0.1667</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E30" s="13">
         <v>0.3514</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F30" s="13">
         <v>0.375</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G30" s="13">
         <v>0.3778</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H30" s="13">
         <v>0.3226</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I30" s="13">
         <v>0.4359</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J30" s="13">
         <v>0.4286</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K30" s="13">
         <v>0.4366</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L30" s="13">
         <v>0.3457</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M30" s="13">
         <v>0.3222</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N30" s="13">
         <v>0.2568</v>
       </c>
-      <c r="O26" s="9">
+      <c r="O30" s="13">
         <v>0.1905</v>
       </c>
-      <c r="P26" s="9">
+      <c r="P30" s="13">
         <v>0.2281</v>
       </c>
-      <c r="Q26" s="9">
+      <c r="Q30" s="13">
         <v>0.3243</v>
       </c>
-      <c r="R26" s="9">
+      <c r="R30" s="13">
         <v>0.3297</v>
       </c>
-      <c r="S26" s="9"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="10">
-        <f>average(R26:Y26)</f>
+      <c r="S30" s="13"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14">
+        <f>average(R30:Y30)</f>
         <v>0.3297</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="1" t="s">
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B33" s="2">
         <v>45658.0</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C33" s="2">
         <v>45689.0</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D33" s="2">
         <v>45717.0</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E33" s="2">
         <v>45748.0</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F33" s="2">
         <v>45778.0</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G33" s="2">
         <v>45809.0</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H33" s="2">
         <v>45839.0</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I33" s="2">
         <v>45870.0</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J33" s="2">
         <v>45901.0</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K33" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M29" s="2">
+      <c r="L33" s="3">
+        <v>45962.0</v>
+      </c>
+      <c r="M33" s="2">
         <v>45992.0</v>
       </c>
-      <c r="N29" s="2">
+      <c r="N33" s="2">
         <v>46023.0</v>
       </c>
-      <c r="O29" s="2">
+      <c r="O33" s="2">
         <v>46054.0</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P33" s="2">
         <v>46082.0</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q33" s="2">
         <v>46113.0</v>
       </c>
-      <c r="R29" s="2">
+      <c r="R33" s="2">
         <v>46143.0</v>
       </c>
-      <c r="S29" s="2">
+      <c r="S33" s="2">
         <v>46174.0</v>
       </c>
-      <c r="T29" s="2">
+      <c r="T33" s="2">
         <v>46204.0</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U33" s="2">
         <v>46235.0</v>
       </c>
-      <c r="V29" s="2">
+      <c r="V33" s="2">
         <v>46266.0</v>
       </c>
-      <c r="W29" s="2">
+      <c r="W33" s="2">
         <v>46296.0</v>
       </c>
-      <c r="X29" s="2">
+      <c r="X33" s="2">
         <v>46327.0</v>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y33" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z29" s="4" t="s">
+      <c r="Z33" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B34" s="5">
         <v>55872.76</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C34" s="5">
         <v>2336.73</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D34" s="5">
         <v>33592.39</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E34" s="5">
         <v>21413.67</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F34" s="5">
         <v>186331.34</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G34" s="5">
         <v>163356.3</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H34" s="5">
         <v>93899.31</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I34" s="5">
         <v>95663.96</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J34" s="5">
         <v>52111.35</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K34" s="5">
         <v>205694.01</v>
       </c>
-      <c r="L30" s="5">
+      <c r="L34" s="5">
         <v>38500.4</v>
       </c>
-      <c r="M30" s="5">
+      <c r="M34" s="5">
         <v>14861.34</v>
       </c>
-      <c r="N30" s="11"/>
-      <c r="O30" s="5">
+      <c r="N34" s="15"/>
+      <c r="O34" s="5">
         <v>8067.86</v>
       </c>
-      <c r="P30" s="5">
+      <c r="P34" s="5">
         <v>108802.59</v>
       </c>
-      <c r="Q30" s="5">
+      <c r="Q34" s="5">
         <v>149911.53</v>
       </c>
-      <c r="R30" s="5">
+      <c r="R34" s="5">
         <v>158044.97</v>
       </c>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-      <c r="Z30" s="6">
-        <f t="shared" ref="Z30:Z31" si="6">sum(N30:Y30)</f>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="Z34" s="6">
+        <f t="shared" ref="Z34:Z35" si="6">sum(N34:Y34)</f>
         <v>424826.95</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B35" s="7">
         <v>2.0</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C35" s="7">
         <v>2.0</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D35" s="7">
         <v>1.0</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E35" s="7">
         <v>8.0</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F35" s="7">
         <v>13.0</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G35" s="7">
         <v>8.0</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H35" s="7">
         <v>10.0</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I35" s="7">
         <v>2.0</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J35" s="7">
         <v>4.0</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K35" s="7">
         <v>17.0</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L35" s="7">
         <v>5.0</v>
       </c>
-      <c r="M31" s="7">
+      <c r="M35" s="7">
         <v>8.0</v>
       </c>
-      <c r="O31" s="7">
+      <c r="O35" s="7">
         <v>1.0</v>
       </c>
-      <c r="P31" s="7">
+      <c r="P35" s="7">
         <v>9.0</v>
       </c>
-      <c r="Q31" s="7">
+      <c r="Q35" s="7">
         <v>16.0</v>
       </c>
-      <c r="R31" s="7">
+      <c r="R35" s="7">
         <v>9.0</v>
       </c>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="Z31" s="4">
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="Z35" s="4">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4" t="s">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B36" s="5">
         <v>27936.38</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C36" s="5">
         <v>1168.36</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D36" s="5">
         <v>33592.39</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E36" s="5">
         <v>2676.71</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F36" s="5">
         <v>14333.18</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G36" s="5">
         <v>20419.54</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H36" s="5">
         <v>9389.93</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I36" s="5">
         <v>47831.98</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J36" s="5">
         <v>13027.84</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K36" s="5">
         <v>12099.65</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L36" s="5">
         <v>7700.08</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M36" s="5">
         <v>1857.67</v>
       </c>
-      <c r="O32" s="5">
+      <c r="O36" s="5">
         <v>8067.86</v>
       </c>
-      <c r="P32" s="5">
+      <c r="P36" s="5">
         <v>12089.18</v>
       </c>
-      <c r="Q32" s="5">
+      <c r="Q36" s="5">
         <v>9369.47</v>
       </c>
-      <c r="R32" s="5">
+      <c r="R36" s="5">
         <v>17560.55</v>
       </c>
-      <c r="Z32" s="6">
-        <f>average(N32:Y32)</f>
+      <c r="Z36" s="6">
+        <f>average(N36:Y36)</f>
         <v>11771.765</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="8" t="s">
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B37" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="C37" s="9">
+        <v>0.4286</v>
+      </c>
+      <c r="D37" s="9">
+        <v>0.4211</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.4091</v>
+      </c>
+      <c r="F37" s="9">
+        <v>0.3793</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0.7143</v>
+      </c>
+      <c r="H37" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I37" s="9">
+        <v>0.2857</v>
+      </c>
+      <c r="J37" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="K37" s="9">
+        <v>0.2609</v>
+      </c>
+      <c r="L37" s="9">
+        <v>0.6364</v>
+      </c>
+      <c r="M37" s="10"/>
+      <c r="N37" s="9">
+        <v>0.1429</v>
+      </c>
+      <c r="O37" s="11">
+        <v>0.3333</v>
+      </c>
+      <c r="P37" s="11">
+        <v>0.3333</v>
+      </c>
+      <c r="Q37" s="9">
+        <v>0.303</v>
+      </c>
+      <c r="R37" s="13">
+        <v>0.0606</v>
+      </c>
+      <c r="S37" s="13"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="4"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="13">
         <v>0.4375</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C38" s="13">
         <v>0.4</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D38" s="13">
         <v>0.4</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E38" s="13">
         <v>0.4</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F38" s="13">
         <v>0.4167</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G38" s="13">
         <v>0.4</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H38" s="13">
         <v>0.4211</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I38" s="13">
         <v>0.451</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J38" s="13">
         <v>0.5161</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K38" s="13">
         <v>0.5128</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L38" s="13">
         <v>0.3913</v>
       </c>
-      <c r="M33" s="9">
+      <c r="M38" s="13">
         <v>0.46</v>
       </c>
-      <c r="N33" s="9">
+      <c r="N38" s="13">
         <v>0.325</v>
       </c>
-      <c r="O33" s="9">
+      <c r="O38" s="13">
         <v>0.3333</v>
       </c>
-      <c r="P33" s="9">
+      <c r="P38" s="13">
         <v>0.2564</v>
       </c>
-      <c r="Q33" s="9">
+      <c r="Q38" s="13">
         <v>0.3238</v>
       </c>
-      <c r="R33" s="9">
+      <c r="R38" s="13">
         <v>0.2432</v>
       </c>
-      <c r="S33" s="9"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="10"/>
-      <c r="V33" s="10"/>
-      <c r="W33" s="10"/>
-      <c r="X33" s="10"/>
-      <c r="Y33" s="10"/>
-      <c r="Z33" s="10">
-        <f>average(R33:Y33)</f>
+      <c r="S38" s="13"/>
+      <c r="T38" s="14"/>
+      <c r="U38" s="14"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="14"/>
+      <c r="Z38" s="14">
+        <f>average(R38:Y38)</f>
         <v>0.2432</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1" t="s">
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B41" s="2">
         <v>45658.0</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C41" s="2">
         <v>45689.0</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D41" s="2">
         <v>45717.0</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E41" s="2">
         <v>45748.0</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F41" s="2">
         <v>45778.0</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G41" s="2">
         <v>45809.0</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H41" s="2">
         <v>45839.0</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I41" s="2">
         <v>45870.0</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J41" s="2">
         <v>45901.0</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K41" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M36" s="2">
+      <c r="L41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M41" s="2">
         <v>45992.0</v>
       </c>
-      <c r="N36" s="2">
+      <c r="N41" s="2">
         <v>46023.0</v>
       </c>
-      <c r="O36" s="2">
+      <c r="O41" s="2">
         <v>46054.0</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P41" s="2">
         <v>46082.0</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q41" s="2">
         <v>46113.0</v>
       </c>
-      <c r="R36" s="2">
+      <c r="R41" s="2">
         <v>46143.0</v>
       </c>
-      <c r="S36" s="2">
+      <c r="S41" s="2">
         <v>46174.0</v>
       </c>
-      <c r="T36" s="2">
+      <c r="T41" s="2">
         <v>46204.0</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U41" s="2">
         <v>46235.0</v>
       </c>
-      <c r="V36" s="2">
+      <c r="V41" s="2">
         <v>46266.0</v>
       </c>
-      <c r="W36" s="2">
+      <c r="W41" s="2">
         <v>46296.0</v>
       </c>
-      <c r="X36" s="2">
+      <c r="X41" s="2">
         <v>46327.0</v>
       </c>
-      <c r="Y36" s="2">
+      <c r="Y41" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z36" s="4" t="s">
+      <c r="Z41" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="4" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="P37" s="5">
+      <c r="P42" s="5">
         <v>9374.61</v>
       </c>
-      <c r="Q37" s="5">
+      <c r="Q42" s="5">
         <v>123258.92</v>
       </c>
-      <c r="R37" s="5">
+      <c r="R42" s="5">
         <v>152476.32</v>
       </c>
-      <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
-      <c r="Z37" s="6">
-        <f t="shared" ref="Z37:Z38" si="7">sum(N37:Y37)</f>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="Z42" s="6">
+        <f t="shared" ref="Z42:Z43" si="7">sum(N42:Y42)</f>
         <v>285109.85</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="7">
+      <c r="P43" s="7">
         <v>5.0</v>
       </c>
-      <c r="Q38" s="7">
+      <c r="Q43" s="7">
         <v>12.0</v>
       </c>
-      <c r="R38" s="7">
+      <c r="R43" s="7">
         <v>12.0</v>
       </c>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="Z38" s="4">
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="Z43" s="4">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L39" s="11"/>
-      <c r="P39" s="5">
-        <v>1874.92</v>
-      </c>
-      <c r="Q39" s="5">
-        <v>10271.58</v>
-      </c>
-      <c r="R39" s="5">
-        <v>12706.36</v>
-      </c>
-      <c r="Z39" s="6">
-        <f>average(N39:Y39)</f>
-        <v>8284.286667</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9">
-        <v>0.1111</v>
-      </c>
-      <c r="Q40" s="9">
-        <v>0.2828</v>
-      </c>
-      <c r="R40" s="9">
-        <v>0.2667</v>
-      </c>
-      <c r="S40" s="9"/>
-      <c r="T40" s="10"/>
-      <c r="U40" s="10"/>
-      <c r="V40" s="10"/>
-      <c r="W40" s="10"/>
-      <c r="X40" s="10"/>
-      <c r="Y40" s="10"/>
-      <c r="Z40" s="10">
-        <f>average(R40:Y40)</f>
-        <v>0.2667</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="2">
-        <v>45658.0</v>
-      </c>
-      <c r="C43" s="2">
-        <v>45689.0</v>
-      </c>
-      <c r="D43" s="2">
-        <v>45717.0</v>
-      </c>
-      <c r="E43" s="2">
-        <v>45748.0</v>
-      </c>
-      <c r="F43" s="2">
-        <v>45778.0</v>
-      </c>
-      <c r="G43" s="2">
-        <v>45809.0</v>
-      </c>
-      <c r="H43" s="2">
-        <v>45839.0</v>
-      </c>
-      <c r="I43" s="2">
-        <v>45870.0</v>
-      </c>
-      <c r="J43" s="2">
-        <v>45901.0</v>
-      </c>
-      <c r="K43" s="2">
-        <v>45931.0</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M43" s="2">
-        <v>45992.0</v>
-      </c>
-      <c r="N43" s="2">
-        <v>46023.0</v>
-      </c>
-      <c r="O43" s="2">
-        <v>46054.0</v>
-      </c>
-      <c r="P43" s="2">
-        <v>46082.0</v>
-      </c>
-      <c r="Q43" s="2">
-        <v>46113.0</v>
-      </c>
-      <c r="R43" s="2">
-        <v>46143.0</v>
-      </c>
-      <c r="S43" s="2">
-        <v>46174.0</v>
-      </c>
-      <c r="T43" s="2">
-        <v>46204.0</v>
-      </c>
-      <c r="U43" s="2">
-        <v>46235.0</v>
-      </c>
-      <c r="V43" s="2">
-        <v>46266.0</v>
-      </c>
-      <c r="W43" s="2">
-        <v>46296.0</v>
-      </c>
-      <c r="X43" s="2">
-        <v>46327.0</v>
-      </c>
-      <c r="Y43" s="2">
-        <v>46357.0</v>
-      </c>
-      <c r="Z43" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="15"/>
+      <c r="P44" s="5">
+        <v>1874.92</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>10271.58</v>
+      </c>
+      <c r="R44" s="5">
+        <v>12706.36</v>
+      </c>
+      <c r="Z44" s="6">
+        <f>average(N44:Y44)</f>
+        <v>8284.286667</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="9">
+        <v>0.1429</v>
+      </c>
+      <c r="P45" s="11">
+        <v>0.3696</v>
+      </c>
+      <c r="Q45" s="11">
+        <v>0.2222</v>
+      </c>
+      <c r="R45" s="11">
+        <v>0.1724</v>
+      </c>
+      <c r="S45" s="13"/>
+      <c r="T45" s="14"/>
+      <c r="U45" s="14"/>
+      <c r="V45" s="14"/>
+      <c r="W45" s="14"/>
+      <c r="X45" s="14"/>
+      <c r="Y45" s="14"/>
+      <c r="Z45" s="14"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="13">
+        <v>0.1111</v>
+      </c>
+      <c r="Q46" s="13">
+        <v>0.2828</v>
+      </c>
+      <c r="R46" s="13">
+        <v>0.2667</v>
+      </c>
+      <c r="S46" s="13"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
+      <c r="Y46" s="14"/>
+      <c r="Z46" s="14">
+        <f>average(R46:Y46)</f>
+        <v>0.2667</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="Q47" s="13"/>
+      <c r="R47" s="13"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="2">
+        <v>45658.0</v>
+      </c>
+      <c r="C49" s="2">
+        <v>45689.0</v>
+      </c>
+      <c r="D49" s="2">
+        <v>45717.0</v>
+      </c>
+      <c r="E49" s="2">
+        <v>45748.0</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45778.0</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45809.0</v>
+      </c>
+      <c r="H49" s="2">
+        <v>45839.0</v>
+      </c>
+      <c r="I49" s="2">
+        <v>45870.0</v>
+      </c>
+      <c r="J49" s="2">
+        <v>45901.0</v>
+      </c>
+      <c r="K49" s="2">
+        <v>45931.0</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M49" s="2">
+        <v>45992.0</v>
+      </c>
+      <c r="N49" s="2">
+        <v>46023.0</v>
+      </c>
+      <c r="O49" s="2">
+        <v>46054.0</v>
+      </c>
+      <c r="P49" s="2">
+        <v>46082.0</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>46113.0</v>
+      </c>
+      <c r="R49" s="2">
+        <v>46143.0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>46174.0</v>
+      </c>
+      <c r="T49" s="2">
+        <v>46204.0</v>
+      </c>
+      <c r="U49" s="2">
+        <v>46235.0</v>
+      </c>
+      <c r="V49" s="2">
+        <v>46266.0</v>
+      </c>
+      <c r="W49" s="2">
+        <v>46296.0</v>
+      </c>
+      <c r="X49" s="2">
+        <v>46327.0</v>
+      </c>
+      <c r="Y49" s="2">
+        <v>46357.0</v>
+      </c>
+      <c r="Z49" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="P44" s="5">
+      <c r="P50" s="5">
         <v>816.62</v>
       </c>
-      <c r="Q44" s="5">
+      <c r="Q50" s="5">
         <v>124770.34</v>
       </c>
-      <c r="R44" s="5">
+      <c r="R50" s="5">
         <v>78978.19</v>
       </c>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="Z44" s="6">
-        <f t="shared" ref="Z44:Z45" si="8">sum(N44:Y44)</f>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="Z50" s="6">
+        <f t="shared" ref="Z50:Z51" si="8">sum(N50:Y50)</f>
         <v>204565.15</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="4" t="s">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="7">
+      <c r="P51" s="7">
         <v>2.0</v>
       </c>
-      <c r="Q45" s="7">
+      <c r="Q51" s="7">
         <v>13.0</v>
       </c>
-      <c r="R45" s="7">
+      <c r="R51" s="7">
         <v>15.0</v>
       </c>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
-      <c r="Z45" s="4">
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="Z51" s="4">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="P46" s="5">
-        <v>408.31</v>
-      </c>
-      <c r="Q46" s="5">
-        <v>9597.72</v>
-      </c>
-      <c r="R46" s="5">
-        <v>5265.21</v>
-      </c>
-      <c r="Z46" s="6">
-        <f>average(N46:Y46)</f>
-        <v>5090.413333</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="9">
-        <v>0.2727</v>
-      </c>
-      <c r="R47" s="9">
-        <v>0.296</v>
-      </c>
-      <c r="S47" s="9"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
-      <c r="V47" s="10"/>
-      <c r="W47" s="10"/>
-      <c r="X47" s="10"/>
-      <c r="Y47" s="10"/>
-      <c r="Z47" s="10">
-        <f>average(R47:Y47)</f>
-        <v>0.296</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B50" s="2">
-        <v>45658.0</v>
-      </c>
-      <c r="C50" s="2">
-        <v>45689.0</v>
-      </c>
-      <c r="D50" s="2">
-        <v>45717.0</v>
-      </c>
-      <c r="E50" s="2">
-        <v>45748.0</v>
-      </c>
-      <c r="F50" s="2">
-        <v>45778.0</v>
-      </c>
-      <c r="G50" s="2">
-        <v>45809.0</v>
-      </c>
-      <c r="H50" s="2">
-        <v>45839.0</v>
-      </c>
-      <c r="I50" s="2">
-        <v>45870.0</v>
-      </c>
-      <c r="J50" s="2">
-        <v>45901.0</v>
-      </c>
-      <c r="K50" s="2">
-        <v>45931.0</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M50" s="2">
-        <v>45992.0</v>
-      </c>
-      <c r="N50" s="2">
-        <v>46023.0</v>
-      </c>
-      <c r="O50" s="2">
-        <v>46054.0</v>
-      </c>
-      <c r="P50" s="2">
-        <v>46082.0</v>
-      </c>
-      <c r="Q50" s="2">
-        <v>46113.0</v>
-      </c>
-      <c r="R50" s="2">
-        <v>46143.0</v>
-      </c>
-      <c r="S50" s="2">
-        <v>46174.0</v>
-      </c>
-      <c r="T50" s="2">
-        <v>46204.0</v>
-      </c>
-      <c r="U50" s="2">
-        <v>46235.0</v>
-      </c>
-      <c r="V50" s="2">
-        <v>46266.0</v>
-      </c>
-      <c r="W50" s="2">
-        <v>46296.0</v>
-      </c>
-      <c r="X50" s="2">
-        <v>46327.0</v>
-      </c>
-      <c r="Y50" s="2">
-        <v>46357.0</v>
-      </c>
-      <c r="Z50" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D51" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="E51" s="5">
-        <v>16769.23</v>
-      </c>
-      <c r="F51" s="5">
-        <v>23954.74</v>
-      </c>
-      <c r="H51" s="5">
-        <v>106322.49</v>
-      </c>
-      <c r="I51" s="5">
-        <v>3769.0</v>
-      </c>
-      <c r="L51" s="11"/>
-      <c r="M51" s="5">
-        <v>2632.6</v>
-      </c>
-      <c r="O51" s="5">
-        <v>33846.16</v>
-      </c>
-      <c r="P51" s="5">
-        <v>1121.66</v>
-      </c>
-      <c r="Q51" s="5">
-        <v>109114.01</v>
-      </c>
-      <c r="R51" s="5">
-        <v>52999.57</v>
-      </c>
-      <c r="S51" s="5"/>
-      <c r="T51" s="5"/>
-      <c r="Z51" s="6">
-        <f t="shared" ref="Z51:Z52" si="9">sum(N51:Y51)</f>
-        <v>197081.4</v>
-      </c>
-    </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="5">
+        <v>408.31</v>
+      </c>
+      <c r="Q52" s="5">
+        <v>9597.72</v>
+      </c>
+      <c r="R52" s="5">
+        <v>5265.21</v>
+      </c>
+      <c r="Z52" s="6">
+        <f>average(N52:Y52)</f>
+        <v>5090.413333</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="11">
+        <v>0.3778</v>
+      </c>
+      <c r="Q53" s="11">
+        <v>0.2222</v>
+      </c>
+      <c r="R53" s="11">
+        <v>0.2857</v>
+      </c>
+      <c r="S53" s="13"/>
+      <c r="T53" s="14"/>
+      <c r="U53" s="14"/>
+      <c r="V53" s="14"/>
+      <c r="W53" s="14"/>
+      <c r="X53" s="14"/>
+      <c r="Y53" s="14"/>
+      <c r="Z53" s="14"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="14"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13">
+        <v>0.2727</v>
+      </c>
+      <c r="R54" s="13">
+        <v>0.296</v>
+      </c>
+      <c r="S54" s="13"/>
+      <c r="T54" s="14"/>
+      <c r="U54" s="14"/>
+      <c r="V54" s="14"/>
+      <c r="W54" s="14"/>
+      <c r="X54" s="14"/>
+      <c r="Y54" s="14"/>
+      <c r="Z54" s="14">
+        <f>average(R54:Y54)</f>
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
+      <c r="T57" s="2"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="2"/>
+      <c r="W57" s="2"/>
+      <c r="X57" s="2"/>
+      <c r="Y57" s="2"/>
+      <c r="Z57" s="4"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="4"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
+      <c r="S58" s="5"/>
+      <c r="T58" s="5"/>
+      <c r="Z58" s="6"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="4"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7"/>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+      <c r="Z59" s="4"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5"/>
+      <c r="Z60" s="6"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="8"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13"/>
+      <c r="P61" s="13"/>
+      <c r="Q61" s="13"/>
+      <c r="R61" s="13"/>
+      <c r="S61" s="14"/>
+      <c r="T61" s="14"/>
+      <c r="U61" s="14"/>
+      <c r="V61" s="14"/>
+      <c r="W61" s="14"/>
+      <c r="X61" s="14"/>
+      <c r="Y61" s="14"/>
+      <c r="Z61" s="4"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="14"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
+      <c r="Q62" s="13"/>
+      <c r="R62" s="13"/>
+      <c r="S62" s="14"/>
+      <c r="T62" s="14"/>
+      <c r="U62" s="14"/>
+      <c r="V62" s="14"/>
+      <c r="W62" s="14"/>
+      <c r="X62" s="14"/>
+      <c r="Y62" s="14"/>
+      <c r="Z62" s="4"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="2"/>
+      <c r="X63" s="2"/>
+      <c r="Y63" s="2"/>
+      <c r="Z63" s="4"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="B64" s="2">
+        <v>45658.0</v>
+      </c>
+      <c r="C64" s="2">
+        <v>45689.0</v>
+      </c>
+      <c r="D64" s="2">
+        <v>45717.0</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45748.0</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45778.0</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45809.0</v>
+      </c>
+      <c r="H64" s="2">
+        <v>45839.0</v>
+      </c>
+      <c r="I64" s="2">
+        <v>45870.0</v>
+      </c>
+      <c r="J64" s="2">
+        <v>45901.0</v>
+      </c>
+      <c r="K64" s="2">
+        <v>45931.0</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M64" s="2">
+        <v>45992.0</v>
+      </c>
+      <c r="N64" s="2">
+        <v>46023.0</v>
+      </c>
+      <c r="O64" s="2">
+        <v>46054.0</v>
+      </c>
+      <c r="P64" s="2">
+        <v>46082.0</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>46113.0</v>
+      </c>
+      <c r="R64" s="2">
+        <v>46143.0</v>
+      </c>
+      <c r="S64" s="2">
+        <v>46174.0</v>
+      </c>
+      <c r="T64" s="2">
+        <v>46204.0</v>
+      </c>
+      <c r="U64" s="2">
+        <v>46235.0</v>
+      </c>
+      <c r="V64" s="2">
+        <v>46266.0</v>
+      </c>
+      <c r="W64" s="2">
+        <v>46296.0</v>
+      </c>
+      <c r="X64" s="2">
+        <v>46327.0</v>
+      </c>
+      <c r="Y64" s="2">
+        <v>46357.0</v>
+      </c>
+      <c r="Z64" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" s="6">
+        <f t="shared" ref="B65:Y65" si="9">sum(B58,B50,B42,B34,B26,B18,B10,B2)</f>
+        <v>89497.5</v>
+      </c>
+      <c r="C65" s="6">
+        <f t="shared" si="9"/>
+        <v>96780.4</v>
+      </c>
+      <c r="D65" s="6">
+        <f t="shared" si="9"/>
+        <v>266085.41</v>
+      </c>
+      <c r="E65" s="6">
+        <f t="shared" si="9"/>
+        <v>174339.54</v>
+      </c>
+      <c r="F65" s="6">
+        <f t="shared" si="9"/>
+        <v>454397.81</v>
+      </c>
+      <c r="G65" s="6">
+        <f t="shared" si="9"/>
+        <v>732280.47</v>
+      </c>
+      <c r="H65" s="6">
+        <f t="shared" si="9"/>
+        <v>577977.59</v>
+      </c>
+      <c r="I65" s="6">
+        <f t="shared" si="9"/>
+        <v>314768.92</v>
+      </c>
+      <c r="J65" s="6">
+        <f t="shared" si="9"/>
+        <v>337890.59</v>
+      </c>
+      <c r="K65" s="6">
+        <f t="shared" si="9"/>
+        <v>691198.5</v>
+      </c>
+      <c r="L65" s="6">
+        <f t="shared" si="9"/>
+        <v>265364.49</v>
+      </c>
+      <c r="M65" s="6">
+        <f t="shared" si="9"/>
+        <v>120054.95</v>
+      </c>
+      <c r="N65" s="6">
+        <f t="shared" si="9"/>
+        <v>165703.1</v>
+      </c>
+      <c r="O65" s="6">
+        <f t="shared" si="9"/>
+        <v>63070.38</v>
+      </c>
+      <c r="P65" s="6">
+        <f t="shared" si="9"/>
+        <v>366951.73</v>
+      </c>
+      <c r="Q65" s="6">
+        <f t="shared" si="9"/>
+        <v>1238188.94</v>
+      </c>
+      <c r="R65" s="6">
+        <f t="shared" si="9"/>
+        <v>1122433.97</v>
+      </c>
+      <c r="S65" s="20">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T65" s="20">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U65" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V65" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W65" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X65" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y65" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z65" s="6">
+        <f>sum(N65:Y65)</f>
+        <v>2956348.12</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="6">
+        <f t="shared" ref="B66:Z66" si="10">average(B58,B50,B42,B34,B26,B18,B10,B2)</f>
+        <v>44748.75</v>
+      </c>
+      <c r="C66" s="6">
+        <f t="shared" si="10"/>
+        <v>24195.1</v>
+      </c>
+      <c r="D66" s="6">
+        <f t="shared" si="10"/>
+        <v>66521.3525</v>
+      </c>
+      <c r="E66" s="6">
+        <f t="shared" si="10"/>
+        <v>34867.908</v>
+      </c>
+      <c r="F66" s="6">
+        <f t="shared" si="10"/>
+        <v>90879.562</v>
+      </c>
+      <c r="G66" s="6">
+        <f t="shared" si="10"/>
+        <v>146456.094</v>
+      </c>
+      <c r="H66" s="6">
+        <f t="shared" si="10"/>
+        <v>115595.518</v>
+      </c>
+      <c r="I66" s="6">
+        <f t="shared" si="10"/>
+        <v>62953.784</v>
+      </c>
+      <c r="J66" s="6">
+        <f t="shared" si="10"/>
+        <v>67578.118</v>
+      </c>
+      <c r="K66" s="6">
+        <f t="shared" si="10"/>
+        <v>138239.7</v>
+      </c>
+      <c r="L66" s="6">
+        <f t="shared" si="10"/>
+        <v>53072.898</v>
+      </c>
+      <c r="M66" s="6">
+        <f t="shared" si="10"/>
+        <v>24010.99</v>
+      </c>
+      <c r="N66" s="6">
+        <f t="shared" si="10"/>
+        <v>55234.36667</v>
+      </c>
+      <c r="O66" s="6">
+        <f t="shared" si="10"/>
+        <v>15767.595</v>
+      </c>
+      <c r="P66" s="6">
+        <f t="shared" si="10"/>
+        <v>52421.67571</v>
+      </c>
+      <c r="Q66" s="6">
+        <f t="shared" si="10"/>
+        <v>176884.1343</v>
+      </c>
+      <c r="R66" s="6">
+        <f t="shared" si="10"/>
+        <v>160347.71</v>
+      </c>
+      <c r="S66" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T66" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U66" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V66" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W66" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X66" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y66" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z66" s="6">
+        <f t="shared" si="10"/>
+        <v>422335.4457</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D52" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="F52" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="H52" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="I52" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="M52" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="O52" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="P52" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="Q52" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="R52" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
-      <c r="Z52" s="4">
-        <f t="shared" si="9"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="4" t="s">
+      <c r="B67" s="21">
+        <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
+        <v>2</v>
+      </c>
+      <c r="C67" s="21">
+        <f t="shared" si="11"/>
+        <v>1.75</v>
+      </c>
+      <c r="D67" s="21">
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="D53" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="E53" s="5">
-        <v>16769.23</v>
-      </c>
-      <c r="F53" s="5">
-        <v>11977.37</v>
-      </c>
-      <c r="H53" s="5">
-        <v>35440.83</v>
-      </c>
-      <c r="I53" s="5">
-        <v>3769.0</v>
-      </c>
-      <c r="M53" s="5">
-        <v>2632.6</v>
-      </c>
-      <c r="O53" s="5">
-        <v>16923.08</v>
-      </c>
-      <c r="P53" s="5">
-        <v>373.89</v>
-      </c>
-      <c r="Q53" s="5">
-        <v>12123.78</v>
-      </c>
-      <c r="R53" s="5">
-        <v>17666.52</v>
-      </c>
-      <c r="Z53" s="6">
-        <f>average(N53:Y53)</f>
-        <v>11771.8175</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="N54" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="O54" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="P54" s="9">
-        <v>0.4286</v>
-      </c>
-      <c r="Q54" s="9">
-        <v>0.4848</v>
-      </c>
-      <c r="R54" s="9">
-        <v>0.4118</v>
-      </c>
-      <c r="S54" s="10"/>
-      <c r="T54" s="10"/>
-      <c r="U54" s="10"/>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
-      <c r="X54" s="10"/>
-      <c r="Y54" s="10"/>
-      <c r="Z54" s="10">
-        <f>average(R54:Y54)</f>
-        <v>0.4118</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="2"/>
-      <c r="T55" s="2"/>
-      <c r="U55" s="2"/>
-      <c r="V55" s="2"/>
-      <c r="W55" s="2"/>
-      <c r="X55" s="2"/>
-      <c r="Y55" s="2"/>
-      <c r="Z55" s="4"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="B56" s="2">
-        <v>45658.0</v>
-      </c>
-      <c r="C56" s="2">
-        <v>45689.0</v>
-      </c>
-      <c r="D56" s="2">
-        <v>45717.0</v>
-      </c>
-      <c r="E56" s="2">
-        <v>45748.0</v>
-      </c>
-      <c r="F56" s="2">
-        <v>45778.0</v>
-      </c>
-      <c r="G56" s="2">
-        <v>45809.0</v>
-      </c>
-      <c r="H56" s="2">
-        <v>45839.0</v>
-      </c>
-      <c r="I56" s="2">
-        <v>45870.0</v>
-      </c>
-      <c r="J56" s="2">
-        <v>45901.0</v>
-      </c>
-      <c r="K56" s="2">
-        <v>45931.0</v>
-      </c>
-      <c r="L56" s="4" t="s">
+      <c r="E67" s="21">
+        <f t="shared" si="11"/>
+        <v>4.6</v>
+      </c>
+      <c r="F67" s="21">
+        <f t="shared" si="11"/>
+        <v>7.4</v>
+      </c>
+      <c r="G67" s="21">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="H67" s="21">
+        <f t="shared" si="11"/>
+        <v>8.2</v>
+      </c>
+      <c r="I67" s="21">
+        <f t="shared" si="11"/>
+        <v>6.4</v>
+      </c>
+      <c r="J67" s="21">
+        <f t="shared" si="11"/>
+        <v>7.2</v>
+      </c>
+      <c r="K67" s="21">
+        <f t="shared" si="11"/>
+        <v>14.2</v>
+      </c>
+      <c r="L67" s="21">
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M56" s="2">
-        <v>45992.0</v>
-      </c>
-      <c r="N56" s="2">
-        <v>46023.0</v>
-      </c>
-      <c r="O56" s="2">
-        <v>46054.0</v>
-      </c>
-      <c r="P56" s="2">
-        <v>46082.0</v>
-      </c>
-      <c r="Q56" s="2">
-        <v>46113.0</v>
-      </c>
-      <c r="R56" s="2">
-        <v>46143.0</v>
-      </c>
-      <c r="S56" s="2">
-        <v>46174.0</v>
-      </c>
-      <c r="T56" s="2">
-        <v>46204.0</v>
-      </c>
-      <c r="U56" s="2">
-        <v>46235.0</v>
-      </c>
-      <c r="V56" s="2">
-        <v>46266.0</v>
-      </c>
-      <c r="W56" s="2">
-        <v>46296.0</v>
-      </c>
-      <c r="X56" s="2">
-        <v>46327.0</v>
-      </c>
-      <c r="Y56" s="2">
-        <v>46357.0</v>
-      </c>
-      <c r="Z56" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B57" s="6">
-        <f t="shared" ref="B57:Y57" si="10">sum(B51,B44,B37,B30,B23,B16,B9,B2)</f>
-        <v>89497.5</v>
-      </c>
-      <c r="C57" s="6">
-        <f t="shared" si="10"/>
-        <v>96780.4</v>
-      </c>
-      <c r="D57" s="6">
-        <f t="shared" si="10"/>
-        <v>266185.41</v>
-      </c>
-      <c r="E57" s="6">
-        <f t="shared" si="10"/>
-        <v>191108.77</v>
-      </c>
-      <c r="F57" s="6">
-        <f t="shared" si="10"/>
-        <v>478352.55</v>
-      </c>
-      <c r="G57" s="6">
-        <f t="shared" si="10"/>
-        <v>732280.47</v>
-      </c>
-      <c r="H57" s="6">
-        <f t="shared" si="10"/>
-        <v>684300.08</v>
-      </c>
-      <c r="I57" s="6">
-        <f t="shared" si="10"/>
-        <v>318537.92</v>
-      </c>
-      <c r="J57" s="6">
-        <f t="shared" si="10"/>
-        <v>337890.59</v>
-      </c>
-      <c r="K57" s="6">
-        <f t="shared" si="10"/>
-        <v>691198.5</v>
-      </c>
-      <c r="L57" s="6">
-        <f t="shared" si="10"/>
-        <v>265364.49</v>
-      </c>
-      <c r="M57" s="6">
-        <f t="shared" si="10"/>
-        <v>122687.55</v>
-      </c>
-      <c r="N57" s="6">
-        <f t="shared" si="10"/>
-        <v>165703.1</v>
-      </c>
-      <c r="O57" s="6">
-        <f t="shared" si="10"/>
-        <v>96916.54</v>
-      </c>
-      <c r="P57" s="6">
-        <f t="shared" si="10"/>
-        <v>368073.39</v>
-      </c>
-      <c r="Q57" s="6">
-        <f t="shared" si="10"/>
-        <v>1347302.95</v>
-      </c>
-      <c r="R57" s="6">
-        <f t="shared" si="10"/>
-        <v>1175433.54</v>
-      </c>
-      <c r="S57" s="15">
-        <f t="shared" si="10"/>
+      <c r="M67" s="21">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="N67" s="21">
+        <f t="shared" si="11"/>
+        <v>5.666666667</v>
+      </c>
+      <c r="O67" s="21">
+        <f t="shared" si="11"/>
+        <v>3.75</v>
+      </c>
+      <c r="P67" s="21">
+        <f t="shared" si="11"/>
+        <v>7.714285714</v>
+      </c>
+      <c r="Q67" s="21">
+        <f t="shared" si="11"/>
+        <v>16.85714286</v>
+      </c>
+      <c r="R67" s="21">
+        <f t="shared" si="11"/>
+        <v>12.28571429</v>
+      </c>
+      <c r="S67" s="4">
+        <f t="shared" ref="S67:Y67" si="12">sum(S59,S51,S43,S35,S27,S19,S11,S3)</f>
         <v>0</v>
       </c>
-      <c r="T57" s="15">
-        <f t="shared" si="10"/>
+      <c r="T67" s="4">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U57" s="4">
-        <f t="shared" si="10"/>
+      <c r="U67" s="4">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="V57" s="4">
-        <f t="shared" si="10"/>
+      <c r="V67" s="4">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="W57" s="4">
-        <f t="shared" si="10"/>
+      <c r="W67" s="4">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X57" s="4">
-        <f t="shared" si="10"/>
+      <c r="X67" s="4">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Y57" s="4">
-        <f t="shared" si="10"/>
+      <c r="Y67" s="4">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z57" s="6">
-        <f>sum(N57:Y57)</f>
-        <v>3153429.52</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58" s="6">
-        <f t="shared" ref="B58:Z58" si="11">average(B51,B44,B37,B30,B23,B16,B9,B2)</f>
-        <v>44748.75</v>
-      </c>
-      <c r="C58" s="6">
-        <f t="shared" si="11"/>
-        <v>24195.1</v>
-      </c>
-      <c r="D58" s="6">
-        <f t="shared" si="11"/>
-        <v>53237.082</v>
-      </c>
-      <c r="E58" s="6">
-        <f t="shared" si="11"/>
-        <v>31851.46167</v>
-      </c>
-      <c r="F58" s="6">
-        <f t="shared" si="11"/>
-        <v>79725.425</v>
-      </c>
-      <c r="G58" s="6">
-        <f t="shared" si="11"/>
-        <v>146456.094</v>
-      </c>
-      <c r="H58" s="6">
-        <f t="shared" si="11"/>
-        <v>114050.0133</v>
-      </c>
-      <c r="I58" s="6">
-        <f t="shared" si="11"/>
-        <v>53089.65333</v>
-      </c>
-      <c r="J58" s="6">
-        <f t="shared" si="11"/>
-        <v>67578.118</v>
-      </c>
-      <c r="K58" s="6">
-        <f t="shared" si="11"/>
-        <v>138239.7</v>
-      </c>
-      <c r="L58" s="6">
-        <f t="shared" si="11"/>
-        <v>53072.898</v>
-      </c>
-      <c r="M58" s="6">
-        <f t="shared" si="11"/>
-        <v>20447.925</v>
-      </c>
-      <c r="N58" s="6">
-        <f t="shared" si="11"/>
-        <v>55234.36667</v>
-      </c>
-      <c r="O58" s="6">
-        <f t="shared" si="11"/>
-        <v>19383.308</v>
-      </c>
-      <c r="P58" s="6">
-        <f t="shared" si="11"/>
-        <v>46009.17375</v>
-      </c>
-      <c r="Q58" s="6">
-        <f t="shared" si="11"/>
-        <v>168412.8688</v>
-      </c>
-      <c r="R58" s="6">
-        <f t="shared" si="11"/>
-        <v>146929.1925</v>
-      </c>
-      <c r="S58" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="Z67" s="21">
+        <f>sum(N67:Y67)</f>
+        <v>46.27380952</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="6">
+        <f t="shared" ref="B68:Y68" si="13">AVERAGE(B60,B52,B44,B36,B28,B20,B12,B4)</f>
+        <v>22374.375</v>
+      </c>
+      <c r="C68" s="6">
+        <f t="shared" si="13"/>
+        <v>14428.8725</v>
+      </c>
+      <c r="D68" s="6">
+        <f t="shared" si="13"/>
+        <v>20022.7475</v>
+      </c>
+      <c r="E68" s="6">
+        <f t="shared" si="13"/>
+        <v>12879.358</v>
+      </c>
+      <c r="F68" s="6">
+        <f t="shared" si="13"/>
+        <v>10576.564</v>
+      </c>
+      <c r="G68" s="6">
+        <f t="shared" si="13"/>
+        <v>14472.008</v>
+      </c>
+      <c r="H68" s="6">
+        <f t="shared" si="13"/>
+        <v>17632.932</v>
+      </c>
+      <c r="I68" s="6">
+        <f t="shared" si="13"/>
+        <v>16201.158</v>
+      </c>
+      <c r="J68" s="6">
+        <f t="shared" si="13"/>
+        <v>10893.582</v>
+      </c>
+      <c r="K68" s="6">
+        <f t="shared" si="13"/>
+        <v>10478.64</v>
+      </c>
+      <c r="L68" s="6">
+        <f t="shared" si="13"/>
+        <v>7528.564</v>
+      </c>
+      <c r="M68" s="6">
+        <f t="shared" si="13"/>
+        <v>6484.368</v>
+      </c>
+      <c r="N68" s="6">
+        <f t="shared" si="13"/>
+        <v>10965.62667</v>
+      </c>
+      <c r="O68" s="6">
+        <f t="shared" si="13"/>
+        <v>7259.26</v>
+      </c>
+      <c r="P68" s="6">
+        <f t="shared" si="13"/>
+        <v>6149.781429</v>
+      </c>
+      <c r="Q68" s="6">
+        <f t="shared" si="13"/>
+        <v>10070.49286</v>
+      </c>
+      <c r="R68" s="6">
+        <f t="shared" si="13"/>
+        <v>13479.04857</v>
+      </c>
+      <c r="S68" s="4" t="str">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T58" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="T68" s="4" t="str">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U58" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="U68" s="4" t="str">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V58" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="V68" s="4" t="str">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W58" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="W68" s="4" t="str">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X58" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="X68" s="4" t="str">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y58" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="Y68" s="4" t="str">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z58" s="6">
-        <f t="shared" si="11"/>
-        <v>394178.69</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B59" s="16">
-        <f t="shared" ref="B59:R59" si="12">AVERAGE(B52,B45,B38,B31,B24,B17,B10,B3)</f>
-        <v>2</v>
-      </c>
-      <c r="C59" s="16">
-        <f t="shared" si="12"/>
-        <v>1.75</v>
-      </c>
-      <c r="D59" s="16">
-        <f t="shared" si="12"/>
-        <v>3.4</v>
-      </c>
-      <c r="E59" s="16">
-        <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="F59" s="16">
-        <f t="shared" si="12"/>
-        <v>6.5</v>
-      </c>
-      <c r="G59" s="16">
-        <f t="shared" si="12"/>
-        <v>12</v>
-      </c>
-      <c r="H59" s="16">
-        <f t="shared" si="12"/>
-        <v>7.333333333</v>
-      </c>
-      <c r="I59" s="16">
-        <f t="shared" si="12"/>
-        <v>5.5</v>
-      </c>
-      <c r="J59" s="16">
-        <f t="shared" si="12"/>
-        <v>7.2</v>
-      </c>
-      <c r="K59" s="16">
-        <f t="shared" si="12"/>
-        <v>14.2</v>
-      </c>
-      <c r="L59" s="16">
-        <f t="shared" si="12"/>
-        <v>7</v>
-      </c>
-      <c r="M59" s="16">
-        <f t="shared" si="12"/>
-        <v>3.5</v>
-      </c>
-      <c r="N59" s="16">
-        <f t="shared" si="12"/>
-        <v>5.666666667</v>
-      </c>
-      <c r="O59" s="16">
-        <f t="shared" si="12"/>
-        <v>3.4</v>
-      </c>
-      <c r="P59" s="16">
-        <f t="shared" si="12"/>
-        <v>7.125</v>
-      </c>
-      <c r="Q59" s="16">
-        <f t="shared" si="12"/>
-        <v>15.875</v>
-      </c>
-      <c r="R59" s="16">
-        <f t="shared" si="12"/>
-        <v>11.125</v>
-      </c>
-      <c r="S59" s="4">
-        <f t="shared" ref="S59:Y59" si="13">sum(S52,S45,S38,S31,S24,S17,S10,S3)</f>
-        <v>0</v>
-      </c>
-      <c r="T59" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U59" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V59" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="W59" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="X59" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Y59" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Z59" s="16">
-        <f>sum(N59:Y59)</f>
-        <v>43.19166667</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="6">
-        <f t="shared" ref="B60:Y60" si="14">AVERAGE(B53,B46,B39,B32,B25,B18,B11,B4)</f>
-        <v>22374.375</v>
-      </c>
-      <c r="C60" s="6">
+      <c r="Z68" s="6" t="str">
+        <f>average(N68:Y68)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="14">
+        <f t="shared" ref="B69:Y69" si="14">AVERAGE(B62,B54,B46,B38,B30,B22,B14,B6)</f>
+        <v>0.50445</v>
+      </c>
+      <c r="C69" s="14">
         <f t="shared" si="14"/>
-        <v>14428.8725</v>
-      </c>
-      <c r="D60" s="6">
+        <v>0.366525</v>
+      </c>
+      <c r="D69" s="14">
         <f t="shared" si="14"/>
-        <v>16038.198</v>
-      </c>
-      <c r="E60" s="6">
+        <v>0.30455</v>
+      </c>
+      <c r="E69" s="14">
         <f t="shared" si="14"/>
-        <v>13527.67</v>
-      </c>
-      <c r="F60" s="6">
+        <v>0.38494</v>
+      </c>
+      <c r="F69" s="14">
         <f t="shared" si="14"/>
-        <v>10810.03167</v>
-      </c>
-      <c r="G60" s="6">
+        <v>0.40984</v>
+      </c>
+      <c r="G69" s="14">
         <f t="shared" si="14"/>
-        <v>14472.008</v>
-      </c>
-      <c r="H60" s="6">
+        <v>0.4393</v>
+      </c>
+      <c r="H69" s="14">
         <f t="shared" si="14"/>
-        <v>20600.915</v>
-      </c>
-      <c r="I60" s="6">
+        <v>0.42082</v>
+      </c>
+      <c r="I69" s="14">
         <f t="shared" si="14"/>
-        <v>14129.13167</v>
-      </c>
-      <c r="J60" s="6">
+        <v>0.4131</v>
+      </c>
+      <c r="J69" s="14">
         <f t="shared" si="14"/>
-        <v>10893.582</v>
-      </c>
-      <c r="K60" s="6">
+        <v>0.3999</v>
+      </c>
+      <c r="K69" s="14">
         <f t="shared" si="14"/>
-        <v>10478.64</v>
-      </c>
-      <c r="L60" s="6">
+        <v>0.38592</v>
+      </c>
+      <c r="L69" s="14">
         <f t="shared" si="14"/>
-        <v>7528.564</v>
-      </c>
-      <c r="M60" s="6">
+        <v>0.33754</v>
+      </c>
+      <c r="M69" s="14">
         <f t="shared" si="14"/>
-        <v>5842.406667</v>
-      </c>
-      <c r="N60" s="6">
+        <v>0.34014</v>
+      </c>
+      <c r="N69" s="14">
         <f t="shared" si="14"/>
-        <v>10965.62667</v>
-      </c>
-      <c r="O60" s="6">
+        <v>0.30044</v>
+      </c>
+      <c r="O69" s="14">
         <f t="shared" si="14"/>
-        <v>9192.024</v>
-      </c>
-      <c r="P60" s="6">
+        <v>0.30184</v>
+      </c>
+      <c r="P69" s="14">
         <f t="shared" si="14"/>
-        <v>5427.795</v>
-      </c>
-      <c r="Q60" s="6">
+        <v>0.2368833333</v>
+      </c>
+      <c r="Q69" s="14">
         <f t="shared" si="14"/>
-        <v>10327.15375</v>
-      </c>
-      <c r="R60" s="6">
+        <v>0.3044714286</v>
+      </c>
+      <c r="R69" s="14">
         <f t="shared" si="14"/>
-        <v>14002.4825</v>
-      </c>
-      <c r="S60" s="4" t="str">
+        <v>0.2830428571</v>
+      </c>
+      <c r="S69" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T60" s="4" t="str">
+      <c r="T69" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U60" s="4" t="str">
+      <c r="U69" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V60" s="4" t="str">
+      <c r="V69" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W60" s="4" t="str">
+      <c r="W69" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X60" s="4" t="str">
+      <c r="X69" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y60" s="4" t="str">
+      <c r="Y69" s="4" t="str">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z60" s="6" t="str">
-        <f>average(N60:Y60)</f>
+      <c r="Z69" s="4" t="str">
+        <f>average(R69:Y69)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B61" s="10">
-        <f t="shared" ref="B61:Y61" si="15">AVERAGE(B54,B47,B40,B33,B26,B19,B12,B5)</f>
-        <v>0.50445</v>
-      </c>
-      <c r="C61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.366525</v>
-      </c>
-      <c r="D61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.30455</v>
-      </c>
-      <c r="E61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.38494</v>
-      </c>
-      <c r="F61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.40984</v>
-      </c>
-      <c r="G61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.4393</v>
-      </c>
-      <c r="H61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.42082</v>
-      </c>
-      <c r="I61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.4131</v>
-      </c>
-      <c r="J61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.3999</v>
-      </c>
-      <c r="K61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.38592</v>
-      </c>
-      <c r="L61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.33754</v>
-      </c>
-      <c r="M61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.4501166667</v>
-      </c>
-      <c r="N61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.4170333333</v>
-      </c>
-      <c r="O61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.3348666667</v>
-      </c>
-      <c r="P61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.2642714286</v>
-      </c>
-      <c r="Q61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.3270125</v>
-      </c>
-      <c r="R61" s="10">
-        <f t="shared" si="15"/>
-        <v>0.2991375</v>
-      </c>
-      <c r="S61" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T61" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U61" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V61" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W61" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X61" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y61" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z61" s="4" t="str">
-        <f>average(R61:Y61)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
     <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="B71" s="1"/>
-      <c r="S71" s="10"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="B72" s="1"/>
-      <c r="S72" s="10"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="B73" s="1"/>
-      <c r="S73" s="10"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="B74" s="1"/>
-      <c r="S74" s="10"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="B75" s="1"/>
-      <c r="S75" s="10"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="1"/>
-      <c r="S76" s="10"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="S77" s="10"/>
-    </row>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="B79" s="1"/>
+      <c r="S79" s="14"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="B80" s="1"/>
+      <c r="S80" s="14"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="B81" s="1"/>
+      <c r="S81" s="14"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="B82" s="1"/>
+      <c r="S82" s="14"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="B83" s="1"/>
+      <c r="S83" s="14"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="B84" s="1"/>
+      <c r="S84" s="14"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="S85" s="14"/>
+    </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
     <row r="88" ht="15.75" customHeight="1"/>
@@ -3284,75 +3553,7 @@
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
     <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="B101" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101" s="10" t="str">
-        <f t="shared" ref="C101:R101" si="16">average(C71:C76)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R101" s="10" t="str">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
+    <row r="101" ht="15.75" customHeight="1"/>
     <row r="102" ht="15.75" customHeight="1"/>
     <row r="103" ht="15.75" customHeight="1"/>
     <row r="104" ht="15.75" customHeight="1"/>
@@ -3360,7 +3561,75 @@
     <row r="106" ht="15.75" customHeight="1"/>
     <row r="107" ht="15.75" customHeight="1"/>
     <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="B109" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109" s="14" t="str">
+        <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R109" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
     <row r="110" ht="15.75" customHeight="1"/>
     <row r="111" ht="15.75" customHeight="1"/>
     <row r="112" ht="15.75" customHeight="1"/>
@@ -4253,6 +4522,14 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="16">
   <si>
     <t>Jamie Jenkins</t>
   </si>
@@ -3398,103 +3398,100 @@
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="12" t="s">
-        <v>6</v>
+      <c r="A69" s="8" t="s">
+        <v>5</v>
       </c>
       <c r="B69" s="14">
-        <f t="shared" ref="B69:Y69" si="14">AVERAGE(B62,B54,B46,B38,B30,B22,B14,B6)</f>
-        <v>0.50445</v>
+        <f t="shared" ref="B69:R69" si="14">average(B53,B45,B37,B29,B21,B13,B5)</f>
+        <v>0.3444333333</v>
       </c>
       <c r="C69" s="14">
         <f t="shared" si="14"/>
-        <v>0.366525</v>
+        <v>0.309525</v>
       </c>
       <c r="D69" s="14">
         <f t="shared" si="14"/>
-        <v>0.30455</v>
+        <v>0.42125</v>
       </c>
       <c r="E69" s="14">
         <f t="shared" si="14"/>
-        <v>0.38494</v>
+        <v>0.42478</v>
       </c>
       <c r="F69" s="14">
         <f t="shared" si="14"/>
-        <v>0.40984</v>
+        <v>0.40488</v>
       </c>
       <c r="G69" s="14">
         <f t="shared" si="14"/>
-        <v>0.4393</v>
+        <v>0.45414</v>
       </c>
       <c r="H69" s="14">
         <f t="shared" si="14"/>
-        <v>0.42082</v>
+        <v>0.40556</v>
       </c>
       <c r="I69" s="14">
         <f t="shared" si="14"/>
-        <v>0.4131</v>
+        <v>0.31688</v>
       </c>
       <c r="J69" s="14">
         <f t="shared" si="14"/>
-        <v>0.3999</v>
+        <v>0.41248</v>
       </c>
       <c r="K69" s="14">
         <f t="shared" si="14"/>
-        <v>0.38592</v>
+        <v>0.29162</v>
       </c>
       <c r="L69" s="14">
         <f t="shared" si="14"/>
-        <v>0.33754</v>
+        <v>0.35694</v>
       </c>
       <c r="M69" s="14">
         <f t="shared" si="14"/>
-        <v>0.34014</v>
+        <v>0.3687333333</v>
       </c>
       <c r="N69" s="14">
         <f t="shared" si="14"/>
-        <v>0.30044</v>
+        <v>0.26642</v>
       </c>
       <c r="O69" s="14">
         <f t="shared" si="14"/>
-        <v>0.30184</v>
+        <v>0.2291666667</v>
       </c>
       <c r="P69" s="14">
         <f t="shared" si="14"/>
-        <v>0.2368833333</v>
+        <v>0.3634</v>
       </c>
       <c r="Q69" s="14">
         <f t="shared" si="14"/>
-        <v>0.3044714286</v>
+        <v>0.2847571429</v>
       </c>
       <c r="R69" s="14">
         <f t="shared" si="14"/>
-        <v>0.2830428571</v>
-      </c>
-      <c r="S69" s="4" t="str">
-        <f t="shared" si="14"/>
+        <v>0.15246</v>
+      </c>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4" t="str">
+        <f t="shared" ref="T69:Y69" si="15">AVERAGE(T62,T54,T46,T38,T30,T22,T14,T6)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T69" s="4" t="str">
-        <f t="shared" si="14"/>
+      <c r="U69" s="4" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U69" s="4" t="str">
-        <f t="shared" si="14"/>
+      <c r="V69" s="4" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V69" s="4" t="str">
-        <f t="shared" si="14"/>
+      <c r="W69" s="4" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W69" s="4" t="str">
-        <f t="shared" si="14"/>
+      <c r="X69" s="4" t="str">
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X69" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="Y69" s="4" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z69" s="4" t="str">
@@ -3502,7 +3499,79 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="14">
+        <f t="shared" ref="B70:R70" si="16">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <v>0.50445</v>
+      </c>
+      <c r="C70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.366525</v>
+      </c>
+      <c r="D70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.30455</v>
+      </c>
+      <c r="E70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.38494</v>
+      </c>
+      <c r="F70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.40984</v>
+      </c>
+      <c r="G70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.4393</v>
+      </c>
+      <c r="H70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.42082</v>
+      </c>
+      <c r="I70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.4131</v>
+      </c>
+      <c r="J70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.3999</v>
+      </c>
+      <c r="K70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.38592</v>
+      </c>
+      <c r="L70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.33754</v>
+      </c>
+      <c r="M70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.34014</v>
+      </c>
+      <c r="N70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.30044</v>
+      </c>
+      <c r="O70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.30184</v>
+      </c>
+      <c r="P70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.2368833333</v>
+      </c>
+      <c r="Q70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.3044714286</v>
+      </c>
+      <c r="R70" s="14">
+        <f t="shared" si="16"/>
+        <v>0.2830428571</v>
+      </c>
+    </row>
     <row r="71" ht="15.75" customHeight="1"/>
     <row r="72" ht="15.75" customHeight="1"/>
     <row r="73" ht="15.75" customHeight="1"/>
@@ -3566,67 +3635,67 @@
         <v>15</v>
       </c>
       <c r="C109" s="14" t="str">
-        <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
+        <f t="shared" ref="C109:R109" si="17">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R109" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="18">
   <si>
     <t>Jamie Jenkins</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>Contract Total Average</t>
+  </si>
+  <si>
+    <t>Monthly Closing Rate Average</t>
+  </si>
+  <si>
+    <t>Rolling 90-Day Closing Rate Average</t>
   </si>
   <si>
     <t>Closing Rate Monthly Average</t>
@@ -398,7 +404,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.88"/>
+    <col customWidth="1" min="1" max="1" width="28.63"/>
     <col customWidth="1" min="2" max="6" width="12.63"/>
   </cols>
   <sheetData>
@@ -3399,7 +3405,7 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B69" s="14">
         <f t="shared" ref="B69:R69" si="14">average(B53,B45,B37,B29,B21,B13,B5)</f>
@@ -3501,7 +3507,7 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="12" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B70" s="14">
         <f t="shared" ref="B70:R70" si="16">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
@@ -3632,7 +3638,7 @@
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1">
       <c r="B109" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C109" s="14" t="str">
         <f t="shared" ref="C109:R109" si="17">average(C79:C84)</f>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -76,7 +76,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -91,11 +91,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -136,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -144,9 +139,6 @@
       <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
@@ -156,7 +148,7 @@
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -167,21 +159,18 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -442,7 +431,7 @@
       <c r="K1" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="2">
         <v>45962.0</v>
       </c>
       <c r="M1" s="2">
@@ -484,306 +473,310 @@
       <c r="Y1" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>33624.74</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>49353.38</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>150019.57</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>35596.98</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <v>121861.65</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>217702.66</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>80860.65</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>56753.76</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>97057.61</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>117013.22</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>39130.08</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <v>24475.43</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="4">
         <v>50427.08</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="4">
         <v>215081.52</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="4">
         <v>378650.28</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="Z2" s="6">
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="Z2" s="5">
         <f t="shared" ref="Z2:Z3" si="1">sum(N2:Y2)</f>
         <v>644158.88</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>2.0</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>2.0</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>5.0</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>2.0</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>9.0</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>12.0</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>5.0</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>4.0</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>5.0</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="6">
         <v>7.0</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="6">
         <v>7.0</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>3.0</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="6">
         <v>7.0</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="6">
         <v>13.0</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3" s="6">
         <v>24.0</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="Z3" s="4">
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="Z3" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>16812.37</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>24676.69</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>30003.91</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>17798.49</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>13540.18</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>18141.89</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>16172.13</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>14188.44</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>19411.52</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>16716.17</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>5590.01</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>8158.48</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="4">
         <v>7203.87</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="4">
         <v>16544.73</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="4">
         <v>15777.09</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="5">
         <f t="shared" ref="Z4:Z6" si="2">average(N4:Y4)</f>
         <v>13175.23</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>0.3333</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.3571</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>0.3333</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>0.375</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>0.52</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>0.3333</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>0.1111</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>0.28</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0.2353</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="8">
         <v>0.24</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <v>0.3333</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="9">
+      <c r="M5" s="9"/>
+      <c r="N5" s="8">
         <v>0.1818</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="8">
         <v>0.2308</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="8">
         <v>0.3529</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="8">
         <v>0.4167</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="8">
         <v>0.1923</v>
       </c>
-      <c r="S5" s="9"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="9">
+      <c r="S5" s="10">
+        <v>0.3333</v>
+      </c>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.2749</v>
+        <v>0.2846333333</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>0.5714</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>0.4167</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="11">
         <v>0.3182</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <v>0.3333</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="11">
         <v>0.3429</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="11">
         <v>0.4348</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="11">
         <v>0.4468</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="11">
         <v>0.3462</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="11">
         <v>0.2456</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="11">
         <v>0.2203</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="11">
         <v>0.2537</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="11">
         <v>0.2593</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="11">
         <v>0.2368</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="11">
         <v>0.2308</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="11">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="11">
         <v>0.3393</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="11">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14">
+      <c r="S6" s="12">
+        <v>0.2673</v>
+      </c>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2699</v>
+        <v>0.2694666667</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -822,7 +815,7 @@
       <c r="K9" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>45962.0</v>
       </c>
       <c r="M9" s="2">
@@ -864,330 +857,334 @@
       <c r="Y9" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z9" s="4" t="s">
+      <c r="Z9" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>26439.71</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>51542.87</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>75885.54</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>103291.98</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>153828.56</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>142652.92</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>63419.5</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>131500.17</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="4">
         <v>131200.28</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="4">
         <v>28825.49</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="4">
         <v>10448.87</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="4">
         <v>90672.39</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="4">
         <v>34294.16</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="4">
         <v>65730.26</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10" s="4">
         <v>349069.93</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R10" s="4">
         <v>118400.53</v>
       </c>
-      <c r="S10" s="5"/>
-      <c r="W10" s="15"/>
-      <c r="Z10" s="6">
+      <c r="S10" s="4"/>
+      <c r="W10" s="13"/>
+      <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>2.0</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>5.0</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>10.0</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>11.0</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>20.0</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>8.0</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>8.0</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>8.0</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <v>15.0</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="6">
         <v>9.0</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <v>3.0</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="6">
         <v>6.0</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="6">
         <v>11.0</v>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="6">
         <v>10.0</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="6">
         <v>30.0</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="6">
         <v>9.0</v>
       </c>
-      <c r="S11" s="7"/>
-      <c r="W11" s="15"/>
-      <c r="Z11" s="4">
+      <c r="S11" s="6"/>
+      <c r="W11" s="13"/>
+      <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>13219.86</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>10308.57</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>7588.55</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>9390.18</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>7691.43</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>17831.62</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>7927.44</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>16437.52</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="4">
         <v>8746.69</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="4">
         <v>3202.83</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="4">
         <v>3482.96</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="4">
         <v>15112.07</v>
       </c>
-      <c r="O12" s="5">
+      <c r="O12" s="4">
         <v>3117.65</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P12" s="4">
         <v>6573.03</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="4">
         <v>11635.66</v>
       </c>
-      <c r="R12" s="5">
+      <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="15"/>
-      <c r="Z12" s="6">
+      <c r="W12" s="13"/>
+      <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>0.5</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>0.2381</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>0.375</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <v>0.4231</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>0.4333</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>0.4231</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>0.25</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>0.2632</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>0.4211</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="8">
         <v>0.2973</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="8">
         <v>0.2727</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="8">
         <v>0.6429</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="8">
         <v>0.5385</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <v>0.2759</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="8">
         <v>0.3429</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="8">
         <v>0.3333</v>
       </c>
-      <c r="R13" s="11">
+      <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="13"/>
-      <c r="T13" s="16"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
+      <c r="S13" s="12">
+        <v>0.0526</v>
+      </c>
+      <c r="T13" s="14"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11">
         <v>0.5161</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="11">
         <v>0.3333</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="11">
         <v>0.34</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="11">
         <v>0.3521</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="11">
         <v>0.4125</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="11">
         <v>0.4321</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="11">
         <v>0.369</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="11">
         <v>0.3194</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="11">
         <v>0.2969</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="11">
         <v>0.32</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="11">
         <v>0.3205</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="11">
         <v>0.3571</v>
       </c>
-      <c r="O14" s="13">
+      <c r="O14" s="11">
         <v>0.449</v>
       </c>
-      <c r="P14" s="13">
+      <c r="P14" s="11">
         <v>0.4182</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="Q14" s="11">
         <v>0.3269</v>
       </c>
-      <c r="R14" s="13">
+      <c r="R14" s="11">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="13"/>
-      <c r="T14" s="16"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14">
+      <c r="S14" s="12">
+        <v>0.2044</v>
+      </c>
+      <c r="T14" s="14"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2711</v>
+        <v>0.23775</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="S15" s="14"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
@@ -1223,7 +1220,7 @@
       <c r="K17" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="2">
         <v>45962.0</v>
       </c>
       <c r="M17" s="2">
@@ -1265,281 +1262,283 @@
       <c r="Y17" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z17" s="4" t="s">
+      <c r="Z17" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>31222.74</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>1972.5</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>165667.1</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>200911.27</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
         <v>46590.51</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="4">
         <v>13253.11</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="4">
         <v>182255.48</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="4">
         <v>128036.34</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="4">
         <v>64847.69</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" s="4">
         <v>65950.63</v>
       </c>
-      <c r="O18" s="5">
+      <c r="O18" s="4">
         <v>14994.71</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P18" s="4">
         <v>76787.72</v>
       </c>
-      <c r="Q18" s="5">
+      <c r="Q18" s="4">
         <v>262251.4</v>
       </c>
-      <c r="R18" s="5">
+      <c r="R18" s="4">
         <v>147003.47</v>
       </c>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="Z18" s="6">
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="Z18" s="5">
         <f t="shared" ref="Z18:Z19" si="4">sum(N18:Y18)</f>
         <v>566987.93</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>1.0</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>1.0</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="6">
         <v>7.0</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>5.0</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="6">
         <v>8.0</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="6">
         <v>6.0</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <v>16.0</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="6">
         <v>8.0</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="6">
         <v>4.0</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="6">
         <v>4.0</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="6">
         <v>1.0</v>
       </c>
-      <c r="P19" s="7">
+      <c r="P19" s="6">
         <v>7.0</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="Q19" s="6">
         <v>22.0</v>
       </c>
-      <c r="R19" s="7">
+      <c r="R19" s="6">
         <v>7.0</v>
       </c>
-      <c r="S19" s="7"/>
-      <c r="Z19" s="4">
+      <c r="S19" s="6"/>
+      <c r="Z19" s="3">
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>31222.74</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>1972.5</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>23666.73</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>40182.25</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="4">
         <v>5823.81</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="4">
         <v>2208.85</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="4">
         <v>11390.97</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="4">
         <v>16004.54</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="4">
         <v>16211.92</v>
       </c>
-      <c r="N20" s="5">
+      <c r="N20" s="4">
         <v>16487.66</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="4">
         <v>14994.71</v>
       </c>
-      <c r="P20" s="5">
+      <c r="P20" s="4">
         <v>10969.67</v>
       </c>
-      <c r="Q20" s="5">
+      <c r="Q20" s="4">
         <v>11920.52</v>
       </c>
-      <c r="R20" s="5">
+      <c r="R20" s="4">
         <v>21000.5</v>
       </c>
-      <c r="Z20" s="6">
+      <c r="Z20" s="5">
         <f>average(N20:Y20)</f>
         <v>15074.612</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="9">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="8">
         <v>0.6667</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="8">
         <v>0.4286</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>0.4286</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>0.5</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="8">
         <v>0.5333</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="8">
         <v>0.381</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="8">
         <v>0.2963</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="8">
         <v>0.3571</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="8">
         <v>0.33</v>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="8">
         <v>0.2308</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="8">
         <v>0.1613</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="8">
         <v>0.3673</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="8">
         <v>0.22</v>
       </c>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="4"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="13">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11">
         <v>0.5</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="11">
         <v>0.5625</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="11">
         <v>0.5714</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="11">
         <v>0.4815</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="11">
         <v>0.4634</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="11">
         <v>0.4898</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="11">
         <v>0.463</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="11">
         <v>0.377</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="11">
         <v>0.3387</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="11">
         <v>0.3265</v>
       </c>
-      <c r="O22" s="13">
+      <c r="O22" s="11">
         <v>0.3056</v>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="11">
         <v>0.2075</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="Q22" s="11">
         <v>0.2615</v>
       </c>
-      <c r="R22" s="13">
+      <c r="R22" s="11">
         <v>0.232</v>
       </c>
-      <c r="S22" s="13"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14">
+      <c r="S22" s="12">
+        <v>0.181</v>
+      </c>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.232</v>
+        <v>0.2065</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1578,7 +1577,7 @@
       <c r="K25" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="2">
         <v>45962.0</v>
       </c>
       <c r="M25" s="2">
@@ -1620,310 +1619,314 @@
       <c r="Y25" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z25" s="4" t="s">
+      <c r="Z25" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>18650.58</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>30930.58</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>10220.61</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>40940.34</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>31725.85</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>59653.44</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="4">
         <v>52341.19</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="4">
         <v>43968.35</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="4">
         <v>55035.51</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="4">
         <v>30872.18</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="4">
         <v>5421.62</v>
       </c>
-      <c r="N26" s="5">
+      <c r="N26" s="4">
         <v>9080.08</v>
       </c>
-      <c r="O26" s="5">
+      <c r="O26" s="4">
         <v>5713.65</v>
       </c>
-      <c r="P26" s="5">
+      <c r="P26" s="4">
         <v>55012.85</v>
       </c>
-      <c r="Q26" s="5">
+      <c r="Q26" s="4">
         <v>13845.3</v>
       </c>
-      <c r="R26" s="5">
+      <c r="R26" s="4">
         <v>88880.21</v>
       </c>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="Z26" s="6">
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="Z26" s="5">
         <f t="shared" ref="Z26:Z27" si="5">sum(N26:Y26)</f>
         <v>172532.09</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>1.0</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>5.0</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="6">
         <v>2.0</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>3.0</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="6">
         <v>13.0</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>13.0</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="6">
         <v>10.0</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="6">
         <v>13.0</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="6">
         <v>16.0</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="6">
         <v>6.0</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="6">
         <v>2.0</v>
       </c>
-      <c r="N27" s="7">
+      <c r="N27" s="6">
         <v>7.0</v>
       </c>
-      <c r="O27" s="7">
+      <c r="O27" s="6">
         <v>2.0</v>
       </c>
-      <c r="P27" s="7">
+      <c r="P27" s="6">
         <v>14.0</v>
       </c>
-      <c r="Q27" s="7">
+      <c r="Q27" s="6">
         <v>12.0</v>
       </c>
-      <c r="R27" s="7">
+      <c r="R27" s="6">
         <v>10.0</v>
       </c>
-      <c r="S27" s="7"/>
-      <c r="W27" s="15"/>
-      <c r="Z27" s="4">
+      <c r="S27" s="6"/>
+      <c r="W27" s="13"/>
+      <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>18650.58</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>6186.12</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>5110.3</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>13646.78</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>2440.45</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>4588.73</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="4">
         <v>5234.12</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="4">
         <v>3382.18</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="4">
         <v>3439.72</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L28" s="4">
         <v>5145.36</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="4">
         <v>2710.81</v>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" s="4">
         <v>1297.15</v>
       </c>
-      <c r="O28" s="5">
+      <c r="O28" s="4">
         <v>2856.82</v>
       </c>
-      <c r="P28" s="5">
+      <c r="P28" s="4">
         <v>3929.49</v>
       </c>
-      <c r="Q28" s="5">
+      <c r="Q28" s="4">
         <v>1153.77</v>
       </c>
-      <c r="R28" s="5">
+      <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="16"/>
-      <c r="W28" s="15"/>
-      <c r="Z28" s="6">
+      <c r="T28" s="14"/>
+      <c r="W28" s="13"/>
+      <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="9">
+      <c r="B29" s="9"/>
+      <c r="C29" s="8">
         <v>0.2143</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>0.5556</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <v>0.25</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <v>0.2632</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="8">
         <v>0.3714</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <v>0.6667</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="8">
         <v>0.2222</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="8">
         <v>0.4</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="8">
         <v>0.3636</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="8">
         <v>0.1852</v>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="8">
         <v>0.1333</v>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="8">
         <v>0.2381</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="8">
         <v>0.2308</v>
       </c>
-      <c r="P29" s="11">
+      <c r="P29" s="8">
         <v>0.4</v>
       </c>
-      <c r="Q29" s="11">
+      <c r="Q29" s="8">
         <v>0.2759</v>
       </c>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="4"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="12">
+        <v>0.0769</v>
+      </c>
+      <c r="T29" s="16"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="13">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11">
         <v>0.1333</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="11">
         <v>0.1667</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0.3514</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="11">
         <v>0.375</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="11">
         <v>0.3778</v>
       </c>
-      <c r="H30" s="13">
+      <c r="H30" s="11">
         <v>0.3226</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="11">
         <v>0.4359</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="11">
         <v>0.4286</v>
       </c>
-      <c r="K30" s="13">
+      <c r="K30" s="11">
         <v>0.4366</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L30" s="11">
         <v>0.3457</v>
       </c>
-      <c r="M30" s="13">
+      <c r="M30" s="11">
         <v>0.3222</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="11">
         <v>0.2568</v>
       </c>
-      <c r="O30" s="13">
+      <c r="O30" s="11">
         <v>0.1905</v>
       </c>
-      <c r="P30" s="13">
+      <c r="P30" s="11">
         <v>0.2281</v>
       </c>
-      <c r="Q30" s="13">
+      <c r="Q30" s="11">
         <v>0.3243</v>
       </c>
-      <c r="R30" s="13">
+      <c r="R30" s="11">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="13"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14">
+      <c r="S30" s="12">
+        <v>0.2759</v>
+      </c>
+      <c r="T30" s="16"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
+      <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.3297</v>
+        <v>0.3028</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -1962,7 +1965,7 @@
       <c r="K33" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="2">
         <v>45962.0</v>
       </c>
       <c r="M33" s="2">
@@ -2004,313 +2007,317 @@
       <c r="Y33" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z33" s="4" t="s">
+      <c r="Z33" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>55872.76</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="4">
         <v>2336.73</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="4">
         <v>33592.39</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="4">
         <v>21413.67</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="4">
         <v>186331.34</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <v>163356.3</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="4">
         <v>93899.31</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="4">
         <v>95663.96</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="4">
         <v>52111.35</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34" s="4">
         <v>205694.01</v>
       </c>
-      <c r="L34" s="5">
+      <c r="L34" s="4">
         <v>38500.4</v>
       </c>
-      <c r="M34" s="5">
+      <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="15"/>
-      <c r="O34" s="5">
+      <c r="N34" s="13"/>
+      <c r="O34" s="4">
         <v>8067.86</v>
       </c>
-      <c r="P34" s="5">
+      <c r="P34" s="4">
         <v>108802.59</v>
       </c>
-      <c r="Q34" s="5">
+      <c r="Q34" s="4">
         <v>149911.53</v>
       </c>
-      <c r="R34" s="5">
+      <c r="R34" s="4">
         <v>158044.97</v>
       </c>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-      <c r="Z34" s="6">
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="Z34" s="5">
         <f t="shared" ref="Z34:Z35" si="6">sum(N34:Y34)</f>
         <v>424826.95</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="6">
         <v>2.0</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>2.0</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="6">
         <v>1.0</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6">
         <v>8.0</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="6">
         <v>13.0</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="6">
         <v>8.0</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="6">
         <v>10.0</v>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="6">
         <v>2.0</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="6">
         <v>4.0</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="6">
         <v>17.0</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="6">
         <v>5.0</v>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="6">
         <v>8.0</v>
       </c>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <v>1.0</v>
       </c>
-      <c r="P35" s="7">
+      <c r="P35" s="6">
         <v>9.0</v>
       </c>
-      <c r="Q35" s="7">
+      <c r="Q35" s="6">
         <v>16.0</v>
       </c>
-      <c r="R35" s="7">
+      <c r="R35" s="6">
         <v>9.0</v>
       </c>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="Z35" s="4">
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
+      <c r="Z35" s="3">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>27936.38</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="4">
         <v>1168.36</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="4">
         <v>33592.39</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <v>2676.71</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="4">
         <v>14333.18</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <v>20419.54</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="4">
         <v>9389.93</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="4">
         <v>47831.98</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="4">
         <v>13027.84</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K36" s="4">
         <v>12099.65</v>
       </c>
-      <c r="L36" s="5">
+      <c r="L36" s="4">
         <v>7700.08</v>
       </c>
-      <c r="M36" s="5">
+      <c r="M36" s="4">
         <v>1857.67</v>
       </c>
-      <c r="O36" s="5">
+      <c r="O36" s="4">
         <v>8067.86</v>
       </c>
-      <c r="P36" s="5">
+      <c r="P36" s="4">
         <v>12089.18</v>
       </c>
-      <c r="Q36" s="5">
+      <c r="Q36" s="4">
         <v>9369.47</v>
       </c>
-      <c r="R36" s="5">
+      <c r="R36" s="4">
         <v>17560.55</v>
       </c>
-      <c r="Z36" s="6">
+      <c r="Z36" s="5">
         <f>average(N36:Y36)</f>
         <v>11771.765</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="8">
         <v>0.2</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="8">
         <v>0.4286</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>0.4211</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="8">
         <v>0.4091</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="8">
         <v>0.3793</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="8">
         <v>0.7143</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="8">
         <v>0.5</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="8">
         <v>0.2857</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="8">
         <v>0.625</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="8">
         <v>0.2609</v>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="8">
         <v>0.6364</v>
       </c>
-      <c r="M37" s="10"/>
-      <c r="N37" s="9">
+      <c r="M37" s="9"/>
+      <c r="N37" s="8">
         <v>0.1429</v>
       </c>
-      <c r="O37" s="11">
+      <c r="O37" s="8">
         <v>0.3333</v>
       </c>
-      <c r="P37" s="11">
+      <c r="P37" s="8">
         <v>0.3333</v>
       </c>
-      <c r="Q37" s="9">
+      <c r="Q37" s="8">
         <v>0.303</v>
       </c>
-      <c r="R37" s="13">
+      <c r="R37" s="11">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="13"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="4"/>
+      <c r="S37" s="12">
+        <v>0.3333</v>
+      </c>
+      <c r="T37" s="11"/>
+      <c r="U37" s="11"/>
+      <c r="V37" s="11"/>
+      <c r="W37" s="11"/>
+      <c r="X37" s="11"/>
+      <c r="Y37" s="11"/>
+      <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="11">
         <v>0.4375</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="11">
         <v>0.4</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="11">
         <v>0.4</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <v>0.4</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="11">
         <v>0.4167</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="11">
         <v>0.4</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="11">
         <v>0.4211</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="11">
         <v>0.451</v>
       </c>
-      <c r="J38" s="13">
+      <c r="J38" s="11">
         <v>0.5161</v>
       </c>
-      <c r="K38" s="13">
+      <c r="K38" s="11">
         <v>0.5128</v>
       </c>
-      <c r="L38" s="13">
+      <c r="L38" s="11">
         <v>0.3913</v>
       </c>
-      <c r="M38" s="13">
+      <c r="M38" s="11">
         <v>0.46</v>
       </c>
-      <c r="N38" s="13">
+      <c r="N38" s="11">
         <v>0.325</v>
       </c>
-      <c r="O38" s="13">
+      <c r="O38" s="11">
         <v>0.3333</v>
       </c>
-      <c r="P38" s="13">
+      <c r="P38" s="11">
         <v>0.2564</v>
       </c>
-      <c r="Q38" s="13">
+      <c r="Q38" s="11">
         <v>0.3238</v>
       </c>
-      <c r="R38" s="13">
+      <c r="R38" s="11">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="13"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-      <c r="X38" s="14"/>
-      <c r="Y38" s="14"/>
-      <c r="Z38" s="14">
+      <c r="S38" s="12">
+        <v>0.2024</v>
+      </c>
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="11"/>
+      <c r="W38" s="11"/>
+      <c r="X38" s="11"/>
+      <c r="Y38" s="11"/>
+      <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2432</v>
+        <v>0.2228</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2349,7 +2356,7 @@
       <c r="K41" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L41" s="4" t="s">
+      <c r="L41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="M41" s="2">
@@ -2391,149 +2398,153 @@
       <c r="Y41" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z41" s="4" t="s">
+      <c r="Z41" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P42" s="5">
+      <c r="P42" s="4">
         <v>9374.61</v>
       </c>
-      <c r="Q42" s="5">
+      <c r="Q42" s="4">
         <v>123258.92</v>
       </c>
-      <c r="R42" s="5">
+      <c r="R42" s="4">
         <v>152476.32</v>
       </c>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="Z42" s="6">
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="Z42" s="5">
         <f t="shared" ref="Z42:Z43" si="7">sum(N42:Y42)</f>
         <v>285109.85</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="7">
+      <c r="P43" s="6">
         <v>5.0</v>
       </c>
-      <c r="Q43" s="7">
+      <c r="Q43" s="6">
         <v>12.0</v>
       </c>
-      <c r="R43" s="7">
+      <c r="R43" s="6">
         <v>12.0</v>
       </c>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="Z43" s="4">
+      <c r="S43" s="6"/>
+      <c r="T43" s="6"/>
+      <c r="Z43" s="3">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="15"/>
-      <c r="P44" s="5">
+      <c r="L44" s="13"/>
+      <c r="P44" s="4">
         <v>1874.92</v>
       </c>
-      <c r="Q44" s="5">
+      <c r="Q44" s="4">
         <v>10271.58</v>
       </c>
-      <c r="R44" s="5">
+      <c r="R44" s="4">
         <v>12706.36</v>
       </c>
-      <c r="Z44" s="6">
+      <c r="Z44" s="5">
         <f>average(N44:Y44)</f>
         <v>8284.286667</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="9">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="8">
         <v>0.1429</v>
       </c>
-      <c r="P45" s="11">
+      <c r="P45" s="8">
         <v>0.3696</v>
       </c>
-      <c r="Q45" s="11">
+      <c r="Q45" s="8">
         <v>0.2222</v>
       </c>
-      <c r="R45" s="11">
+      <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="13"/>
-      <c r="T45" s="14"/>
-      <c r="U45" s="14"/>
-      <c r="V45" s="14"/>
-      <c r="W45" s="14"/>
-      <c r="X45" s="14"/>
-      <c r="Y45" s="14"/>
-      <c r="Z45" s="14"/>
+      <c r="S45" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="T45" s="11"/>
+      <c r="U45" s="11"/>
+      <c r="V45" s="11"/>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="Z45" s="11"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
-      <c r="L46" s="13"/>
-      <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="13">
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11">
         <v>0.1111</v>
       </c>
-      <c r="Q46" s="13">
+      <c r="Q46" s="11">
         <v>0.2828</v>
       </c>
-      <c r="R46" s="13">
+      <c r="R46" s="11">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="13"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="14"/>
-      <c r="W46" s="14"/>
-      <c r="X46" s="14"/>
-      <c r="Y46" s="14"/>
-      <c r="Z46" s="14">
+      <c r="S46" s="12">
+        <v>0.2157</v>
+      </c>
+      <c r="T46" s="11"/>
+      <c r="U46" s="11"/>
+      <c r="V46" s="11"/>
+      <c r="W46" s="11"/>
+      <c r="X46" s="11"/>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2667</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
@@ -2570,7 +2581,7 @@
       <c r="K49" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L49" s="4" t="s">
+      <c r="L49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="M49" s="2">
@@ -2612,139 +2623,143 @@
       <c r="Y49" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z49" s="4" t="s">
+      <c r="Z49" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P50" s="5">
+      <c r="P50" s="4">
         <v>816.62</v>
       </c>
-      <c r="Q50" s="5">
+      <c r="Q50" s="4">
         <v>124770.34</v>
       </c>
-      <c r="R50" s="5">
+      <c r="R50" s="4">
         <v>78978.19</v>
       </c>
-      <c r="S50" s="5"/>
-      <c r="T50" s="5"/>
-      <c r="Z50" s="6">
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="Z50" s="5">
         <f t="shared" ref="Z50:Z51" si="8">sum(N50:Y50)</f>
         <v>204565.15</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P51" s="7">
+      <c r="P51" s="6">
         <v>2.0</v>
       </c>
-      <c r="Q51" s="7">
+      <c r="Q51" s="6">
         <v>13.0</v>
       </c>
-      <c r="R51" s="7">
+      <c r="R51" s="6">
         <v>15.0</v>
       </c>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
-      <c r="Z51" s="4">
+      <c r="S51" s="6"/>
+      <c r="T51" s="6"/>
+      <c r="Z51" s="3">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="5">
+      <c r="P52" s="4">
         <v>408.31</v>
       </c>
-      <c r="Q52" s="5">
+      <c r="Q52" s="4">
         <v>9597.72</v>
       </c>
-      <c r="R52" s="5">
+      <c r="R52" s="4">
         <v>5265.21</v>
       </c>
-      <c r="Z52" s="6">
+      <c r="Z52" s="5">
         <f>average(N52:Y52)</f>
         <v>5090.413333</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="11">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="8">
         <v>0.3778</v>
       </c>
-      <c r="Q53" s="11">
+      <c r="Q53" s="8">
         <v>0.2222</v>
       </c>
-      <c r="R53" s="11">
+      <c r="R53" s="8">
         <v>0.2857</v>
       </c>
-      <c r="S53" s="13"/>
-      <c r="T53" s="14"/>
-      <c r="U53" s="14"/>
-      <c r="V53" s="14"/>
-      <c r="W53" s="14"/>
-      <c r="X53" s="14"/>
-      <c r="Y53" s="14"/>
-      <c r="Z53" s="14"/>
+      <c r="S53" s="12">
+        <v>0.0333</v>
+      </c>
+      <c r="T53" s="11"/>
+      <c r="U53" s="11"/>
+      <c r="V53" s="11"/>
+      <c r="W53" s="11"/>
+      <c r="X53" s="11"/>
+      <c r="Y53" s="11"/>
+      <c r="Z53" s="11"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="13"/>
-      <c r="Q54" s="13">
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11">
         <v>0.2727</v>
       </c>
-      <c r="R54" s="13">
+      <c r="R54" s="11">
         <v>0.296</v>
       </c>
-      <c r="S54" s="13"/>
-      <c r="T54" s="14"/>
-      <c r="U54" s="14"/>
-      <c r="V54" s="14"/>
-      <c r="W54" s="14"/>
-      <c r="X54" s="14"/>
-      <c r="Y54" s="14"/>
-      <c r="Z54" s="14">
+      <c r="S54" s="12">
+        <v>0.2222</v>
+      </c>
+      <c r="T54" s="11"/>
+      <c r="U54" s="11"/>
+      <c r="V54" s="11"/>
+      <c r="W54" s="11"/>
+      <c r="X54" s="11"/>
+      <c r="Y54" s="11"/>
+      <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.296</v>
+        <v>0.2591</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -2761,7 +2776,7 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
-      <c r="L57" s="4"/>
+      <c r="L57" s="3"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -2775,109 +2790,109 @@
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
-      <c r="Z57" s="4"/>
+      <c r="Z57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="4"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-      <c r="L58" s="15"/>
-      <c r="M58" s="5"/>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
-      <c r="R58" s="5"/>
-      <c r="S58" s="5"/>
-      <c r="T58" s="5"/>
-      <c r="Z58" s="6"/>
+      <c r="A58" s="3"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="Z58" s="5"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="4"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="M59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="7"/>
-      <c r="S59" s="7"/>
-      <c r="T59" s="7"/>
-      <c r="Z59" s="4"/>
+      <c r="A59" s="3"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6"/>
+      <c r="T59" s="6"/>
+      <c r="Z59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="4"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="M60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="5"/>
-      <c r="Z60" s="6"/>
+      <c r="A60" s="3"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="Z60" s="5"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="8"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="13"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="13"/>
-      <c r="P61" s="13"/>
-      <c r="Q61" s="13"/>
-      <c r="R61" s="13"/>
-      <c r="S61" s="14"/>
-      <c r="T61" s="14"/>
-      <c r="U61" s="14"/>
-      <c r="V61" s="14"/>
-      <c r="W61" s="14"/>
-      <c r="X61" s="14"/>
-      <c r="Y61" s="14"/>
-      <c r="Z61" s="4"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="11"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="11"/>
+      <c r="Q61" s="11"/>
+      <c r="R61" s="11"/>
+      <c r="S61" s="11"/>
+      <c r="T61" s="11"/>
+      <c r="U61" s="11"/>
+      <c r="V61" s="11"/>
+      <c r="W61" s="11"/>
+      <c r="X61" s="11"/>
+      <c r="Y61" s="11"/>
+      <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
-      <c r="Q62" s="13"/>
-      <c r="R62" s="13"/>
-      <c r="S62" s="14"/>
-      <c r="T62" s="14"/>
-      <c r="U62" s="14"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="14"/>
-      <c r="X62" s="14"/>
-      <c r="Y62" s="14"/>
-      <c r="Z62" s="4"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11"/>
+      <c r="O62" s="11"/>
+      <c r="P62" s="11"/>
+      <c r="Q62" s="11"/>
+      <c r="R62" s="11"/>
+      <c r="S62" s="11"/>
+      <c r="T62" s="11"/>
+      <c r="U62" s="11"/>
+      <c r="V62" s="11"/>
+      <c r="W62" s="11"/>
+      <c r="X62" s="11"/>
+      <c r="Y62" s="11"/>
+      <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="B63" s="2"/>
@@ -2890,7 +2905,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="4"/>
+      <c r="L63" s="3"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -2904,7 +2919,7 @@
       <c r="W63" s="2"/>
       <c r="X63" s="2"/>
       <c r="Y63" s="2"/>
-      <c r="Z63" s="4"/>
+      <c r="Z63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="2">
@@ -2937,7 +2952,7 @@
       <c r="K64" s="2">
         <v>45931.0</v>
       </c>
-      <c r="L64" s="4" t="s">
+      <c r="L64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="M64" s="2">
@@ -2979,601 +2994,601 @@
       <c r="Y64" s="2">
         <v>46357.0</v>
       </c>
-      <c r="Z64" s="4" t="s">
+      <c r="Z64" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="5">
         <f t="shared" ref="B65:Y65" si="9">sum(B58,B50,B42,B34,B26,B18,B10,B2)</f>
         <v>89497.5</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="5">
         <f t="shared" si="9"/>
         <v>96780.4</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="5">
         <f t="shared" si="9"/>
         <v>266085.41</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E65" s="5">
         <f t="shared" si="9"/>
         <v>174339.54</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="5">
         <f t="shared" si="9"/>
         <v>454397.81</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="5">
         <f t="shared" si="9"/>
         <v>732280.47</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H65" s="5">
         <f t="shared" si="9"/>
         <v>577977.59</v>
       </c>
-      <c r="I65" s="6">
+      <c r="I65" s="5">
         <f t="shared" si="9"/>
         <v>314768.92</v>
       </c>
-      <c r="J65" s="6">
+      <c r="J65" s="5">
         <f t="shared" si="9"/>
         <v>337890.59</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <f t="shared" si="9"/>
         <v>691198.5</v>
       </c>
-      <c r="L65" s="6">
+      <c r="L65" s="5">
         <f t="shared" si="9"/>
         <v>265364.49</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="5">
         <f t="shared" si="9"/>
         <v>120054.95</v>
       </c>
-      <c r="N65" s="6">
+      <c r="N65" s="5">
         <f t="shared" si="9"/>
         <v>165703.1</v>
       </c>
-      <c r="O65" s="6">
+      <c r="O65" s="5">
         <f t="shared" si="9"/>
         <v>63070.38</v>
       </c>
-      <c r="P65" s="6">
+      <c r="P65" s="5">
         <f t="shared" si="9"/>
         <v>366951.73</v>
       </c>
-      <c r="Q65" s="6">
+      <c r="Q65" s="5">
         <f t="shared" si="9"/>
         <v>1238188.94</v>
       </c>
-      <c r="R65" s="6">
+      <c r="R65" s="5">
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="20">
+      <c r="S65" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T65" s="20">
+      <c r="T65" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U65" s="4">
+      <c r="U65" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="V65" s="4">
+      <c r="V65" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W65" s="4">
+      <c r="W65" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X65" s="4">
+      <c r="X65" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y65" s="4">
+      <c r="Y65" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z65" s="6">
+      <c r="Z65" s="5">
         <f>sum(N65:Y65)</f>
         <v>2956348.12</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66" s="5">
         <f t="shared" ref="B66:Z66" si="10">average(B58,B50,B42,B34,B26,B18,B10,B2)</f>
         <v>44748.75</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="5">
         <f t="shared" si="10"/>
         <v>24195.1</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="5">
         <f t="shared" si="10"/>
         <v>66521.3525</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="5">
         <f t="shared" si="10"/>
         <v>34867.908</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="5">
         <f t="shared" si="10"/>
         <v>90879.562</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="5">
         <f t="shared" si="10"/>
         <v>146456.094</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="5">
         <f t="shared" si="10"/>
         <v>115595.518</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I66" s="5">
         <f t="shared" si="10"/>
         <v>62953.784</v>
       </c>
-      <c r="J66" s="6">
+      <c r="J66" s="5">
         <f t="shared" si="10"/>
         <v>67578.118</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <f t="shared" si="10"/>
         <v>138239.7</v>
       </c>
-      <c r="L66" s="6">
+      <c r="L66" s="5">
         <f t="shared" si="10"/>
         <v>53072.898</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="5">
         <f t="shared" si="10"/>
         <v>24010.99</v>
       </c>
-      <c r="N66" s="6">
+      <c r="N66" s="5">
         <f t="shared" si="10"/>
         <v>55234.36667</v>
       </c>
-      <c r="O66" s="6">
+      <c r="O66" s="5">
         <f t="shared" si="10"/>
         <v>15767.595</v>
       </c>
-      <c r="P66" s="6">
+      <c r="P66" s="5">
         <f t="shared" si="10"/>
         <v>52421.67571</v>
       </c>
-      <c r="Q66" s="6">
+      <c r="Q66" s="5">
         <f t="shared" si="10"/>
         <v>176884.1343</v>
       </c>
-      <c r="R66" s="6">
+      <c r="R66" s="5">
         <f t="shared" si="10"/>
         <v>160347.71</v>
       </c>
-      <c r="S66" s="4" t="str">
+      <c r="S66" s="3" t="str">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T66" s="4" t="str">
+      <c r="T66" s="3" t="str">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U66" s="4" t="str">
+      <c r="U66" s="3" t="str">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V66" s="4" t="str">
+      <c r="V66" s="3" t="str">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W66" s="4" t="str">
+      <c r="W66" s="3" t="str">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X66" s="4" t="str">
+      <c r="X66" s="3" t="str">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y66" s="4" t="str">
+      <c r="Y66" s="3" t="str">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z66" s="6">
+      <c r="Z66" s="5">
         <f t="shared" si="10"/>
         <v>422335.4457</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="21">
+      <c r="B67" s="19">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="21">
+      <c r="C67" s="19">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="21">
+      <c r="D67" s="19">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="21">
+      <c r="E67" s="19">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="19">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="21">
+      <c r="G67" s="19">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="21">
+      <c r="H67" s="19">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="21">
+      <c r="I67" s="19">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="21">
+      <c r="J67" s="19">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="21">
+      <c r="K67" s="19">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="21">
+      <c r="L67" s="19">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="21">
+      <c r="M67" s="19">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="21">
+      <c r="N67" s="19">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="21">
+      <c r="O67" s="19">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="21">
+      <c r="P67" s="19">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="21">
+      <c r="Q67" s="19">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="21">
+      <c r="R67" s="19">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
-      <c r="S67" s="4">
+      <c r="S67" s="3">
         <f t="shared" ref="S67:Y67" si="12">sum(S59,S51,S43,S35,S27,S19,S11,S3)</f>
         <v>0</v>
       </c>
-      <c r="T67" s="4">
+      <c r="T67" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U67" s="4">
+      <c r="U67" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="V67" s="4">
+      <c r="V67" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="W67" s="4">
+      <c r="W67" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X67" s="4">
+      <c r="X67" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Y67" s="4">
+      <c r="Y67" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z67" s="21">
+      <c r="Z67" s="19">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B68" s="6">
+      <c r="B68" s="5">
         <f t="shared" ref="B68:Y68" si="13">AVERAGE(B60,B52,B44,B36,B28,B20,B12,B4)</f>
         <v>22374.375</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="5">
         <f t="shared" si="13"/>
         <v>14428.8725</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="5">
         <f t="shared" si="13"/>
         <v>20022.7475</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68" s="5">
         <f t="shared" si="13"/>
         <v>12879.358</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="5">
         <f t="shared" si="13"/>
         <v>10576.564</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G68" s="5">
         <f t="shared" si="13"/>
         <v>14472.008</v>
       </c>
-      <c r="H68" s="6">
+      <c r="H68" s="5">
         <f t="shared" si="13"/>
         <v>17632.932</v>
       </c>
-      <c r="I68" s="6">
+      <c r="I68" s="5">
         <f t="shared" si="13"/>
         <v>16201.158</v>
       </c>
-      <c r="J68" s="6">
+      <c r="J68" s="5">
         <f t="shared" si="13"/>
         <v>10893.582</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="5">
         <f t="shared" si="13"/>
         <v>10478.64</v>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="5">
         <f t="shared" si="13"/>
         <v>7528.564</v>
       </c>
-      <c r="M68" s="6">
+      <c r="M68" s="5">
         <f t="shared" si="13"/>
         <v>6484.368</v>
       </c>
-      <c r="N68" s="6">
+      <c r="N68" s="5">
         <f t="shared" si="13"/>
         <v>10965.62667</v>
       </c>
-      <c r="O68" s="6">
+      <c r="O68" s="5">
         <f t="shared" si="13"/>
         <v>7259.26</v>
       </c>
-      <c r="P68" s="6">
+      <c r="P68" s="5">
         <f t="shared" si="13"/>
         <v>6149.781429</v>
       </c>
-      <c r="Q68" s="6">
+      <c r="Q68" s="5">
         <f t="shared" si="13"/>
         <v>10070.49286</v>
       </c>
-      <c r="R68" s="6">
+      <c r="R68" s="5">
         <f t="shared" si="13"/>
         <v>13479.04857</v>
       </c>
-      <c r="S68" s="4" t="str">
+      <c r="S68" s="3" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T68" s="4" t="str">
+      <c r="T68" s="3" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U68" s="4" t="str">
+      <c r="U68" s="3" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V68" s="4" t="str">
+      <c r="V68" s="3" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W68" s="4" t="str">
+      <c r="W68" s="3" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X68" s="4" t="str">
+      <c r="X68" s="3" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y68" s="4" t="str">
+      <c r="Y68" s="3" t="str">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z68" s="6" t="str">
+      <c r="Z68" s="5" t="str">
         <f>average(N68:Y68)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B69" s="14">
+      <c r="B69" s="11">
         <f t="shared" ref="B69:R69" si="14">average(B53,B45,B37,B29,B21,B13,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C69" s="14">
+      <c r="C69" s="11">
         <f t="shared" si="14"/>
         <v>0.309525</v>
       </c>
-      <c r="D69" s="14">
+      <c r="D69" s="11">
         <f t="shared" si="14"/>
         <v>0.42125</v>
       </c>
-      <c r="E69" s="14">
+      <c r="E69" s="11">
         <f t="shared" si="14"/>
         <v>0.42478</v>
       </c>
-      <c r="F69" s="14">
+      <c r="F69" s="11">
         <f t="shared" si="14"/>
         <v>0.40488</v>
       </c>
-      <c r="G69" s="14">
+      <c r="G69" s="11">
         <f t="shared" si="14"/>
         <v>0.45414</v>
       </c>
-      <c r="H69" s="14">
+      <c r="H69" s="11">
         <f t="shared" si="14"/>
         <v>0.40556</v>
       </c>
-      <c r="I69" s="14">
+      <c r="I69" s="11">
         <f t="shared" si="14"/>
         <v>0.31688</v>
       </c>
-      <c r="J69" s="14">
+      <c r="J69" s="11">
         <f t="shared" si="14"/>
         <v>0.41248</v>
       </c>
-      <c r="K69" s="14">
+      <c r="K69" s="11">
         <f t="shared" si="14"/>
         <v>0.29162</v>
       </c>
-      <c r="L69" s="14">
+      <c r="L69" s="11">
         <f t="shared" si="14"/>
         <v>0.35694</v>
       </c>
-      <c r="M69" s="14">
+      <c r="M69" s="11">
         <f t="shared" si="14"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N69" s="14">
+      <c r="N69" s="11">
         <f t="shared" si="14"/>
         <v>0.26642</v>
       </c>
-      <c r="O69" s="14">
+      <c r="O69" s="11">
         <f t="shared" si="14"/>
         <v>0.2291666667</v>
       </c>
-      <c r="P69" s="14">
+      <c r="P69" s="11">
         <f t="shared" si="14"/>
         <v>0.3634</v>
       </c>
-      <c r="Q69" s="14">
+      <c r="Q69" s="11">
         <f t="shared" si="14"/>
         <v>0.2847571429</v>
       </c>
-      <c r="R69" s="14">
+      <c r="R69" s="11">
         <f t="shared" si="14"/>
         <v>0.15246</v>
       </c>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4" t="str">
+      <c r="S69" s="3"/>
+      <c r="T69" s="3" t="str">
         <f t="shared" ref="T69:Y69" si="15">AVERAGE(T62,T54,T46,T38,T30,T22,T14,T6)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U69" s="4" t="str">
+      <c r="U69" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V69" s="4" t="str">
+      <c r="V69" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W69" s="4" t="str">
+      <c r="W69" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X69" s="4" t="str">
+      <c r="X69" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y69" s="4" t="str">
+      <c r="Y69" s="3" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z69" s="4" t="str">
+      <c r="Z69" s="3" t="str">
         <f>average(R69:Y69)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="14">
+      <c r="B70" s="11">
         <f t="shared" ref="B70:R70" si="16">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
-      <c r="C70" s="14">
+      <c r="C70" s="11">
         <f t="shared" si="16"/>
         <v>0.366525</v>
       </c>
-      <c r="D70" s="14">
+      <c r="D70" s="11">
         <f t="shared" si="16"/>
         <v>0.30455</v>
       </c>
-      <c r="E70" s="14">
+      <c r="E70" s="11">
         <f t="shared" si="16"/>
         <v>0.38494</v>
       </c>
-      <c r="F70" s="14">
+      <c r="F70" s="11">
         <f t="shared" si="16"/>
         <v>0.40984</v>
       </c>
-      <c r="G70" s="14">
+      <c r="G70" s="11">
         <f t="shared" si="16"/>
         <v>0.4393</v>
       </c>
-      <c r="H70" s="14">
+      <c r="H70" s="11">
         <f t="shared" si="16"/>
         <v>0.42082</v>
       </c>
-      <c r="I70" s="14">
+      <c r="I70" s="11">
         <f t="shared" si="16"/>
         <v>0.4131</v>
       </c>
-      <c r="J70" s="14">
+      <c r="J70" s="11">
         <f t="shared" si="16"/>
         <v>0.3999</v>
       </c>
-      <c r="K70" s="14">
+      <c r="K70" s="11">
         <f t="shared" si="16"/>
         <v>0.38592</v>
       </c>
-      <c r="L70" s="14">
+      <c r="L70" s="11">
         <f t="shared" si="16"/>
         <v>0.33754</v>
       </c>
-      <c r="M70" s="14">
+      <c r="M70" s="11">
         <f t="shared" si="16"/>
         <v>0.34014</v>
       </c>
-      <c r="N70" s="14">
+      <c r="N70" s="11">
         <f t="shared" si="16"/>
         <v>0.30044</v>
       </c>
-      <c r="O70" s="14">
+      <c r="O70" s="11">
         <f t="shared" si="16"/>
         <v>0.30184</v>
       </c>
-      <c r="P70" s="14">
+      <c r="P70" s="11">
         <f t="shared" si="16"/>
         <v>0.2368833333</v>
       </c>
-      <c r="Q70" s="14">
+      <c r="Q70" s="11">
         <f t="shared" si="16"/>
         <v>0.3044714286</v>
       </c>
-      <c r="R70" s="14">
+      <c r="R70" s="11">
         <f t="shared" si="16"/>
         <v>0.2830428571</v>
       </c>
@@ -3588,30 +3603,30 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="1"/>
-      <c r="S79" s="14"/>
+      <c r="S79" s="11"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="1"/>
-      <c r="S80" s="14"/>
+      <c r="S80" s="11"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="1"/>
-      <c r="S81" s="14"/>
+      <c r="S81" s="11"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="1"/>
-      <c r="S82" s="14"/>
+      <c r="S82" s="11"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="1"/>
-      <c r="S83" s="14"/>
+      <c r="S83" s="11"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="1"/>
-      <c r="S84" s="14"/>
+      <c r="S84" s="11"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="S85" s="14"/>
+      <c r="S85" s="11"/>
     </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
@@ -3637,70 +3652,70 @@
     <row r="107" ht="15.75" customHeight="1"/>
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="14" t="str">
+      <c r="C109" s="11" t="str">
         <f t="shared" ref="C109:R109" si="17">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D109" s="14" t="str">
+      <c r="D109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E109" s="14" t="str">
+      <c r="E109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="14" t="str">
+      <c r="F109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G109" s="14" t="str">
+      <c r="G109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H109" s="14" t="str">
+      <c r="H109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="14" t="str">
+      <c r="I109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J109" s="14" t="str">
+      <c r="J109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K109" s="14" t="str">
+      <c r="K109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L109" s="14" t="str">
+      <c r="L109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M109" s="14" t="str">
+      <c r="M109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N109" s="14" t="str">
+      <c r="N109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O109" s="14" t="str">
+      <c r="O109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P109" s="14" t="str">
+      <c r="P109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q109" s="14" t="str">
+      <c r="Q109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R109" s="14" t="str">
+      <c r="R109" s="11" t="str">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
@@ -4596,15 +4611,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
-    <row r="1005" ht="15.75" customHeight="1"/>
-    <row r="1006" ht="15.75" customHeight="1"/>
-    <row r="1007" ht="15.75" customHeight="1"/>
-    <row r="1008" ht="15.75" customHeight="1"/>
-    <row r="1009" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -3003,7 +3003,7 @@
         <v>2</v>
       </c>
       <c r="B65" s="5">
-        <f t="shared" ref="B65:Y65" si="9">sum(B58,B50,B42,B34,B26,B18,B10,B2)</f>
+        <f t="shared" ref="B65:R65" si="9">sum(B58,B50,B42,B34,B26,B18,B10,B2)</f>
         <v>89497.5</v>
       </c>
       <c r="C65" s="5">
@@ -3070,34 +3070,13 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T65" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W65" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X65" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Y65" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="S65" s="18"/>
+      <c r="T65" s="18"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
       <c r="Z65" s="5">
         <f>sum(N65:Y65)</f>
         <v>2956348.12</v>
@@ -3108,7 +3087,7 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <f t="shared" ref="B66:Z66" si="10">average(B58,B50,B42,B34,B26,B18,B10,B2)</f>
+        <f t="shared" ref="B66:R66" si="10">average(B58,B50,B42,B34,B26,B18,B10,B2)</f>
         <v>44748.75</v>
       </c>
       <c r="C66" s="5">
@@ -3175,36 +3154,15 @@
         <f t="shared" si="10"/>
         <v>160347.71</v>
       </c>
-      <c r="S66" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T66" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U66" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V66" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W66" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X66" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y66" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
       <c r="Z66" s="5">
-        <f t="shared" si="10"/>
+        <f>average(Z58,Z50,Z42,Z34,Z26,Z18,Z10,Z2)</f>
         <v>422335.4457</v>
       </c>
     </row>
@@ -3280,34 +3238,13 @@
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
-      <c r="S67" s="3">
-        <f t="shared" ref="S67:Y67" si="12">sum(S59,S51,S43,S35,S27,S19,S11,S3)</f>
-        <v>0</v>
-      </c>
-      <c r="T67" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U67" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="V67" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="W67" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="X67" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Y67" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
       <c r="Z67" s="19">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
@@ -3318,104 +3255,83 @@
         <v>4</v>
       </c>
       <c r="B68" s="5">
-        <f t="shared" ref="B68:Y68" si="13">AVERAGE(B60,B52,B44,B36,B28,B20,B12,B4)</f>
+        <f t="shared" ref="B68:R68" si="12">AVERAGE(B60,B52,B44,B36,B28,B20,B12,B4)</f>
         <v>22374.375</v>
       </c>
       <c r="C68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>14428.8725</v>
       </c>
       <c r="D68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>20022.7475</v>
       </c>
       <c r="E68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>12879.358</v>
       </c>
       <c r="F68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>10576.564</v>
       </c>
       <c r="G68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>14472.008</v>
       </c>
       <c r="H68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>17632.932</v>
       </c>
       <c r="I68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>16201.158</v>
       </c>
       <c r="J68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>10893.582</v>
       </c>
       <c r="K68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>10478.64</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>7528.564</v>
       </c>
       <c r="M68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6484.368</v>
       </c>
       <c r="N68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>10965.62667</v>
       </c>
       <c r="O68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>7259.26</v>
       </c>
       <c r="P68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6149.781429</v>
       </c>
       <c r="Q68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>10070.49286</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>13479.04857</v>
       </c>
-      <c r="S68" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T68" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U68" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V68" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W68" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X68" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y68" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z68" s="5" t="str">
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="5">
         <f>average(N68:Y68)</f>
-        <v>#DIV/0!</v>
+        <v>9584.841905</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
@@ -3423,101 +3339,86 @@
         <v>15</v>
       </c>
       <c r="B69" s="11">
-        <f t="shared" ref="B69:R69" si="14">average(B53,B45,B37,B29,B21,B13,B5)</f>
+        <f t="shared" ref="B69:S69" si="13">average(B53,B45,B37,B29,B21,B13,B5)</f>
         <v>0.3444333333</v>
       </c>
       <c r="C69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.309525</v>
       </c>
       <c r="D69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.42125</v>
       </c>
       <c r="E69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.42478</v>
       </c>
       <c r="F69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.40488</v>
       </c>
       <c r="G69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.45414</v>
       </c>
       <c r="H69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.40556</v>
       </c>
       <c r="I69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.31688</v>
       </c>
       <c r="J69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.41248</v>
       </c>
       <c r="K69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.29162</v>
       </c>
       <c r="L69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.35694</v>
       </c>
       <c r="M69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.3687333333</v>
       </c>
       <c r="N69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.26642</v>
       </c>
       <c r="O69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.2291666667</v>
       </c>
       <c r="P69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.3634</v>
       </c>
       <c r="Q69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.2847571429</v>
       </c>
       <c r="R69" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.15246</v>
       </c>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3" t="str">
-        <f t="shared" ref="T69:Y69" si="15">AVERAGE(T62,T54,T46,T38,T30,T22,T14,T6)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U69" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V69" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W69" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X69" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y69" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z69" s="3" t="str">
+      <c r="S69" s="11">
+        <f t="shared" si="13"/>
+        <v>0.1382333333</v>
+      </c>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>#DIV/0!</v>
+        <v>0.1453466667</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3525,72 +3426,76 @@
         <v>16</v>
       </c>
       <c r="B70" s="11">
-        <f t="shared" ref="B70:R70" si="16">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <f t="shared" ref="B70:S70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
       <c r="C70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.366525</v>
       </c>
       <c r="D70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.30455</v>
       </c>
       <c r="E70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.38494</v>
       </c>
       <c r="F70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.40984</v>
       </c>
       <c r="G70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.4393</v>
       </c>
       <c r="H70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.42082</v>
       </c>
       <c r="I70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.4131</v>
       </c>
       <c r="J70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.3999</v>
       </c>
       <c r="K70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.38592</v>
       </c>
       <c r="L70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.33754</v>
       </c>
       <c r="M70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.34014</v>
       </c>
       <c r="N70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.30044</v>
       </c>
       <c r="O70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.30184</v>
       </c>
       <c r="P70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.2368833333</v>
       </c>
       <c r="Q70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.3044714286</v>
       </c>
       <c r="R70" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.2830428571</v>
+      </c>
+      <c r="S70" s="11">
+        <f t="shared" si="14"/>
+        <v>0.2241285714</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3656,67 +3561,67 @@
         <v>17</v>
       </c>
       <c r="C109" s="11" t="str">
-        <f t="shared" ref="C109:R109" si="17">average(C79:C84)</f>
+        <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R109" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -697,7 +697,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.3333</v>
+        <v>0.04</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -707,7 +707,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.2846333333</v>
+        <v>0.23575</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -766,7 +766,7 @@
         <v>0.3426</v>
       </c>
       <c r="S6" s="12">
-        <v>0.2673</v>
+        <v>0.2549</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -776,7 +776,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2694666667</v>
+        <v>0.2674</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1155,7 +1155,7 @@
         <v>0.2711</v>
       </c>
       <c r="S14" s="12">
-        <v>0.2044</v>
+        <v>0.2031</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="15"/>
@@ -1163,7 +1163,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.23775</v>
+        <v>0.2371</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1528,7 +1528,7 @@
         <v>0.232</v>
       </c>
       <c r="S22" s="12">
-        <v>0.181</v>
+        <v>0.1881</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
@@ -1538,7 +1538,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.2065</v>
+        <v>0.21005</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1916,7 +1916,7 @@
         <v>0.3297</v>
       </c>
       <c r="S30" s="12">
-        <v>0.2759</v>
+        <v>0.2778</v>
       </c>
       <c r="T30" s="16"/>
       <c r="U30" s="11"/>
@@ -1926,7 +1926,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.3028</v>
+        <v>0.30375</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2241,7 +2241,7 @@
         <v>0.0606</v>
       </c>
       <c r="S37" s="12">
-        <v>0.3333</v>
+        <v>0.2</v>
       </c>
       <c r="T37" s="11"/>
       <c r="U37" s="11"/>
@@ -2307,7 +2307,7 @@
         <v>0.2432</v>
       </c>
       <c r="S38" s="12">
-        <v>0.2024</v>
+        <v>0.1923</v>
       </c>
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
@@ -2317,7 +2317,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2228</v>
+        <v>0.21775</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2529,7 +2529,7 @@
         <v>0.2667</v>
       </c>
       <c r="S46" s="12">
-        <v>0.2157</v>
+        <v>0.2062</v>
       </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
@@ -2539,7 +2539,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2412</v>
+        <v>0.23645</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2713,7 +2713,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0333</v>
+        <v>0.0294</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2749,7 +2749,7 @@
         <v>0.296</v>
       </c>
       <c r="S54" s="12">
-        <v>0.2222</v>
+        <v>0.2114</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -2759,7 +2759,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2591</v>
+        <v>0.2537</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.1382333333</v>
+        <v>0.06648333333</v>
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
@@ -3418,7 +3418,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.1453466667</v>
+        <v>0.1094716667</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S70" s="11">
         <f t="shared" si="14"/>
-        <v>0.2241285714</v>
+        <v>0.2191142857</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -169,6 +169,9 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -697,7 +700,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.04</v>
+        <v>0.0385</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -707,7 +710,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.23575</v>
+        <v>0.2355</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -766,7 +769,7 @@
         <v>0.3426</v>
       </c>
       <c r="S6" s="12">
-        <v>0.2549</v>
+        <v>0.2647</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -776,7 +779,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2674</v>
+        <v>0.2690333333</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1092,7 +1095,7 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="11">
         <v>0.0526</v>
       </c>
       <c r="T13" s="14"/>
@@ -1154,8 +1157,8 @@
       <c r="R14" s="11">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="12">
-        <v>0.2031</v>
+      <c r="S14" s="16">
+        <v>22.66</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="15"/>
@@ -1163,12 +1166,12 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2371</v>
+        <v>11.46555</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="S15" s="11"/>
-      <c r="T15" s="16"/>
+      <c r="T15" s="17"/>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
@@ -1469,7 +1472,7 @@
         <v>0.22</v>
       </c>
       <c r="R21" s="11"/>
-      <c r="S21" s="12"/>
+      <c r="S21" s="11"/>
       <c r="T21" s="11"/>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
@@ -1528,7 +1531,7 @@
         <v>0.232</v>
       </c>
       <c r="S22" s="12">
-        <v>0.1881</v>
+        <v>0.1765</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
@@ -1538,7 +1541,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.21005</v>
+        <v>0.20425</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1851,10 +1854,10 @@
         <v>0.2759</v>
       </c>
       <c r="R29" s="11"/>
-      <c r="S29" s="12">
+      <c r="S29" s="11">
         <v>0.0769</v>
       </c>
-      <c r="T29" s="16"/>
+      <c r="T29" s="17"/>
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
@@ -1916,9 +1919,9 @@
         <v>0.3297</v>
       </c>
       <c r="S30" s="12">
-        <v>0.2778</v>
-      </c>
-      <c r="T30" s="16"/>
+        <v>0.2549</v>
+      </c>
+      <c r="T30" s="17"/>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
@@ -1926,7 +1929,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.30375</v>
+        <v>0.2923</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2240,7 +2243,7 @@
       <c r="R37" s="11">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="12">
+      <c r="S37" s="11">
         <v>0.2</v>
       </c>
       <c r="T37" s="11"/>
@@ -2306,7 +2309,7 @@
       <c r="R38" s="11">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="11">
         <v>0.1923</v>
       </c>
       <c r="T38" s="11"/>
@@ -2472,7 +2475,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="17"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2490,7 +2493,7 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="12">
+      <c r="S45" s="11">
         <v>0.0</v>
       </c>
       <c r="T45" s="11"/>
@@ -2529,7 +2532,7 @@
         <v>0.2667</v>
       </c>
       <c r="S46" s="12">
-        <v>0.2062</v>
+        <v>0.1979</v>
       </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
@@ -2539,7 +2542,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.23645</v>
+        <v>0.2323</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2713,7 +2716,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0294</v>
+        <v>0.0588</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2749,7 +2752,7 @@
         <v>0.296</v>
       </c>
       <c r="S54" s="12">
-        <v>0.2114</v>
+        <v>0.2131</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -2759,7 +2762,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2537</v>
+        <v>0.25455</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3070,8 +3073,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="18"/>
-      <c r="T65" s="18"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3170,71 +3173,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="20">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="19">
+      <c r="C67" s="20">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="20">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="19">
+      <c r="G67" s="20">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="19">
+      <c r="H67" s="20">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="19">
+      <c r="I67" s="20">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="19">
+      <c r="J67" s="20">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="19">
+      <c r="K67" s="20">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="20">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="19">
+      <c r="M67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="19">
+      <c r="N67" s="20">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="19">
+      <c r="O67" s="20">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="19">
+      <c r="P67" s="20">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="19">
+      <c r="Q67" s="20">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="19">
+      <c r="R67" s="20">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3245,7 +3248,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="19">
+      <c r="Z67" s="20">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3408,7 +3411,7 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.06648333333</v>
+        <v>0.07113333333</v>
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
@@ -3418,7 +3421,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.1094716667</v>
+        <v>0.1117966667</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3495,7 +3498,7 @@
       </c>
       <c r="S70" s="11">
         <f t="shared" si="14"/>
-        <v>0.2191142857</v>
+        <v>3.422771429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -169,9 +169,6 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -769,7 +766,7 @@
         <v>0.3426</v>
       </c>
       <c r="S6" s="12">
-        <v>0.2647</v>
+        <v>0.2772</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -779,7 +776,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2690333333</v>
+        <v>0.2711166667</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1095,8 +1092,8 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="11">
-        <v>0.0526</v>
+      <c r="S13" s="12">
+        <v>0.0476</v>
       </c>
       <c r="T13" s="14"/>
       <c r="W13" s="15"/>
@@ -1157,8 +1154,8 @@
       <c r="R14" s="11">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="16">
-        <v>22.66</v>
+      <c r="S14" s="12">
+        <v>0.2403</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="15"/>
@@ -1166,12 +1163,12 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>11.46555</v>
+        <v>0.2557</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="S15" s="11"/>
-      <c r="T15" s="17"/>
+      <c r="T15" s="16"/>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
@@ -1531,7 +1528,7 @@
         <v>0.232</v>
       </c>
       <c r="S22" s="12">
-        <v>0.1765</v>
+        <v>0.1818</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
@@ -1541,7 +1538,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.20425</v>
+        <v>0.2069</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1854,10 +1851,10 @@
         <v>0.2759</v>
       </c>
       <c r="R29" s="11"/>
-      <c r="S29" s="11">
-        <v>0.0769</v>
-      </c>
-      <c r="T29" s="17"/>
+      <c r="S29" s="12">
+        <v>0.0714</v>
+      </c>
+      <c r="T29" s="16"/>
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
@@ -1919,9 +1916,9 @@
         <v>0.3297</v>
       </c>
       <c r="S30" s="12">
-        <v>0.2549</v>
-      </c>
-      <c r="T30" s="17"/>
+        <v>0.24</v>
+      </c>
+      <c r="T30" s="16"/>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
@@ -1929,7 +1926,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2923</v>
+        <v>0.28485</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2309,8 +2306,8 @@
       <c r="R38" s="11">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="11">
-        <v>0.1923</v>
+      <c r="S38" s="12">
+        <v>0.1948</v>
       </c>
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
@@ -2320,7 +2317,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.21775</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2475,7 +2472,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="18"/>
+      <c r="I45" s="17"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2493,9 +2490,7 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="11">
-        <v>0.0</v>
-      </c>
+      <c r="S45" s="11"/>
       <c r="T45" s="11"/>
       <c r="U45" s="11"/>
       <c r="V45" s="11"/>
@@ -2532,7 +2527,7 @@
         <v>0.2667</v>
       </c>
       <c r="S46" s="12">
-        <v>0.1979</v>
+        <v>0.1957</v>
       </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
@@ -2542,7 +2537,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2323</v>
+        <v>0.2312</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2716,7 +2711,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0588</v>
+        <v>0.0789</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2752,7 +2747,7 @@
         <v>0.296</v>
       </c>
       <c r="S54" s="12">
-        <v>0.2131</v>
+        <v>0.2114</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -2762,7 +2757,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.25455</v>
+        <v>0.2537</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3073,8 +3068,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
+      <c r="S65" s="18"/>
+      <c r="T65" s="18"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3173,71 +3168,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="19">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="19">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="19">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="19">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="19">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="19">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="19">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="20">
+      <c r="I67" s="19">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J67" s="19">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="20">
+      <c r="K67" s="19">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="20">
+      <c r="L67" s="19">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="20">
+      <c r="M67" s="19">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="20">
+      <c r="N67" s="19">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="20">
+      <c r="O67" s="19">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="20">
+      <c r="P67" s="19">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="20">
+      <c r="Q67" s="19">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="20">
+      <c r="R67" s="19">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3248,7 +3243,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="20">
+      <c r="Z67" s="19">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3411,7 +3406,7 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.07113333333</v>
+        <v>0.08728</v>
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
@@ -3421,7 +3416,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.1117966667</v>
+        <v>0.11987</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3498,7 +3493,7 @@
       </c>
       <c r="S70" s="11">
         <f t="shared" si="14"/>
-        <v>3.422771429</v>
+        <v>0.2201714286</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -697,7 +697,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.0385</v>
+        <v>0.037</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -707,7 +707,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.2355</v>
+        <v>0.23525</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -766,7 +766,7 @@
         <v>0.3426</v>
       </c>
       <c r="S6" s="12">
-        <v>0.2772</v>
+        <v>0.2745</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -776,7 +776,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2711166667</v>
+        <v>0.2706666667</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1093,7 +1093,7 @@
         <v>0.0513</v>
       </c>
       <c r="S13" s="12">
-        <v>0.0476</v>
+        <v>0.0455</v>
       </c>
       <c r="T13" s="14"/>
       <c r="W13" s="15"/>
@@ -1155,7 +1155,7 @@
         <v>0.2711</v>
       </c>
       <c r="S14" s="12">
-        <v>0.2403</v>
+        <v>0.2339</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="15"/>
@@ -1163,7 +1163,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2557</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1528,7 +1528,7 @@
         <v>0.232</v>
       </c>
       <c r="S22" s="12">
-        <v>0.1818</v>
+        <v>0.1443</v>
       </c>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
@@ -1538,7 +1538,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.2069</v>
+        <v>0.18815</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="R29" s="11"/>
       <c r="S29" s="12">
-        <v>0.0714</v>
+        <v>0.0625</v>
       </c>
       <c r="T29" s="16"/>
       <c r="U29" s="11"/>
@@ -1916,7 +1916,7 @@
         <v>0.3297</v>
       </c>
       <c r="S30" s="12">
-        <v>0.24</v>
+        <v>0.2308</v>
       </c>
       <c r="T30" s="16"/>
       <c r="U30" s="11"/>
@@ -1926,7 +1926,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.28485</v>
+        <v>0.28025</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2240,8 +2240,8 @@
       <c r="R37" s="11">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="11">
-        <v>0.2</v>
+      <c r="S37" s="12">
+        <v>0.1429</v>
       </c>
       <c r="T37" s="11"/>
       <c r="U37" s="11"/>
@@ -2307,7 +2307,7 @@
         <v>0.2432</v>
       </c>
       <c r="S38" s="12">
-        <v>0.1948</v>
+        <v>0.1974</v>
       </c>
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
@@ -2317,7 +2317,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.219</v>
+        <v>0.2203</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2527,7 +2527,7 @@
         <v>0.2667</v>
       </c>
       <c r="S46" s="12">
-        <v>0.1957</v>
+        <v>0.1705</v>
       </c>
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
@@ -2537,7 +2537,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2312</v>
+        <v>0.2186</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2711,7 +2711,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0789</v>
+        <v>0.0698</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2747,7 +2747,7 @@
         <v>0.296</v>
       </c>
       <c r="S54" s="12">
-        <v>0.2114</v>
+        <v>0.192</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -2757,7 +2757,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2537</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.08728</v>
+        <v>0.07154</v>
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
@@ -3416,7 +3416,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.11987</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="S70" s="11">
         <f t="shared" si="14"/>
-        <v>0.2201714286</v>
+        <v>0.2062</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -697,7 +697,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.037</v>
+        <v>0.0968</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -707,7 +707,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.23525</v>
+        <v>0.2452166667</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -765,10 +765,12 @@
       <c r="R6" s="11">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="11">
         <v>0.2745</v>
       </c>
-      <c r="T6" s="11"/>
+      <c r="T6" s="12">
+        <v>0.2551</v>
+      </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
@@ -776,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2706666667</v>
+        <v>0.2684428571</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1093,7 +1095,7 @@
         <v>0.0513</v>
       </c>
       <c r="S13" s="12">
-        <v>0.0455</v>
+        <v>0.0435</v>
       </c>
       <c r="T13" s="14"/>
       <c r="W13" s="15"/>
@@ -1154,16 +1156,20 @@
       <c r="R14" s="11">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S14" s="11">
         <v>0.2339</v>
       </c>
-      <c r="T14" s="14"/>
-      <c r="W14" s="15"/>
+      <c r="T14" s="12">
+        <v>0.2393</v>
+      </c>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2525</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1527,10 +1533,12 @@
       <c r="R22" s="11">
         <v>0.232</v>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="11">
         <v>0.1443</v>
       </c>
-      <c r="T22" s="11"/>
+      <c r="T22" s="12">
+        <v>0.1505</v>
+      </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
@@ -1538,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.18815</v>
+        <v>0.1756</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1852,7 +1860,7 @@
       </c>
       <c r="R29" s="11"/>
       <c r="S29" s="12">
-        <v>0.0625</v>
+        <v>0.0588</v>
       </c>
       <c r="T29" s="16"/>
       <c r="U29" s="11"/>
@@ -1915,10 +1923,12 @@
       <c r="R30" s="11">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="12">
+      <c r="S30" s="11">
         <v>0.2308</v>
       </c>
-      <c r="T30" s="16"/>
+      <c r="T30" s="12">
+        <v>0.2</v>
+      </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
@@ -1926,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.28025</v>
+        <v>0.2535</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2241,7 +2251,7 @@
         <v>0.0606</v>
       </c>
       <c r="S37" s="12">
-        <v>0.1429</v>
+        <v>0.1111</v>
       </c>
       <c r="T37" s="11"/>
       <c r="U37" s="11"/>
@@ -2306,10 +2316,12 @@
       <c r="R38" s="11">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="11">
         <v>0.1974</v>
       </c>
-      <c r="T38" s="11"/>
+      <c r="T38" s="12">
+        <v>0.1757</v>
+      </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
       <c r="W38" s="11"/>
@@ -2317,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2203</v>
+        <v>0.2054333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2526,10 +2538,12 @@
       <c r="R46" s="11">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="12">
+      <c r="S46" s="11">
         <v>0.1705</v>
       </c>
-      <c r="T46" s="11"/>
+      <c r="T46" s="12">
+        <v>0.1548</v>
+      </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
       <c r="W46" s="11"/>
@@ -2537,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.2186</v>
+        <v>0.1973333333</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2711,7 +2725,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="12">
-        <v>0.0698</v>
+        <v>0.093</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -2746,10 +2760,12 @@
       <c r="R54" s="11">
         <v>0.296</v>
       </c>
-      <c r="S54" s="12">
+      <c r="S54" s="11">
         <v>0.192</v>
       </c>
-      <c r="T54" s="11"/>
+      <c r="T54" s="12">
+        <v>0.2016</v>
+      </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
       <c r="W54" s="11"/>
@@ -2757,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.244</v>
+        <v>0.2298666667</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3406,9 +3422,9 @@
       </c>
       <c r="S69" s="11">
         <f t="shared" si="13"/>
-        <v>0.07154</v>
-      </c>
-      <c r="T69" s="3"/>
+        <v>0.08064</v>
+      </c>
+      <c r="T69" s="11"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
@@ -3416,7 +3432,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="11">
         <f>average(R69:Y69)</f>
-        <v>0.112</v>
+        <v>0.11655</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3424,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="11">
-        <f t="shared" ref="B70:S70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
       <c r="C70" s="11">
@@ -3494,6 +3510,10 @@
       <c r="S70" s="11">
         <f t="shared" si="14"/>
         <v>0.2062</v>
+      </c>
+      <c r="T70" s="11">
+        <f t="shared" si="14"/>
+        <v>0.1967142857</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.2551</v>
+        <v>0.2449</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2684428571</v>
+        <v>0.2669857143</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2393</v>
+        <v>0.2261</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2481</v>
+        <v>0.2437</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1537,7 +1537,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="12">
-        <v>0.1505</v>
+        <v>0.1264</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1546,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.1756</v>
+        <v>0.1675666667</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.2</v>
+        <v>0.1837</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2535</v>
+        <v>0.2480666667</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1757</v>
+        <v>0.1644</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2054333333</v>
+        <v>0.2016666667</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1548</v>
+        <v>0.1429</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1973333333</v>
+        <v>0.1933666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1967142857</v>
+        <v>0.1842857143</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.2449</v>
+        <v>0.2474</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2669857143</v>
+        <v>0.2673428571</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2261</v>
+        <v>0.2155</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2437</v>
+        <v>0.2401666667</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.1837</v>
+        <v>0.1923</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2480666667</v>
+        <v>0.2509333333</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1644</v>
+        <v>0.1739</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2016666667</v>
+        <v>0.2048333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1429</v>
+        <v>0.1375</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1933666667</v>
+        <v>0.1915666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1842857143</v>
+        <v>0.1849428571</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.2474</v>
+        <v>0.2143</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2673428571</v>
+        <v>0.2626142857</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2155</v>
+        <v>0.2047</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2401666667</v>
+        <v>0.2365666667</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1537,7 +1537,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="12">
-        <v>0.1264</v>
+        <v>0.129</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1546,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.1675666667</v>
+        <v>0.1684333333</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.1923</v>
+        <v>0.1887</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2509333333</v>
+        <v>0.2497333333</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1739</v>
+        <v>0.1778</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2048333333</v>
+        <v>0.2061333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1375</v>
+        <v>0.1333</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1915666667</v>
+        <v>0.1901666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2764,7 +2764,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="12">
-        <v>0.2016</v>
+        <v>0.2</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
@@ -2773,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2298666667</v>
+        <v>0.2293333333</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1849428571</v>
+        <v>0.1782571429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.2143</v>
+        <v>0.1895</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2626142857</v>
+        <v>0.2590714286</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2047</v>
+        <v>0.2063</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2365666667</v>
+        <v>0.2371</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1537,7 +1537,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="12">
-        <v>0.129</v>
+        <v>0.1319</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1546,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.1684333333</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1778</v>
+        <v>0.1591</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.2061333333</v>
+        <v>0.1999</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1333</v>
+        <v>0.1233</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1901666667</v>
+        <v>0.1868333333</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2764,7 +2764,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="12">
-        <v>0.2</v>
+        <v>0.2017</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
@@ -2773,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2293333333</v>
+        <v>0.2299</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1782571429</v>
+        <v>0.1715</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.1895</v>
+        <v>0.1978</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2590714286</v>
+        <v>0.2602571429</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.2063</v>
+        <v>0.1641</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2371</v>
+        <v>0.2230333333</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1537,7 +1537,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="12">
-        <v>0.1319</v>
+        <v>0.1034</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1546,7 +1546,7 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11">
         <f>average(R22:Y22)</f>
-        <v>0.1694</v>
+        <v>0.1599</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.1887</v>
+        <v>0.16</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2497333333</v>
+        <v>0.2401666667</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1591</v>
+        <v>0.1</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.1999</v>
+        <v>0.1802</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1233</v>
+        <v>0.1194</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1868333333</v>
+        <v>0.1855333333</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2764,7 +2764,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="12">
-        <v>0.2017</v>
+        <v>0.1951</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
@@ -2773,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2299</v>
+        <v>0.2277</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1715</v>
+        <v>0.1485428571</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -769,7 +769,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="12">
-        <v>0.1978</v>
+        <v>0.1932</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -778,7 +778,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11">
         <f t="shared" si="2"/>
-        <v>0.2602571429</v>
+        <v>0.2596</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1160,7 +1160,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="12">
-        <v>0.1641</v>
+        <v>0.1508</v>
       </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -1169,7 +1169,7 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11">
         <f>average(R14:Y14)</f>
-        <v>0.2230333333</v>
+        <v>0.2186</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1927,7 +1927,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="12">
-        <v>0.16</v>
+        <v>0.1875</v>
       </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
@@ -1936,7 +1936,7 @@
       <c r="Y30" s="11"/>
       <c r="Z30" s="11">
         <f>average(R30:Y30)</f>
-        <v>0.2401666667</v>
+        <v>0.2493333333</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2320,7 +2320,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="12">
-        <v>0.1</v>
+        <v>0.1053</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
@@ -2329,7 +2329,7 @@
       <c r="Y38" s="11"/>
       <c r="Z38" s="11">
         <f>average(R38:Y38)</f>
-        <v>0.1802</v>
+        <v>0.1819666667</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2542,7 +2542,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="12">
-        <v>0.1194</v>
+        <v>0.127</v>
       </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
@@ -2551,7 +2551,7 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11">
         <f>average(R46:Y46)</f>
-        <v>0.1855333333</v>
+        <v>0.1880666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2764,7 +2764,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="12">
-        <v>0.1951</v>
+        <v>0.1935</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
@@ -2773,7 +2773,7 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11">
         <f>average(R54:Y54)</f>
-        <v>0.2277</v>
+        <v>0.2271666667</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="T70" s="11">
         <f t="shared" si="14"/>
-        <v>0.1485428571</v>
+        <v>0.1515285714</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -158,6 +158,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -699,7 +702,7 @@
       <c r="S5" s="10">
         <v>0.0968</v>
       </c>
-      <c r="T5" s="9"/>
+      <c r="T5" s="11"/>
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -714,71 +717,71 @@
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="12">
         <v>0.5714</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <v>0.4167</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="12">
         <v>0.3182</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <v>0.3333</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <v>0.3429</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="12">
         <v>0.4348</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="12">
         <v>0.4468</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="12">
         <v>0.3462</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="12">
         <v>0.2456</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="12">
         <v>0.2203</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="12">
         <v>0.2537</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="12">
         <v>0.2593</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="12">
         <v>0.2368</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="12">
         <v>0.2308</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="12">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="12">
         <v>0.3393</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="12">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="11">
+      <c r="S6" s="12">
         <v>0.2745</v>
       </c>
-      <c r="T6" s="12">
-        <v>0.1932</v>
-      </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11">
+      <c r="T6" s="13">
+        <v>0.1867</v>
+      </c>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2596</v>
+        <v>0.2586714286</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -916,7 +919,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="13"/>
+      <c r="W10" s="14"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -975,7 +978,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="13"/>
+      <c r="W11" s="14"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1033,7 +1036,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="13"/>
+      <c r="W12" s="14"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1094,103 +1097,103 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="13">
         <v>0.0435</v>
       </c>
-      <c r="T13" s="14"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="11"/>
+      <c r="T13" s="15"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12">
         <v>0.5161</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="12">
         <v>0.3333</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="12">
         <v>0.34</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="12">
         <v>0.3521</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="12">
         <v>0.4125</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="12">
         <v>0.4321</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="12">
         <v>0.369</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="12">
         <v>0.3194</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="12">
         <v>0.2969</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="12">
         <v>0.32</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="12">
         <v>0.3205</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="12">
         <v>0.3571</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="12">
         <v>0.449</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="12">
         <v>0.4182</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="12">
         <v>0.3269</v>
       </c>
-      <c r="R14" s="11">
+      <c r="R14" s="12">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="11">
+      <c r="S14" s="12">
         <v>0.2339</v>
       </c>
-      <c r="T14" s="12">
-        <v>0.1508</v>
-      </c>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="11">
+      <c r="T14" s="13">
+        <v>0.099</v>
+      </c>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.2186</v>
+        <v>0.2013333333</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="S15" s="11"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
@@ -1474,79 +1477,79 @@
       <c r="Q21" s="8">
         <v>0.22</v>
       </c>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="11"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
       <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12">
         <v>0.5</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="12">
         <v>0.5625</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="12">
         <v>0.5714</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="12">
         <v>0.4815</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="12">
         <v>0.4634</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="12">
         <v>0.4898</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="12">
         <v>0.463</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="12">
         <v>0.377</v>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="12">
         <v>0.3387</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="12">
         <v>0.3265</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="12">
         <v>0.3056</v>
       </c>
-      <c r="P22" s="11">
+      <c r="P22" s="12">
         <v>0.2075</v>
       </c>
-      <c r="Q22" s="11">
+      <c r="Q22" s="12">
         <v>0.2615</v>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="12">
         <v>0.232</v>
       </c>
-      <c r="S22" s="11">
+      <c r="S22" s="12">
         <v>0.1443</v>
       </c>
-      <c r="T22" s="12">
-        <v>0.1034</v>
-      </c>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11">
+      <c r="T22" s="13">
+        <v>0.0575</v>
+      </c>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1599</v>
+        <v>0.1446</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1743,7 +1746,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="13"/>
+      <c r="W27" s="14"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1801,8 +1804,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="14"/>
-      <c r="W28" s="13"/>
+      <c r="T28" s="15"/>
+      <c r="W28" s="14"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1858,85 +1861,85 @@
       <c r="Q29" s="8">
         <v>0.2759</v>
       </c>
-      <c r="R29" s="11"/>
-      <c r="S29" s="12">
+      <c r="R29" s="12"/>
+      <c r="S29" s="13">
         <v>0.0588</v>
       </c>
-      <c r="T29" s="16"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="11"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
       <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12">
         <v>0.1333</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="12">
         <v>0.1667</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="12">
         <v>0.3514</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="12">
         <v>0.375</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="12">
         <v>0.3778</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="12">
         <v>0.3226</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="12">
         <v>0.4359</v>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="12">
         <v>0.4286</v>
       </c>
-      <c r="K30" s="11">
+      <c r="K30" s="12">
         <v>0.4366</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="12">
         <v>0.3457</v>
       </c>
-      <c r="M30" s="11">
+      <c r="M30" s="12">
         <v>0.3222</v>
       </c>
-      <c r="N30" s="11">
+      <c r="N30" s="12">
         <v>0.2568</v>
       </c>
-      <c r="O30" s="11">
+      <c r="O30" s="12">
         <v>0.1905</v>
       </c>
-      <c r="P30" s="11">
+      <c r="P30" s="12">
         <v>0.2281</v>
       </c>
-      <c r="Q30" s="11">
+      <c r="Q30" s="12">
         <v>0.3243</v>
       </c>
-      <c r="R30" s="11">
+      <c r="R30" s="12">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="11">
+      <c r="S30" s="12">
         <v>0.2308</v>
       </c>
-      <c r="T30" s="12">
-        <v>0.1875</v>
-      </c>
-      <c r="U30" s="11"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11"/>
-      <c r="Z30" s="11">
+      <c r="T30" s="13">
+        <v>0.1591</v>
+      </c>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.2493333333</v>
+        <v>0.2398666667</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2061,7 +2064,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="13"/>
+      <c r="N34" s="14"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2247,89 +2250,89 @@
       <c r="Q37" s="8">
         <v>0.303</v>
       </c>
-      <c r="R37" s="11">
+      <c r="R37" s="12">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="12">
+      <c r="S37" s="13">
         <v>0.1111</v>
       </c>
-      <c r="T37" s="11"/>
-      <c r="U37" s="11"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="11"/>
-      <c r="X37" s="11"/>
-      <c r="Y37" s="11"/>
+      <c r="T37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
       <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="12">
         <v>0.4375</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="12">
         <v>0.4</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="12">
         <v>0.4</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="12">
         <v>0.4</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="12">
         <v>0.4167</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="12">
         <v>0.4</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="12">
         <v>0.4211</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="12">
         <v>0.451</v>
       </c>
-      <c r="J38" s="11">
+      <c r="J38" s="12">
         <v>0.5161</v>
       </c>
-      <c r="K38" s="11">
+      <c r="K38" s="12">
         <v>0.5128</v>
       </c>
-      <c r="L38" s="11">
+      <c r="L38" s="12">
         <v>0.3913</v>
       </c>
-      <c r="M38" s="11">
+      <c r="M38" s="12">
         <v>0.46</v>
       </c>
-      <c r="N38" s="11">
+      <c r="N38" s="12">
         <v>0.325</v>
       </c>
-      <c r="O38" s="11">
+      <c r="O38" s="12">
         <v>0.3333</v>
       </c>
-      <c r="P38" s="11">
+      <c r="P38" s="12">
         <v>0.2564</v>
       </c>
-      <c r="Q38" s="11">
+      <c r="Q38" s="12">
         <v>0.3238</v>
       </c>
-      <c r="R38" s="11">
+      <c r="R38" s="12">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="11">
+      <c r="S38" s="12">
         <v>0.1974</v>
       </c>
-      <c r="T38" s="12">
-        <v>0.1053</v>
-      </c>
-      <c r="U38" s="11"/>
-      <c r="V38" s="11"/>
-      <c r="W38" s="11"/>
-      <c r="X38" s="11"/>
-      <c r="Y38" s="11"/>
-      <c r="Z38" s="11">
+      <c r="T38" s="13">
+        <v>0.0741</v>
+      </c>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.1819666667</v>
+        <v>0.1715666667</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2458,7 +2461,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="13"/>
+      <c r="L44" s="14"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2484,7 +2487,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="17"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2502,61 +2505,61 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
-      <c r="U45" s="11"/>
-      <c r="V45" s="11"/>
-      <c r="W45" s="11"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
-      <c r="Z45" s="11"/>
+      <c r="S45" s="12"/>
+      <c r="T45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="12"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12">
         <v>0.1111</v>
       </c>
-      <c r="Q46" s="11">
+      <c r="Q46" s="12">
         <v>0.2828</v>
       </c>
-      <c r="R46" s="11">
+      <c r="R46" s="12">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="11">
+      <c r="S46" s="12">
         <v>0.1705</v>
       </c>
-      <c r="T46" s="12">
-        <v>0.127</v>
-      </c>
-      <c r="U46" s="11"/>
-      <c r="V46" s="11"/>
-      <c r="W46" s="11"/>
-      <c r="X46" s="11"/>
-      <c r="Y46" s="11"/>
-      <c r="Z46" s="11">
+      <c r="T46" s="13">
+        <v>0.1429</v>
+      </c>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.1880666667</v>
+        <v>0.1933666667</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="Q47" s="11"/>
-      <c r="R47" s="11"/>
+      <c r="Q47" s="12"/>
+      <c r="R47" s="12"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
@@ -2724,56 +2727,56 @@
       <c r="R53" s="8">
         <v>0.2857</v>
       </c>
-      <c r="S53" s="12">
+      <c r="S53" s="13">
         <v>0.093</v>
       </c>
-      <c r="T53" s="11"/>
-      <c r="U53" s="11"/>
-      <c r="V53" s="11"/>
-      <c r="W53" s="11"/>
-      <c r="X53" s="11"/>
-      <c r="Y53" s="11"/>
-      <c r="Z53" s="11"/>
+      <c r="T53" s="12"/>
+      <c r="U53" s="12"/>
+      <c r="V53" s="12"/>
+      <c r="W53" s="12"/>
+      <c r="X53" s="12"/>
+      <c r="Y53" s="12"/>
+      <c r="Z53" s="12"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="11"/>
-      <c r="Q54" s="11">
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12"/>
+      <c r="Q54" s="12">
         <v>0.2727</v>
       </c>
-      <c r="R54" s="11">
+      <c r="R54" s="12">
         <v>0.296</v>
       </c>
-      <c r="S54" s="11">
+      <c r="S54" s="12">
         <v>0.192</v>
       </c>
-      <c r="T54" s="12">
-        <v>0.1935</v>
-      </c>
-      <c r="U54" s="11"/>
-      <c r="V54" s="11"/>
-      <c r="W54" s="11"/>
-      <c r="X54" s="11"/>
-      <c r="Y54" s="11"/>
-      <c r="Z54" s="11">
+      <c r="T54" s="13">
+        <v>0.1636</v>
+      </c>
+      <c r="U54" s="12"/>
+      <c r="V54" s="12"/>
+      <c r="W54" s="12"/>
+      <c r="X54" s="12"/>
+      <c r="Y54" s="12"/>
+      <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.2271666667</v>
+        <v>0.2172</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -2813,7 +2816,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="13"/>
+      <c r="L58" s="14"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -2855,57 +2858,57 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="11"/>
-      <c r="P61" s="11"/>
-      <c r="Q61" s="11"/>
-      <c r="R61" s="11"/>
-      <c r="S61" s="11"/>
-      <c r="T61" s="11"/>
-      <c r="U61" s="11"/>
-      <c r="V61" s="11"/>
-      <c r="W61" s="11"/>
-      <c r="X61" s="11"/>
-      <c r="Y61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="P61" s="12"/>
+      <c r="Q61" s="12"/>
+      <c r="R61" s="12"/>
+      <c r="S61" s="12"/>
+      <c r="T61" s="12"/>
+      <c r="U61" s="12"/>
+      <c r="V61" s="12"/>
+      <c r="W61" s="12"/>
+      <c r="X61" s="12"/>
+      <c r="Y61" s="12"/>
       <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
-      <c r="P62" s="11"/>
-      <c r="Q62" s="11"/>
-      <c r="R62" s="11"/>
-      <c r="S62" s="11"/>
-      <c r="T62" s="11"/>
-      <c r="U62" s="11"/>
-      <c r="V62" s="11"/>
-      <c r="W62" s="11"/>
-      <c r="X62" s="11"/>
-      <c r="Y62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="12"/>
+      <c r="S62" s="12"/>
+      <c r="T62" s="12"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
       <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -3084,8 +3087,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="18"/>
-      <c r="T65" s="18"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3184,71 +3187,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="20">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="19">
+      <c r="C67" s="20">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="20">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="19">
+      <c r="G67" s="20">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="19">
+      <c r="H67" s="20">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="19">
+      <c r="I67" s="20">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="19">
+      <c r="J67" s="20">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="19">
+      <c r="K67" s="20">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="20">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="19">
+      <c r="M67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="19">
+      <c r="N67" s="20">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="19">
+      <c r="O67" s="20">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="19">
+      <c r="P67" s="20">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="19">
+      <c r="Q67" s="20">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="19">
+      <c r="R67" s="20">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3259,7 +3262,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="19">
+      <c r="Z67" s="20">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3352,85 +3355,85 @@
       <c r="A69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="12">
         <f t="shared" ref="B69:S69" si="13">average(B53,B45,B37,B29,B21,B13,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="12">
         <f t="shared" si="13"/>
         <v>0.309525</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="12">
         <f t="shared" si="13"/>
         <v>0.42125</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E69" s="12">
         <f t="shared" si="13"/>
         <v>0.42478</v>
       </c>
-      <c r="F69" s="11">
+      <c r="F69" s="12">
         <f t="shared" si="13"/>
         <v>0.40488</v>
       </c>
-      <c r="G69" s="11">
+      <c r="G69" s="12">
         <f t="shared" si="13"/>
         <v>0.45414</v>
       </c>
-      <c r="H69" s="11">
+      <c r="H69" s="12">
         <f t="shared" si="13"/>
         <v>0.40556</v>
       </c>
-      <c r="I69" s="11">
+      <c r="I69" s="12">
         <f t="shared" si="13"/>
         <v>0.31688</v>
       </c>
-      <c r="J69" s="11">
+      <c r="J69" s="12">
         <f t="shared" si="13"/>
         <v>0.41248</v>
       </c>
-      <c r="K69" s="11">
+      <c r="K69" s="12">
         <f t="shared" si="13"/>
         <v>0.29162</v>
       </c>
-      <c r="L69" s="11">
+      <c r="L69" s="12">
         <f t="shared" si="13"/>
         <v>0.35694</v>
       </c>
-      <c r="M69" s="11">
+      <c r="M69" s="12">
         <f t="shared" si="13"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N69" s="11">
+      <c r="N69" s="12">
         <f t="shared" si="13"/>
         <v>0.26642</v>
       </c>
-      <c r="O69" s="11">
+      <c r="O69" s="12">
         <f t="shared" si="13"/>
         <v>0.2291666667</v>
       </c>
-      <c r="P69" s="11">
+      <c r="P69" s="12">
         <f t="shared" si="13"/>
         <v>0.3634</v>
       </c>
-      <c r="Q69" s="11">
+      <c r="Q69" s="12">
         <f t="shared" si="13"/>
         <v>0.2847571429</v>
       </c>
-      <c r="R69" s="11">
+      <c r="R69" s="12">
         <f t="shared" si="13"/>
         <v>0.15246</v>
       </c>
-      <c r="S69" s="11">
+      <c r="S69" s="12">
         <f t="shared" si="13"/>
         <v>0.08064</v>
       </c>
-      <c r="T69" s="11"/>
+      <c r="T69" s="12"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
-      <c r="Z69" s="11">
+      <c r="Z69" s="12">
         <f>average(R69:Y69)</f>
         <v>0.11655</v>
       </c>
@@ -3439,81 +3442,81 @@
       <c r="A70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="11">
+      <c r="B70" s="12">
         <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="12">
         <f t="shared" si="14"/>
         <v>0.366525</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="12">
         <f t="shared" si="14"/>
         <v>0.30455</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="12">
         <f t="shared" si="14"/>
         <v>0.38494</v>
       </c>
-      <c r="F70" s="11">
+      <c r="F70" s="12">
         <f t="shared" si="14"/>
         <v>0.40984</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G70" s="12">
         <f t="shared" si="14"/>
         <v>0.4393</v>
       </c>
-      <c r="H70" s="11">
+      <c r="H70" s="12">
         <f t="shared" si="14"/>
         <v>0.42082</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I70" s="12">
         <f t="shared" si="14"/>
         <v>0.4131</v>
       </c>
-      <c r="J70" s="11">
+      <c r="J70" s="12">
         <f t="shared" si="14"/>
         <v>0.3999</v>
       </c>
-      <c r="K70" s="11">
+      <c r="K70" s="12">
         <f t="shared" si="14"/>
         <v>0.38592</v>
       </c>
-      <c r="L70" s="11">
+      <c r="L70" s="12">
         <f t="shared" si="14"/>
         <v>0.33754</v>
       </c>
-      <c r="M70" s="11">
+      <c r="M70" s="12">
         <f t="shared" si="14"/>
         <v>0.34014</v>
       </c>
-      <c r="N70" s="11">
+      <c r="N70" s="12">
         <f t="shared" si="14"/>
         <v>0.30044</v>
       </c>
-      <c r="O70" s="11">
+      <c r="O70" s="12">
         <f t="shared" si="14"/>
         <v>0.30184</v>
       </c>
-      <c r="P70" s="11">
+      <c r="P70" s="12">
         <f t="shared" si="14"/>
         <v>0.2368833333</v>
       </c>
-      <c r="Q70" s="11">
+      <c r="Q70" s="12">
         <f t="shared" si="14"/>
         <v>0.3044714286</v>
       </c>
-      <c r="R70" s="11">
+      <c r="R70" s="12">
         <f t="shared" si="14"/>
         <v>0.2830428571</v>
       </c>
-      <c r="S70" s="11">
+      <c r="S70" s="12">
         <f t="shared" si="14"/>
         <v>0.2062</v>
       </c>
-      <c r="T70" s="11">
+      <c r="T70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1515285714</v>
+        <v>0.1261285714</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3526,30 +3529,30 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="1"/>
-      <c r="S79" s="11"/>
+      <c r="S79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="1"/>
-      <c r="S80" s="11"/>
+      <c r="S80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="1"/>
-      <c r="S81" s="11"/>
+      <c r="S81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="1"/>
-      <c r="S82" s="11"/>
+      <c r="S82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="1"/>
-      <c r="S83" s="11"/>
+      <c r="S83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="1"/>
-      <c r="S84" s="11"/>
+      <c r="S84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="S85" s="11"/>
+      <c r="S85" s="12"/>
     </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
@@ -3578,67 +3581,67 @@
       <c r="B109" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="11" t="str">
+      <c r="C109" s="12" t="str">
         <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D109" s="11" t="str">
+      <c r="D109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E109" s="11" t="str">
+      <c r="E109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="11" t="str">
+      <c r="F109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G109" s="11" t="str">
+      <c r="G109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H109" s="11" t="str">
+      <c r="H109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="11" t="str">
+      <c r="I109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J109" s="11" t="str">
+      <c r="J109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K109" s="11" t="str">
+      <c r="K109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L109" s="11" t="str">
+      <c r="L109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M109" s="11" t="str">
+      <c r="M109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N109" s="11" t="str">
+      <c r="N109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O109" s="11" t="str">
+      <c r="O109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P109" s="11" t="str">
+      <c r="P109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q109" s="11" t="str">
+      <c r="Q109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R109" s="11" t="str">
+      <c r="R109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -700,7 +700,7 @@
         <v>0.1923</v>
       </c>
       <c r="S5" s="10">
-        <v>0.0968</v>
+        <v>0.1515</v>
       </c>
       <c r="T5" s="11"/>
       <c r="U5" s="9"/>
@@ -710,7 +710,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="8">
         <f t="shared" si="2"/>
-        <v>0.2452166667</v>
+        <v>0.2543333333</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -772,7 +772,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="13">
-        <v>0.1867</v>
+        <v>0.1831</v>
       </c>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
@@ -781,7 +781,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2586714286</v>
+        <v>0.2581571429</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1098,7 +1098,7 @@
         <v>0.0513</v>
       </c>
       <c r="S13" s="13">
-        <v>0.0435</v>
+        <v>0.16</v>
       </c>
       <c r="T13" s="15"/>
       <c r="W13" s="16"/>
@@ -1163,7 +1163,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="13">
-        <v>0.099</v>
+        <v>0.1188</v>
       </c>
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
@@ -1172,7 +1172,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.2013333333</v>
+        <v>0.2079333333</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1478,7 +1478,9 @@
         <v>0.22</v>
       </c>
       <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
+      <c r="S21" s="13">
+        <v>0.1</v>
+      </c>
       <c r="T21" s="12"/>
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
@@ -1540,7 +1542,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="13">
-        <v>0.0575</v>
+        <v>0.0617</v>
       </c>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
@@ -1549,7 +1551,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1446</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1863,7 +1865,7 @@
       </c>
       <c r="R29" s="12"/>
       <c r="S29" s="13">
-        <v>0.0588</v>
+        <v>0.1111</v>
       </c>
       <c r="T29" s="17"/>
       <c r="U29" s="12"/>
@@ -1930,7 +1932,7 @@
         <v>0.2308</v>
       </c>
       <c r="T30" s="13">
-        <v>0.1591</v>
+        <v>0.1304</v>
       </c>
       <c r="U30" s="12"/>
       <c r="V30" s="12"/>
@@ -1939,7 +1941,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.2398666667</v>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2253,9 +2255,7 @@
       <c r="R37" s="12">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="13">
-        <v>0.1111</v>
-      </c>
+      <c r="S37" s="13"/>
       <c r="T37" s="12"/>
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
@@ -2323,7 +2323,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="13">
-        <v>0.0741</v>
+        <v>0.087</v>
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
@@ -2332,7 +2332,7 @@
       <c r="Y38" s="12"/>
       <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.1715666667</v>
+        <v>0.1758666667</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2505,7 +2505,9 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="12"/>
+      <c r="S45" s="13">
+        <v>0.0714</v>
+      </c>
       <c r="T45" s="12"/>
       <c r="U45" s="12"/>
       <c r="V45" s="12"/>
@@ -2728,7 +2730,7 @@
         <v>0.2857</v>
       </c>
       <c r="S53" s="13">
-        <v>0.093</v>
+        <v>0.122</v>
       </c>
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
@@ -2767,7 +2769,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="13">
-        <v>0.1636</v>
+        <v>0.1504</v>
       </c>
       <c r="U54" s="12"/>
       <c r="V54" s="12"/>
@@ -2776,7 +2778,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.2172</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3425,7 +3427,7 @@
       </c>
       <c r="S69" s="12">
         <f t="shared" si="13"/>
-        <v>0.08064</v>
+        <v>0.1193333333</v>
       </c>
       <c r="T69" s="12"/>
       <c r="U69" s="3"/>
@@ -3435,7 +3437,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="12">
         <f>average(R69:Y69)</f>
-        <v>0.11655</v>
+        <v>0.1358966667</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -3516,7 +3518,7 @@
       </c>
       <c r="T70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1261285714</v>
+        <v>0.1249</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -155,12 +155,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -699,10 +693,10 @@
       <c r="R5" s="8">
         <v>0.1923</v>
       </c>
-      <c r="S5" s="10">
+      <c r="S5" s="8">
         <v>0.1515</v>
       </c>
-      <c r="T5" s="11"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -717,71 +711,73 @@
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>0.5714</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>0.4167</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="10">
         <v>0.3182</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>0.3333</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>0.3429</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="10">
         <v>0.4348</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="10">
         <v>0.4468</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="10">
         <v>0.3462</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="10">
         <v>0.2456</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="10">
         <v>0.2203</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="10">
         <v>0.2537</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="10">
         <v>0.2593</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="10">
         <v>0.2368</v>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="10">
         <v>0.2308</v>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="10">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="10">
         <v>0.3393</v>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="10">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="10">
         <v>0.2745</v>
       </c>
-      <c r="T6" s="13">
+      <c r="T6" s="10">
         <v>0.1831</v>
       </c>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12">
+      <c r="U6" s="11">
+        <v>0.1774</v>
+      </c>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10">
         <f t="shared" si="2"/>
-        <v>0.2581571429</v>
+        <v>0.2480625</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -919,7 +915,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="14"/>
+      <c r="W10" s="12"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -978,7 +974,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="14"/>
+      <c r="W11" s="12"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1036,7 +1032,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="14"/>
+      <c r="W12" s="12"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1097,103 +1093,105 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="13">
+      <c r="S13" s="10">
         <v>0.16</v>
       </c>
-      <c r="T13" s="15"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
+      <c r="T13" s="13"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10">
         <v>0.5161</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="10">
         <v>0.3333</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="10">
         <v>0.34</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="10">
         <v>0.3521</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="10">
         <v>0.4125</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="10">
         <v>0.4321</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="10">
         <v>0.369</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="10">
         <v>0.3194</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="10">
         <v>0.2969</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="10">
         <v>0.32</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="10">
         <v>0.3205</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="10">
         <v>0.3571</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="10">
         <v>0.449</v>
       </c>
-      <c r="P14" s="12">
+      <c r="P14" s="10">
         <v>0.4182</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="Q14" s="10">
         <v>0.3269</v>
       </c>
-      <c r="R14" s="12">
+      <c r="R14" s="10">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S14" s="10">
         <v>0.2339</v>
       </c>
-      <c r="T14" s="13">
+      <c r="T14" s="10">
         <v>0.1188</v>
       </c>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12">
+      <c r="U14" s="11">
+        <v>0.1023</v>
+      </c>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10">
         <f>average(R14:Y14)</f>
-        <v>0.2079333333</v>
+        <v>0.181525</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="S15" s="12"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="12"/>
-      <c r="Z15" s="12"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
@@ -1477,81 +1475,83 @@
       <c r="Q21" s="8">
         <v>0.22</v>
       </c>
-      <c r="R21" s="12"/>
-      <c r="S21" s="13">
+      <c r="R21" s="10"/>
+      <c r="S21" s="10">
         <v>0.1</v>
       </c>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
       <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10">
         <v>0.5</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="10">
         <v>0.5625</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="10">
         <v>0.5714</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="10">
         <v>0.4815</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="10">
         <v>0.4634</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="10">
         <v>0.4898</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="10">
         <v>0.463</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="10">
         <v>0.377</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="10">
         <v>0.3387</v>
       </c>
-      <c r="N22" s="12">
+      <c r="N22" s="10">
         <v>0.3265</v>
       </c>
-      <c r="O22" s="12">
+      <c r="O22" s="10">
         <v>0.3056</v>
       </c>
-      <c r="P22" s="12">
+      <c r="P22" s="10">
         <v>0.2075</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="10">
         <v>0.2615</v>
       </c>
-      <c r="R22" s="12">
+      <c r="R22" s="10">
         <v>0.232</v>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="10">
         <v>0.1443</v>
       </c>
-      <c r="T22" s="13">
+      <c r="T22" s="10">
         <v>0.0617</v>
       </c>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12">
+      <c r="U22" s="11">
+        <v>0.08</v>
+      </c>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10">
         <f>average(R22:Y22)</f>
-        <v>0.146</v>
+        <v>0.1295</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1748,7 +1748,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="14"/>
+      <c r="W27" s="12"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1806,8 +1806,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="15"/>
-      <c r="W28" s="14"/>
+      <c r="T28" s="13"/>
+      <c r="W28" s="12"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1863,85 +1863,87 @@
       <c r="Q29" s="8">
         <v>0.2759</v>
       </c>
-      <c r="R29" s="12"/>
-      <c r="S29" s="13">
+      <c r="R29" s="10"/>
+      <c r="S29" s="10">
         <v>0.1111</v>
       </c>
-      <c r="T29" s="17"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
       <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10">
         <v>0.1333</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="10">
         <v>0.1667</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="10">
         <v>0.3514</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="10">
         <v>0.375</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="10">
         <v>0.3778</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="10">
         <v>0.3226</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="10">
         <v>0.4359</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="10">
         <v>0.4286</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="10">
         <v>0.4366</v>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="10">
         <v>0.3457</v>
       </c>
-      <c r="M30" s="12">
+      <c r="M30" s="10">
         <v>0.3222</v>
       </c>
-      <c r="N30" s="12">
+      <c r="N30" s="10">
         <v>0.2568</v>
       </c>
-      <c r="O30" s="12">
+      <c r="O30" s="10">
         <v>0.1905</v>
       </c>
-      <c r="P30" s="12">
+      <c r="P30" s="10">
         <v>0.2281</v>
       </c>
-      <c r="Q30" s="12">
+      <c r="Q30" s="10">
         <v>0.3243</v>
       </c>
-      <c r="R30" s="12">
+      <c r="R30" s="10">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="12">
+      <c r="S30" s="10">
         <v>0.2308</v>
       </c>
-      <c r="T30" s="13">
+      <c r="T30" s="10">
         <v>0.1304</v>
       </c>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12">
+      <c r="U30" s="11">
+        <v>0.102</v>
+      </c>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10">
         <f>average(R30:Y30)</f>
-        <v>0.2303</v>
+        <v>0.198225</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2066,7 +2068,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="14"/>
+      <c r="N34" s="12"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2252,87 +2254,89 @@
       <c r="Q37" s="8">
         <v>0.303</v>
       </c>
-      <c r="R37" s="12">
+      <c r="R37" s="10">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="13"/>
-      <c r="T37" s="12"/>
-      <c r="U37" s="12"/>
-      <c r="V37" s="12"/>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="10"/>
       <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="10">
         <v>0.4375</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="10">
         <v>0.4</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="10">
         <v>0.4</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="10">
         <v>0.4</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="10">
         <v>0.4167</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="10">
         <v>0.4</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="10">
         <v>0.4211</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="10">
         <v>0.451</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="10">
         <v>0.5161</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K38" s="10">
         <v>0.5128</v>
       </c>
-      <c r="L38" s="12">
+      <c r="L38" s="10">
         <v>0.3913</v>
       </c>
-      <c r="M38" s="12">
+      <c r="M38" s="10">
         <v>0.46</v>
       </c>
-      <c r="N38" s="12">
+      <c r="N38" s="10">
         <v>0.325</v>
       </c>
-      <c r="O38" s="12">
+      <c r="O38" s="10">
         <v>0.3333</v>
       </c>
-      <c r="P38" s="12">
+      <c r="P38" s="10">
         <v>0.2564</v>
       </c>
-      <c r="Q38" s="12">
+      <c r="Q38" s="10">
         <v>0.3238</v>
       </c>
-      <c r="R38" s="12">
+      <c r="R38" s="10">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="10">
         <v>0.1974</v>
       </c>
-      <c r="T38" s="13">
+      <c r="T38" s="10">
         <v>0.087</v>
       </c>
-      <c r="U38" s="12"/>
-      <c r="V38" s="12"/>
-      <c r="W38" s="12"/>
-      <c r="X38" s="12"/>
-      <c r="Y38" s="12"/>
-      <c r="Z38" s="12">
+      <c r="U38" s="11">
+        <v>0.0833</v>
+      </c>
+      <c r="V38" s="10"/>
+      <c r="W38" s="10"/>
+      <c r="X38" s="10"/>
+      <c r="Y38" s="10"/>
+      <c r="Z38" s="10">
         <f>average(R38:Y38)</f>
-        <v>0.1758666667</v>
+        <v>0.152725</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2461,7 +2465,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="14"/>
+      <c r="L44" s="12"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2487,7 +2491,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="18"/>
+      <c r="I45" s="16"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2505,63 +2509,65 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="13">
+      <c r="S45" s="10">
         <v>0.0714</v>
       </c>
-      <c r="T45" s="12"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="12"/>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12"/>
-      <c r="Y45" s="12"/>
-      <c r="Z45" s="12"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="10"/>
+      <c r="X45" s="10"/>
+      <c r="Y45" s="10"/>
+      <c r="Z45" s="10"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10">
         <v>0.1111</v>
       </c>
-      <c r="Q46" s="12">
+      <c r="Q46" s="10">
         <v>0.2828</v>
       </c>
-      <c r="R46" s="12">
+      <c r="R46" s="10">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="12">
+      <c r="S46" s="10">
         <v>0.1705</v>
       </c>
-      <c r="T46" s="13">
+      <c r="T46" s="10">
         <v>0.1429</v>
       </c>
-      <c r="U46" s="12"/>
-      <c r="V46" s="12"/>
-      <c r="W46" s="12"/>
-      <c r="X46" s="12"/>
-      <c r="Y46" s="12"/>
-      <c r="Z46" s="12">
+      <c r="U46" s="11">
+        <v>0.1136</v>
+      </c>
+      <c r="V46" s="10"/>
+      <c r="W46" s="10"/>
+      <c r="X46" s="10"/>
+      <c r="Y46" s="10"/>
+      <c r="Z46" s="10">
         <f>average(R46:Y46)</f>
-        <v>0.1933666667</v>
+        <v>0.173425</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="Q47" s="12"/>
-      <c r="R47" s="12"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
@@ -2729,56 +2735,58 @@
       <c r="R53" s="8">
         <v>0.2857</v>
       </c>
-      <c r="S53" s="13">
+      <c r="S53" s="10">
         <v>0.122</v>
       </c>
-      <c r="T53" s="12"/>
-      <c r="U53" s="12"/>
-      <c r="V53" s="12"/>
-      <c r="W53" s="12"/>
-      <c r="X53" s="12"/>
-      <c r="Y53" s="12"/>
-      <c r="Z53" s="12"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Y53" s="10"/>
+      <c r="Z53" s="10"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="N54" s="12"/>
-      <c r="O54" s="12"/>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="12">
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10">
         <v>0.2727</v>
       </c>
-      <c r="R54" s="12">
+      <c r="R54" s="10">
         <v>0.296</v>
       </c>
-      <c r="S54" s="12">
+      <c r="S54" s="10">
         <v>0.192</v>
       </c>
-      <c r="T54" s="13">
+      <c r="T54" s="10">
         <v>0.1504</v>
       </c>
-      <c r="U54" s="12"/>
-      <c r="V54" s="12"/>
-      <c r="W54" s="12"/>
-      <c r="X54" s="12"/>
-      <c r="Y54" s="12"/>
-      <c r="Z54" s="12">
+      <c r="U54" s="11">
+        <v>0.1359</v>
+      </c>
+      <c r="V54" s="10"/>
+      <c r="W54" s="10"/>
+      <c r="X54" s="10"/>
+      <c r="Y54" s="10"/>
+      <c r="Z54" s="10">
         <f>average(R54:Y54)</f>
-        <v>0.2128</v>
+        <v>0.193575</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -2818,7 +2826,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="14"/>
+      <c r="L58" s="12"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -2860,57 +2868,57 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12"/>
-      <c r="L61" s="12"/>
-      <c r="M61" s="12"/>
-      <c r="N61" s="12"/>
-      <c r="O61" s="12"/>
-      <c r="P61" s="12"/>
-      <c r="Q61" s="12"/>
-      <c r="R61" s="12"/>
-      <c r="S61" s="12"/>
-      <c r="T61" s="12"/>
-      <c r="U61" s="12"/>
-      <c r="V61" s="12"/>
-      <c r="W61" s="12"/>
-      <c r="X61" s="12"/>
-      <c r="Y61" s="12"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
+      <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
+      <c r="X61" s="10"/>
+      <c r="Y61" s="10"/>
       <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="12"/>
-      <c r="L62" s="12"/>
-      <c r="M62" s="12"/>
-      <c r="N62" s="12"/>
-      <c r="O62" s="12"/>
-      <c r="P62" s="12"/>
-      <c r="Q62" s="12"/>
-      <c r="R62" s="12"/>
-      <c r="S62" s="12"/>
-      <c r="T62" s="12"/>
-      <c r="U62" s="12"/>
-      <c r="V62" s="12"/>
-      <c r="W62" s="12"/>
-      <c r="X62" s="12"/>
-      <c r="Y62" s="12"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="10"/>
+      <c r="X62" s="10"/>
+      <c r="Y62" s="10"/>
       <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -3089,8 +3097,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
+      <c r="S65" s="17"/>
+      <c r="T65" s="17"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3189,71 +3197,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="18">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="18">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="18">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="18">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="18">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="18">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="20">
+      <c r="I67" s="18">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J67" s="18">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="20">
+      <c r="K67" s="18">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="20">
+      <c r="L67" s="18">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="20">
+      <c r="M67" s="18">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="20">
+      <c r="N67" s="18">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="20">
+      <c r="O67" s="18">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="20">
+      <c r="P67" s="18">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="20">
+      <c r="Q67" s="18">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="20">
+      <c r="R67" s="18">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3264,7 +3272,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="20">
+      <c r="Z67" s="18">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3357,85 +3365,85 @@
       <c r="A69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="10">
         <f t="shared" ref="B69:S69" si="13">average(B53,B45,B37,B29,B21,B13,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="10">
         <f t="shared" si="13"/>
         <v>0.309525</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="10">
         <f t="shared" si="13"/>
         <v>0.42125</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="10">
         <f t="shared" si="13"/>
         <v>0.42478</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="10">
         <f t="shared" si="13"/>
         <v>0.40488</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="10">
         <f t="shared" si="13"/>
         <v>0.45414</v>
       </c>
-      <c r="H69" s="12">
+      <c r="H69" s="10">
         <f t="shared" si="13"/>
         <v>0.40556</v>
       </c>
-      <c r="I69" s="12">
+      <c r="I69" s="10">
         <f t="shared" si="13"/>
         <v>0.31688</v>
       </c>
-      <c r="J69" s="12">
+      <c r="J69" s="10">
         <f t="shared" si="13"/>
         <v>0.41248</v>
       </c>
-      <c r="K69" s="12">
+      <c r="K69" s="10">
         <f t="shared" si="13"/>
         <v>0.29162</v>
       </c>
-      <c r="L69" s="12">
+      <c r="L69" s="10">
         <f t="shared" si="13"/>
         <v>0.35694</v>
       </c>
-      <c r="M69" s="12">
+      <c r="M69" s="10">
         <f t="shared" si="13"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N69" s="12">
+      <c r="N69" s="10">
         <f t="shared" si="13"/>
         <v>0.26642</v>
       </c>
-      <c r="O69" s="12">
+      <c r="O69" s="10">
         <f t="shared" si="13"/>
         <v>0.2291666667</v>
       </c>
-      <c r="P69" s="12">
+      <c r="P69" s="10">
         <f t="shared" si="13"/>
         <v>0.3634</v>
       </c>
-      <c r="Q69" s="12">
+      <c r="Q69" s="10">
         <f t="shared" si="13"/>
         <v>0.2847571429</v>
       </c>
-      <c r="R69" s="12">
+      <c r="R69" s="10">
         <f t="shared" si="13"/>
         <v>0.15246</v>
       </c>
-      <c r="S69" s="12">
+      <c r="S69" s="10">
         <f t="shared" si="13"/>
         <v>0.1193333333</v>
       </c>
-      <c r="T69" s="12"/>
+      <c r="T69" s="10"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
-      <c r="Z69" s="12">
+      <c r="Z69" s="10">
         <f>average(R69:Y69)</f>
         <v>0.1358966667</v>
       </c>
@@ -3444,79 +3452,79 @@
       <c r="A70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="10">
         <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="10">
         <f t="shared" si="14"/>
         <v>0.366525</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="10">
         <f t="shared" si="14"/>
         <v>0.30455</v>
       </c>
-      <c r="E70" s="12">
+      <c r="E70" s="10">
         <f t="shared" si="14"/>
         <v>0.38494</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="10">
         <f t="shared" si="14"/>
         <v>0.40984</v>
       </c>
-      <c r="G70" s="12">
+      <c r="G70" s="10">
         <f t="shared" si="14"/>
         <v>0.4393</v>
       </c>
-      <c r="H70" s="12">
+      <c r="H70" s="10">
         <f t="shared" si="14"/>
         <v>0.42082</v>
       </c>
-      <c r="I70" s="12">
+      <c r="I70" s="10">
         <f t="shared" si="14"/>
         <v>0.4131</v>
       </c>
-      <c r="J70" s="12">
+      <c r="J70" s="10">
         <f t="shared" si="14"/>
         <v>0.3999</v>
       </c>
-      <c r="K70" s="12">
+      <c r="K70" s="10">
         <f t="shared" si="14"/>
         <v>0.38592</v>
       </c>
-      <c r="L70" s="12">
+      <c r="L70" s="10">
         <f t="shared" si="14"/>
         <v>0.33754</v>
       </c>
-      <c r="M70" s="12">
+      <c r="M70" s="10">
         <f t="shared" si="14"/>
         <v>0.34014</v>
       </c>
-      <c r="N70" s="12">
+      <c r="N70" s="10">
         <f t="shared" si="14"/>
         <v>0.30044</v>
       </c>
-      <c r="O70" s="12">
+      <c r="O70" s="10">
         <f t="shared" si="14"/>
         <v>0.30184</v>
       </c>
-      <c r="P70" s="12">
+      <c r="P70" s="10">
         <f t="shared" si="14"/>
         <v>0.2368833333</v>
       </c>
-      <c r="Q70" s="12">
+      <c r="Q70" s="10">
         <f t="shared" si="14"/>
         <v>0.3044714286</v>
       </c>
-      <c r="R70" s="12">
+      <c r="R70" s="10">
         <f t="shared" si="14"/>
         <v>0.2830428571</v>
       </c>
-      <c r="S70" s="12">
+      <c r="S70" s="10">
         <f t="shared" si="14"/>
         <v>0.2062</v>
       </c>
-      <c r="T70" s="12">
+      <c r="T70" s="10">
         <f t="shared" si="14"/>
         <v>0.1249</v>
       </c>
@@ -3531,30 +3539,30 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="1"/>
-      <c r="S79" s="12"/>
+      <c r="S79" s="10"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="1"/>
-      <c r="S80" s="12"/>
+      <c r="S80" s="10"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="1"/>
-      <c r="S81" s="12"/>
+      <c r="S81" s="10"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="1"/>
-      <c r="S82" s="12"/>
+      <c r="S82" s="10"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="1"/>
-      <c r="S83" s="12"/>
+      <c r="S83" s="10"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="1"/>
-      <c r="S84" s="12"/>
+      <c r="S84" s="10"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="S85" s="12"/>
+      <c r="S85" s="10"/>
     </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
@@ -3583,67 +3591,67 @@
       <c r="B109" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="12" t="str">
+      <c r="C109" s="10" t="str">
         <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D109" s="12" t="str">
+      <c r="D109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E109" s="12" t="str">
+      <c r="E109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="12" t="str">
+      <c r="F109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G109" s="12" t="str">
+      <c r="G109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H109" s="12" t="str">
+      <c r="H109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="12" t="str">
+      <c r="I109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J109" s="12" t="str">
+      <c r="J109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K109" s="12" t="str">
+      <c r="K109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L109" s="12" t="str">
+      <c r="L109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M109" s="12" t="str">
+      <c r="M109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N109" s="12" t="str">
+      <c r="N109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O109" s="12" t="str">
+      <c r="O109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P109" s="12" t="str">
+      <c r="P109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q109" s="12" t="str">
+      <c r="Q109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R109" s="12" t="str">
+      <c r="R109" s="10" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -1543,7 +1543,7 @@
         <v>0.0617</v>
       </c>
       <c r="U22" s="11">
-        <v>0.08</v>
+        <v>0.0986</v>
       </c>
       <c r="V22" s="10"/>
       <c r="W22" s="10"/>
@@ -1551,7 +1551,7 @@
       <c r="Y22" s="10"/>
       <c r="Z22" s="10">
         <f>average(R22:Y22)</f>
-        <v>0.1295</v>
+        <v>0.13415</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1935,7 +1935,7 @@
         <v>0.1304</v>
       </c>
       <c r="U30" s="11">
-        <v>0.102</v>
+        <v>0.08</v>
       </c>
       <c r="V30" s="10"/>
       <c r="W30" s="10"/>
@@ -1943,7 +1943,7 @@
       <c r="Y30" s="10"/>
       <c r="Z30" s="10">
         <f>average(R30:Y30)</f>
-        <v>0.198225</v>
+        <v>0.192725</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2328,7 +2328,7 @@
         <v>0.087</v>
       </c>
       <c r="U38" s="11">
-        <v>0.0833</v>
+        <v>0.1</v>
       </c>
       <c r="V38" s="10"/>
       <c r="W38" s="10"/>
@@ -2336,7 +2336,7 @@
       <c r="Y38" s="10"/>
       <c r="Z38" s="10">
         <f>average(R38:Y38)</f>
-        <v>0.152725</v>
+        <v>0.1569</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2554,7 +2554,7 @@
         <v>0.1429</v>
       </c>
       <c r="U46" s="11">
-        <v>0.1136</v>
+        <v>0.05</v>
       </c>
       <c r="V46" s="10"/>
       <c r="W46" s="10"/>
@@ -2562,7 +2562,7 @@
       <c r="Y46" s="10"/>
       <c r="Z46" s="10">
         <f>average(R46:Y46)</f>
-        <v>0.173425</v>
+        <v>0.157525</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2778,7 +2778,7 @@
         <v>0.1504</v>
       </c>
       <c r="U54" s="11">
-        <v>0.1359</v>
+        <v>0.1327</v>
       </c>
       <c r="V54" s="10"/>
       <c r="W54" s="10"/>
@@ -2786,7 +2786,7 @@
       <c r="Y54" s="10"/>
       <c r="Z54" s="10">
         <f>average(R54:Y54)</f>
-        <v>0.193575</v>
+        <v>0.192775</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3453,7 +3453,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="10">
-        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <f t="shared" ref="B70:U70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
       <c r="C70" s="10">
@@ -3527,6 +3527,10 @@
       <c r="T70" s="10">
         <f t="shared" si="14"/>
         <v>0.1249</v>
+      </c>
+      <c r="U70" s="10">
+        <f t="shared" si="14"/>
+        <v>0.1058571429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -155,6 +155,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -693,10 +699,10 @@
       <c r="R5" s="8">
         <v>0.1923</v>
       </c>
-      <c r="S5" s="8">
+      <c r="S5" s="10">
         <v>0.1515</v>
       </c>
-      <c r="T5" s="9"/>
+      <c r="T5" s="11"/>
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -711,73 +717,71 @@
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="12">
         <v>0.5714</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="12">
         <v>0.4167</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="12">
         <v>0.3182</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="12">
         <v>0.3333</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="12">
         <v>0.3429</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="12">
         <v>0.4348</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="12">
         <v>0.4468</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="12">
         <v>0.3462</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="12">
         <v>0.2456</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="12">
         <v>0.2203</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="12">
         <v>0.2537</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="12">
         <v>0.2593</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="12">
         <v>0.2368</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="12">
         <v>0.2308</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="12">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="12">
         <v>0.3393</v>
       </c>
-      <c r="R6" s="10">
+      <c r="R6" s="12">
         <v>0.3426</v>
       </c>
-      <c r="S6" s="10">
+      <c r="S6" s="12">
         <v>0.2745</v>
       </c>
-      <c r="T6" s="10">
-        <v>0.1831</v>
-      </c>
-      <c r="U6" s="11">
-        <v>0.1774</v>
-      </c>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10">
+      <c r="T6" s="13">
+        <v>0.1538</v>
+      </c>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2480625</v>
+        <v>0.2539714286</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -915,7 +919,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="12"/>
+      <c r="W10" s="14"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -974,7 +978,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="12"/>
+      <c r="W11" s="14"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1032,7 +1036,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="12"/>
+      <c r="W12" s="14"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1093,105 +1097,103 @@
       <c r="R13" s="8">
         <v>0.0513</v>
       </c>
-      <c r="S13" s="10">
+      <c r="S13" s="13">
         <v>0.16</v>
       </c>
-      <c r="T13" s="13"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
+      <c r="T13" s="15"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12">
         <v>0.5161</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="12">
         <v>0.3333</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="12">
         <v>0.34</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="12">
         <v>0.3521</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="12">
         <v>0.4125</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="12">
         <v>0.4321</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="12">
         <v>0.369</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="12">
         <v>0.3194</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="12">
         <v>0.2969</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="12">
         <v>0.32</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="12">
         <v>0.3205</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="12">
         <v>0.3571</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="12">
         <v>0.449</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="12">
         <v>0.4182</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="12">
         <v>0.3269</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="12">
         <v>0.2711</v>
       </c>
-      <c r="S14" s="10">
+      <c r="S14" s="12">
         <v>0.2339</v>
       </c>
-      <c r="T14" s="10">
-        <v>0.1188</v>
-      </c>
-      <c r="U14" s="11">
-        <v>0.1023</v>
-      </c>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10">
+      <c r="T14" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.181525</v>
+        <v>0.2016666667</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="S15" s="10"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
@@ -1475,83 +1477,81 @@
       <c r="Q21" s="8">
         <v>0.22</v>
       </c>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10">
+      <c r="R21" s="12"/>
+      <c r="S21" s="13">
         <v>0.1</v>
       </c>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
-      <c r="Y21" s="10"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
       <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12">
         <v>0.5</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="12">
         <v>0.5625</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="12">
         <v>0.5714</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="12">
         <v>0.4815</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="12">
         <v>0.4634</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="12">
         <v>0.4898</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="12">
         <v>0.463</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="12">
         <v>0.377</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="12">
         <v>0.3387</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="12">
         <v>0.3265</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="12">
         <v>0.3056</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="12">
         <v>0.2075</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="12">
         <v>0.2615</v>
       </c>
-      <c r="R22" s="10">
+      <c r="R22" s="12">
         <v>0.232</v>
       </c>
-      <c r="S22" s="10">
+      <c r="S22" s="12">
         <v>0.1443</v>
       </c>
-      <c r="T22" s="10">
-        <v>0.0617</v>
-      </c>
-      <c r="U22" s="11">
-        <v>0.0986</v>
-      </c>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10">
+      <c r="T22" s="13">
+        <v>0.1014</v>
+      </c>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.13415</v>
+        <v>0.1592333333</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1748,7 +1748,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="12"/>
+      <c r="W27" s="14"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1806,8 +1806,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="13"/>
-      <c r="W28" s="12"/>
+      <c r="T28" s="15"/>
+      <c r="W28" s="14"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1863,87 +1863,85 @@
       <c r="Q29" s="8">
         <v>0.2759</v>
       </c>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10">
+      <c r="R29" s="12"/>
+      <c r="S29" s="13">
         <v>0.1111</v>
       </c>
-      <c r="T29" s="15"/>
-      <c r="U29" s="10"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10"/>
-      <c r="X29" s="10"/>
-      <c r="Y29" s="10"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
       <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12">
         <v>0.1333</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="12">
         <v>0.1667</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="12">
         <v>0.3514</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="12">
         <v>0.375</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="12">
         <v>0.3778</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="12">
         <v>0.3226</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="12">
         <v>0.4359</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="12">
         <v>0.4286</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="12">
         <v>0.4366</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="12">
         <v>0.3457</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="12">
         <v>0.3222</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="12">
         <v>0.2568</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="12">
         <v>0.1905</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="12">
         <v>0.2281</v>
       </c>
-      <c r="Q30" s="10">
+      <c r="Q30" s="12">
         <v>0.3243</v>
       </c>
-      <c r="R30" s="10">
+      <c r="R30" s="12">
         <v>0.3297</v>
       </c>
-      <c r="S30" s="10">
+      <c r="S30" s="12">
         <v>0.2308</v>
       </c>
-      <c r="T30" s="10">
-        <v>0.1304</v>
-      </c>
-      <c r="U30" s="11">
-        <v>0.08</v>
-      </c>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10"/>
-      <c r="Y30" s="10"/>
-      <c r="Z30" s="10">
+      <c r="T30" s="13">
+        <v>0.0784</v>
+      </c>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.192725</v>
+        <v>0.2129666667</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2068,7 +2066,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="12"/>
+      <c r="N34" s="14"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2254,89 +2252,87 @@
       <c r="Q37" s="8">
         <v>0.303</v>
       </c>
-      <c r="R37" s="10">
+      <c r="R37" s="12">
         <v>0.0606</v>
       </c>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
-      <c r="U37" s="10"/>
-      <c r="V37" s="10"/>
-      <c r="W37" s="10"/>
-      <c r="X37" s="10"/>
-      <c r="Y37" s="10"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
       <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="12">
         <v>0.4375</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="12">
         <v>0.4</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="12">
         <v>0.4</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="12">
         <v>0.4</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="12">
         <v>0.4167</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="12">
         <v>0.4</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="12">
         <v>0.4211</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="12">
         <v>0.451</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J38" s="12">
         <v>0.5161</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="12">
         <v>0.5128</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38" s="12">
         <v>0.3913</v>
       </c>
-      <c r="M38" s="10">
+      <c r="M38" s="12">
         <v>0.46</v>
       </c>
-      <c r="N38" s="10">
+      <c r="N38" s="12">
         <v>0.325</v>
       </c>
-      <c r="O38" s="10">
+      <c r="O38" s="12">
         <v>0.3333</v>
       </c>
-      <c r="P38" s="10">
+      <c r="P38" s="12">
         <v>0.2564</v>
       </c>
-      <c r="Q38" s="10">
+      <c r="Q38" s="12">
         <v>0.3238</v>
       </c>
-      <c r="R38" s="10">
+      <c r="R38" s="12">
         <v>0.2432</v>
       </c>
-      <c r="S38" s="10">
+      <c r="S38" s="12">
         <v>0.1974</v>
       </c>
-      <c r="T38" s="10">
-        <v>0.087</v>
-      </c>
-      <c r="U38" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="V38" s="10"/>
-      <c r="W38" s="10"/>
-      <c r="X38" s="10"/>
-      <c r="Y38" s="10"/>
-      <c r="Z38" s="10">
+      <c r="T38" s="13">
+        <v>0.125</v>
+      </c>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.1569</v>
+        <v>0.1885333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2465,7 +2461,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="12"/>
+      <c r="L44" s="14"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2491,7 +2487,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="16"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2509,65 +2505,63 @@
       <c r="R45" s="8">
         <v>0.1724</v>
       </c>
-      <c r="S45" s="10">
+      <c r="S45" s="13">
         <v>0.0714</v>
       </c>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="10"/>
-      <c r="Y45" s="10"/>
-      <c r="Z45" s="10"/>
+      <c r="T45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="12"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12">
         <v>0.1111</v>
       </c>
-      <c r="Q46" s="10">
+      <c r="Q46" s="12">
         <v>0.2828</v>
       </c>
-      <c r="R46" s="10">
+      <c r="R46" s="12">
         <v>0.2667</v>
       </c>
-      <c r="S46" s="10">
+      <c r="S46" s="12">
         <v>0.1705</v>
       </c>
-      <c r="T46" s="10">
-        <v>0.1429</v>
-      </c>
-      <c r="U46" s="11">
+      <c r="T46" s="13">
         <v>0.05</v>
       </c>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
-      <c r="X46" s="10"/>
-      <c r="Y46" s="10"/>
-      <c r="Z46" s="10">
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.157525</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
+      <c r="Q47" s="12"/>
+      <c r="R47" s="12"/>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
@@ -2735,58 +2729,56 @@
       <c r="R53" s="8">
         <v>0.2857</v>
       </c>
-      <c r="S53" s="10">
+      <c r="S53" s="13">
         <v>0.122</v>
       </c>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="X53" s="10"/>
-      <c r="Y53" s="10"/>
-      <c r="Z53" s="10"/>
+      <c r="T53" s="12"/>
+      <c r="U53" s="12"/>
+      <c r="V53" s="12"/>
+      <c r="W53" s="12"/>
+      <c r="X53" s="12"/>
+      <c r="Y53" s="12"/>
+      <c r="Z53" s="12"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10">
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12"/>
+      <c r="Q54" s="12">
         <v>0.2727</v>
       </c>
-      <c r="R54" s="10">
+      <c r="R54" s="12">
         <v>0.296</v>
       </c>
-      <c r="S54" s="10">
+      <c r="S54" s="12">
         <v>0.192</v>
       </c>
-      <c r="T54" s="10">
-        <v>0.1504</v>
-      </c>
-      <c r="U54" s="11">
-        <v>0.1327</v>
-      </c>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
-      <c r="X54" s="10"/>
-      <c r="Y54" s="10"/>
-      <c r="Z54" s="10">
+      <c r="T54" s="13">
+        <v>0.125</v>
+      </c>
+      <c r="U54" s="12"/>
+      <c r="V54" s="12"/>
+      <c r="W54" s="12"/>
+      <c r="X54" s="12"/>
+      <c r="Y54" s="12"/>
+      <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.192775</v>
+        <v>0.2043333333</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -2826,7 +2818,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="12"/>
+      <c r="L58" s="14"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -2868,57 +2860,57 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
-      <c r="V61" s="10"/>
-      <c r="W61" s="10"/>
-      <c r="X61" s="10"/>
-      <c r="Y61" s="10"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="P61" s="12"/>
+      <c r="Q61" s="12"/>
+      <c r="R61" s="12"/>
+      <c r="S61" s="12"/>
+      <c r="T61" s="12"/>
+      <c r="U61" s="12"/>
+      <c r="V61" s="12"/>
+      <c r="W61" s="12"/>
+      <c r="X61" s="12"/>
+      <c r="Y61" s="12"/>
       <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
-      <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-      <c r="Q62" s="10"/>
-      <c r="R62" s="10"/>
-      <c r="S62" s="10"/>
-      <c r="T62" s="10"/>
-      <c r="U62" s="10"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="10"/>
-      <c r="X62" s="10"/>
-      <c r="Y62" s="10"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="12"/>
+      <c r="S62" s="12"/>
+      <c r="T62" s="12"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
       <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -3097,8 +3089,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="17"/>
-      <c r="T65" s="17"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3197,71 +3189,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="20">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C67" s="20">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="18">
+      <c r="D67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="18">
+      <c r="E67" s="20">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="18">
+      <c r="F67" s="20">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="18">
+      <c r="G67" s="20">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="18">
+      <c r="H67" s="20">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="18">
+      <c r="I67" s="20">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="18">
+      <c r="J67" s="20">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="18">
+      <c r="K67" s="20">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="18">
+      <c r="L67" s="20">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="18">
+      <c r="M67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="18">
+      <c r="N67" s="20">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="18">
+      <c r="O67" s="20">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="18">
+      <c r="P67" s="20">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="18">
+      <c r="Q67" s="20">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="18">
+      <c r="R67" s="20">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3272,7 +3264,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="18">
+      <c r="Z67" s="20">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3365,85 +3357,85 @@
       <c r="A69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="12">
         <f t="shared" ref="B69:S69" si="13">average(B53,B45,B37,B29,B21,B13,B5)</f>
         <v>0.3444333333</v>
       </c>
-      <c r="C69" s="10">
+      <c r="C69" s="12">
         <f t="shared" si="13"/>
         <v>0.309525</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="12">
         <f t="shared" si="13"/>
         <v>0.42125</v>
       </c>
-      <c r="E69" s="10">
+      <c r="E69" s="12">
         <f t="shared" si="13"/>
         <v>0.42478</v>
       </c>
-      <c r="F69" s="10">
+      <c r="F69" s="12">
         <f t="shared" si="13"/>
         <v>0.40488</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G69" s="12">
         <f t="shared" si="13"/>
         <v>0.45414</v>
       </c>
-      <c r="H69" s="10">
+      <c r="H69" s="12">
         <f t="shared" si="13"/>
         <v>0.40556</v>
       </c>
-      <c r="I69" s="10">
+      <c r="I69" s="12">
         <f t="shared" si="13"/>
         <v>0.31688</v>
       </c>
-      <c r="J69" s="10">
+      <c r="J69" s="12">
         <f t="shared" si="13"/>
         <v>0.41248</v>
       </c>
-      <c r="K69" s="10">
+      <c r="K69" s="12">
         <f t="shared" si="13"/>
         <v>0.29162</v>
       </c>
-      <c r="L69" s="10">
+      <c r="L69" s="12">
         <f t="shared" si="13"/>
         <v>0.35694</v>
       </c>
-      <c r="M69" s="10">
+      <c r="M69" s="12">
         <f t="shared" si="13"/>
         <v>0.3687333333</v>
       </c>
-      <c r="N69" s="10">
+      <c r="N69" s="12">
         <f t="shared" si="13"/>
         <v>0.26642</v>
       </c>
-      <c r="O69" s="10">
+      <c r="O69" s="12">
         <f t="shared" si="13"/>
         <v>0.2291666667</v>
       </c>
-      <c r="P69" s="10">
+      <c r="P69" s="12">
         <f t="shared" si="13"/>
         <v>0.3634</v>
       </c>
-      <c r="Q69" s="10">
+      <c r="Q69" s="12">
         <f t="shared" si="13"/>
         <v>0.2847571429</v>
       </c>
-      <c r="R69" s="10">
+      <c r="R69" s="12">
         <f t="shared" si="13"/>
         <v>0.15246</v>
       </c>
-      <c r="S69" s="10">
+      <c r="S69" s="12">
         <f t="shared" si="13"/>
         <v>0.1193333333</v>
       </c>
-      <c r="T69" s="10"/>
+      <c r="T69" s="12"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
-      <c r="Z69" s="10">
+      <c r="Z69" s="12">
         <f>average(R69:Y69)</f>
         <v>0.1358966667</v>
       </c>
@@ -3452,85 +3444,81 @@
       <c r="A70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="10">
-        <f t="shared" ref="B70:U70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+      <c r="B70" s="12">
+        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
-      <c r="C70" s="10">
+      <c r="C70" s="12">
         <f t="shared" si="14"/>
         <v>0.366525</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="12">
         <f t="shared" si="14"/>
         <v>0.30455</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="12">
         <f t="shared" si="14"/>
         <v>0.38494</v>
       </c>
-      <c r="F70" s="10">
+      <c r="F70" s="12">
         <f t="shared" si="14"/>
         <v>0.40984</v>
       </c>
-      <c r="G70" s="10">
+      <c r="G70" s="12">
         <f t="shared" si="14"/>
         <v>0.4393</v>
       </c>
-      <c r="H70" s="10">
+      <c r="H70" s="12">
         <f t="shared" si="14"/>
         <v>0.42082</v>
       </c>
-      <c r="I70" s="10">
+      <c r="I70" s="12">
         <f t="shared" si="14"/>
         <v>0.4131</v>
       </c>
-      <c r="J70" s="10">
+      <c r="J70" s="12">
         <f t="shared" si="14"/>
         <v>0.3999</v>
       </c>
-      <c r="K70" s="10">
+      <c r="K70" s="12">
         <f t="shared" si="14"/>
         <v>0.38592</v>
       </c>
-      <c r="L70" s="10">
+      <c r="L70" s="12">
         <f t="shared" si="14"/>
         <v>0.33754</v>
       </c>
-      <c r="M70" s="10">
+      <c r="M70" s="12">
         <f t="shared" si="14"/>
         <v>0.34014</v>
       </c>
-      <c r="N70" s="10">
+      <c r="N70" s="12">
         <f t="shared" si="14"/>
         <v>0.30044</v>
       </c>
-      <c r="O70" s="10">
+      <c r="O70" s="12">
         <f t="shared" si="14"/>
         <v>0.30184</v>
       </c>
-      <c r="P70" s="10">
+      <c r="P70" s="12">
         <f t="shared" si="14"/>
         <v>0.2368833333</v>
       </c>
-      <c r="Q70" s="10">
+      <c r="Q70" s="12">
         <f t="shared" si="14"/>
         <v>0.3044714286</v>
       </c>
-      <c r="R70" s="10">
+      <c r="R70" s="12">
         <f t="shared" si="14"/>
         <v>0.2830428571</v>
       </c>
-      <c r="S70" s="10">
+      <c r="S70" s="12">
         <f t="shared" si="14"/>
         <v>0.2062</v>
       </c>
-      <c r="T70" s="10">
+      <c r="T70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1249</v>
-      </c>
-      <c r="U70" s="10">
-        <f t="shared" si="14"/>
-        <v>0.1058571429</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3543,30 +3531,30 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="1"/>
-      <c r="S79" s="10"/>
+      <c r="S79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="1"/>
-      <c r="S80" s="10"/>
+      <c r="S80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="1"/>
-      <c r="S81" s="10"/>
+      <c r="S81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="1"/>
-      <c r="S82" s="10"/>
+      <c r="S82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="1"/>
-      <c r="S83" s="10"/>
+      <c r="S83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="1"/>
-      <c r="S84" s="10"/>
+      <c r="S84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="S85" s="10"/>
+      <c r="S85" s="12"/>
     </row>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
@@ -3595,67 +3583,67 @@
       <c r="B109" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="10" t="str">
+      <c r="C109" s="12" t="str">
         <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D109" s="10" t="str">
+      <c r="D109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E109" s="10" t="str">
+      <c r="E109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="10" t="str">
+      <c r="F109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G109" s="10" t="str">
+      <c r="G109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H109" s="10" t="str">
+      <c r="H109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="10" t="str">
+      <c r="I109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J109" s="10" t="str">
+      <c r="J109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K109" s="10" t="str">
+      <c r="K109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L109" s="10" t="str">
+      <c r="L109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M109" s="10" t="str">
+      <c r="M109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N109" s="10" t="str">
+      <c r="N109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O109" s="10" t="str">
+      <c r="O109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P109" s="10" t="str">
+      <c r="P109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q109" s="10" t="str">
+      <c r="Q109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R109" s="10" t="str">
+      <c r="R109" s="12" t="str">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -131,12 +131,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -165,6 +165,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -772,7 +775,7 @@
         <v>0.2745</v>
       </c>
       <c r="T6" s="13">
-        <v>0.1538</v>
+        <v>0.127</v>
       </c>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
@@ -781,13 +784,13 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2539714286</v>
+        <v>0.2501428571</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2">
@@ -919,7 +922,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="14"/>
+      <c r="W10" s="15"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -978,7 +981,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="14"/>
+      <c r="W11" s="15"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1036,7 +1039,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="14"/>
+      <c r="W12" s="15"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1100,8 +1103,8 @@
       <c r="S13" s="13">
         <v>0.16</v>
       </c>
-      <c r="T13" s="15"/>
-      <c r="W13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="W13" s="17"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
@@ -1163,7 +1166,7 @@
         <v>0.2339</v>
       </c>
       <c r="T14" s="13">
-        <v>0.1</v>
+        <v>0.0787</v>
       </c>
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
@@ -1172,12 +1175,12 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.2016666667</v>
+        <v>0.1945666667</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="S15" s="12"/>
-      <c r="T15" s="17"/>
+      <c r="T15" s="18"/>
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
@@ -1196,7 +1199,7 @@
       <c r="Z16" s="12"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="2">
@@ -1542,7 +1545,7 @@
         <v>0.1443</v>
       </c>
       <c r="T22" s="13">
-        <v>0.1014</v>
+        <v>0.1029</v>
       </c>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
@@ -1551,13 +1554,13 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1592333333</v>
+        <v>0.1597333333</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2">
@@ -1748,7 +1751,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="14"/>
+      <c r="W27" s="15"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1806,8 +1809,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="15"/>
-      <c r="W28" s="14"/>
+      <c r="T28" s="16"/>
+      <c r="W28" s="15"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1867,7 +1870,7 @@
       <c r="S29" s="13">
         <v>0.1111</v>
       </c>
-      <c r="T29" s="17"/>
+      <c r="T29" s="18"/>
       <c r="U29" s="12"/>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
@@ -1947,7 +1950,7 @@
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B33" s="2">
@@ -2066,7 +2069,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="14"/>
+      <c r="N34" s="15"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2323,7 +2326,7 @@
         <v>0.1974</v>
       </c>
       <c r="T38" s="13">
-        <v>0.125</v>
+        <v>0.1667</v>
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
@@ -2332,13 +2335,13 @@
       <c r="Y38" s="12"/>
       <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.1885333333</v>
+        <v>0.2024333333</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="14" t="s">
         <v>11</v>
       </c>
       <c r="B41" s="2">
@@ -2461,7 +2464,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="14"/>
+      <c r="L44" s="15"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2487,7 +2490,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="18"/>
+      <c r="I45" s="19"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2547,7 +2550,7 @@
         <v>0.1705</v>
       </c>
       <c r="T46" s="13">
-        <v>0.05</v>
+        <v>0.0263</v>
       </c>
       <c r="U46" s="12"/>
       <c r="V46" s="12"/>
@@ -2556,7 +2559,7 @@
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.1624</v>
+        <v>0.1545</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2565,7 +2568,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B49" s="2">
@@ -2769,7 +2772,7 @@
         <v>0.192</v>
       </c>
       <c r="T54" s="13">
-        <v>0.125</v>
+        <v>0.1226</v>
       </c>
       <c r="U54" s="12"/>
       <c r="V54" s="12"/>
@@ -2778,13 +2781,13 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.2043333333</v>
+        <v>0.2035333333</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="1"/>
+      <c r="A57" s="14"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2818,7 +2821,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="14"/>
+      <c r="L58" s="15"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -3089,8 +3092,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3189,71 +3192,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="21">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="21">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="21">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="21">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="21">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="21">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="21">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="20">
+      <c r="I67" s="21">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J67" s="21">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="20">
+      <c r="K67" s="21">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="20">
+      <c r="L67" s="21">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="20">
+      <c r="M67" s="21">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="20">
+      <c r="N67" s="21">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="20">
+      <c r="O67" s="21">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="20">
+      <c r="P67" s="21">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="20">
+      <c r="Q67" s="21">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="20">
+      <c r="R67" s="21">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3264,7 +3267,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="20">
+      <c r="Z67" s="21">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3518,7 +3521,7 @@
       </c>
       <c r="T70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1048</v>
+        <v>0.1003714286</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3530,27 +3533,27 @@
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="B79" s="1"/>
+      <c r="B79" s="14"/>
       <c r="S79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="B80" s="1"/>
+      <c r="B80" s="14"/>
       <c r="S80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="1"/>
+      <c r="B81" s="14"/>
       <c r="S81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="1"/>
+      <c r="B82" s="14"/>
       <c r="S82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="1"/>
+      <c r="B83" s="14"/>
       <c r="S83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="B84" s="1"/>
+      <c r="B84" s="14"/>
       <c r="S84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -777,14 +777,16 @@
       <c r="T6" s="13">
         <v>0.127</v>
       </c>
-      <c r="U6" s="12"/>
+      <c r="U6" s="13">
+        <v>0.125</v>
+      </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2501428571</v>
+        <v>0.2345</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,14 +1170,16 @@
       <c r="T14" s="13">
         <v>0.0787</v>
       </c>
-      <c r="U14" s="12"/>
+      <c r="U14" s="13">
+        <v>0.069</v>
+      </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.1945666667</v>
+        <v>0.163175</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1547,14 +1551,16 @@
       <c r="T22" s="13">
         <v>0.1029</v>
       </c>
-      <c r="U22" s="12"/>
+      <c r="U22" s="13">
+        <v>0.1045</v>
+      </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1597333333</v>
+        <v>0.145925</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1937,14 +1943,16 @@
       <c r="T30" s="13">
         <v>0.0784</v>
       </c>
-      <c r="U30" s="12"/>
+      <c r="U30" s="13">
+        <v>0.1053</v>
+      </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.2129666667</v>
+        <v>0.18605</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2328,14 +2336,16 @@
       <c r="T38" s="13">
         <v>0.1667</v>
       </c>
-      <c r="U38" s="12"/>
+      <c r="U38" s="13">
+        <v>0.2</v>
+      </c>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
       <c r="X38" s="12"/>
       <c r="Y38" s="12"/>
       <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.2024333333</v>
+        <v>0.201825</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2552,14 +2562,16 @@
       <c r="T46" s="13">
         <v>0.0263</v>
       </c>
-      <c r="U46" s="12"/>
+      <c r="U46" s="13">
+        <v>0.0286</v>
+      </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.1545</v>
+        <v>0.123025</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2774,14 +2786,16 @@
       <c r="T54" s="13">
         <v>0.1226</v>
       </c>
-      <c r="U54" s="12"/>
+      <c r="U54" s="13">
+        <v>0.1171</v>
+      </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.2035333333</v>
+        <v>0.181925</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -131,12 +131,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -165,9 +165,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -792,7 +789,7 @@
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2">
@@ -924,7 +921,7 @@
         <v>118400.53</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="W10" s="15"/>
+      <c r="W10" s="14"/>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:Z11" si="3">sum(N10:Y10)</f>
         <v>658167.27</v>
@@ -983,7 +980,7 @@
         <v>9.0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="W11" s="15"/>
+      <c r="W11" s="14"/>
       <c r="Z11" s="3">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -1041,7 +1038,7 @@
       <c r="R12" s="4">
         <v>13155.61</v>
       </c>
-      <c r="W12" s="15"/>
+      <c r="W12" s="14"/>
       <c r="Z12" s="5">
         <f>average(N12:Y12)</f>
         <v>9918.804</v>
@@ -1105,8 +1102,8 @@
       <c r="S13" s="13">
         <v>0.16</v>
       </c>
-      <c r="T13" s="16"/>
-      <c r="W13" s="17"/>
+      <c r="T13" s="15"/>
+      <c r="W13" s="16"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
@@ -1184,7 +1181,7 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="S15" s="12"/>
-      <c r="T15" s="18"/>
+      <c r="T15" s="17"/>
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
@@ -1203,7 +1200,7 @@
       <c r="Z16" s="12"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="2">
@@ -1566,7 +1563,7 @@
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2">
@@ -1757,7 +1754,7 @@
         <v>10.0</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="W27" s="15"/>
+      <c r="W27" s="14"/>
       <c r="Z27" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
@@ -1815,8 +1812,8 @@
       <c r="R28" s="4">
         <v>8888.02</v>
       </c>
-      <c r="T28" s="16"/>
-      <c r="W28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="W28" s="14"/>
       <c r="Z28" s="5">
         <f>average(N28:Y28)</f>
         <v>3625.05</v>
@@ -1876,7 +1873,7 @@
       <c r="S29" s="13">
         <v>0.1111</v>
       </c>
-      <c r="T29" s="18"/>
+      <c r="T29" s="17"/>
       <c r="U29" s="12"/>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
@@ -1958,7 +1955,7 @@
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B33" s="2">
@@ -2077,7 +2074,7 @@
       <c r="M34" s="4">
         <v>14861.34</v>
       </c>
-      <c r="N34" s="15"/>
+      <c r="N34" s="14"/>
       <c r="O34" s="4">
         <v>8067.86</v>
       </c>
@@ -2351,7 +2348,7 @@
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B41" s="2">
@@ -2474,7 +2471,7 @@
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="15"/>
+      <c r="L44" s="14"/>
       <c r="P44" s="4">
         <v>1874.92</v>
       </c>
@@ -2500,7 +2497,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="19"/>
+      <c r="I45" s="18"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -2580,7 +2577,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B49" s="2">
@@ -2801,7 +2798,7 @@
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="14"/>
+      <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2835,7 +2832,7 @@
       <c r="F58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="L58" s="15"/>
+      <c r="L58" s="14"/>
       <c r="M58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4"/>
@@ -3106,8 +3103,8 @@
         <f t="shared" si="9"/>
         <v>1122433.97</v>
       </c>
-      <c r="S65" s="20"/>
-      <c r="T65" s="20"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -3206,71 +3203,71 @@
       <c r="A67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="21">
+      <c r="B67" s="20">
         <f t="shared" ref="B67:R67" si="11">AVERAGE(B59,B51,B43,B35,B27,B19,B11,B3)</f>
         <v>2</v>
       </c>
-      <c r="C67" s="21">
+      <c r="C67" s="20">
         <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
-      <c r="D67" s="21">
+      <c r="D67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="E67" s="21">
+      <c r="E67" s="20">
         <f t="shared" si="11"/>
         <v>4.6</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="20">
         <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
-      <c r="G67" s="21">
+      <c r="G67" s="20">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="H67" s="21">
+      <c r="H67" s="20">
         <f t="shared" si="11"/>
         <v>8.2</v>
       </c>
-      <c r="I67" s="21">
+      <c r="I67" s="20">
         <f t="shared" si="11"/>
         <v>6.4</v>
       </c>
-      <c r="J67" s="21">
+      <c r="J67" s="20">
         <f t="shared" si="11"/>
         <v>7.2</v>
       </c>
-      <c r="K67" s="21">
+      <c r="K67" s="20">
         <f t="shared" si="11"/>
         <v>14.2</v>
       </c>
-      <c r="L67" s="21">
+      <c r="L67" s="20">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M67" s="21">
+      <c r="M67" s="20">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="N67" s="21">
+      <c r="N67" s="20">
         <f t="shared" si="11"/>
         <v>5.666666667</v>
       </c>
-      <c r="O67" s="21">
+      <c r="O67" s="20">
         <f t="shared" si="11"/>
         <v>3.75</v>
       </c>
-      <c r="P67" s="21">
+      <c r="P67" s="20">
         <f t="shared" si="11"/>
         <v>7.714285714</v>
       </c>
-      <c r="Q67" s="21">
+      <c r="Q67" s="20">
         <f t="shared" si="11"/>
         <v>16.85714286</v>
       </c>
-      <c r="R67" s="21">
+      <c r="R67" s="20">
         <f t="shared" si="11"/>
         <v>12.28571429</v>
       </c>
@@ -3281,7 +3278,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-      <c r="Z67" s="21">
+      <c r="Z67" s="20">
         <f>sum(N67:Y67)</f>
         <v>46.27380952</v>
       </c>
@@ -3462,7 +3459,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="12">
-        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <f t="shared" ref="B70:U70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
       <c r="C70" s="12">
@@ -3536,6 +3533,10 @@
       <c r="T70" s="12">
         <f t="shared" si="14"/>
         <v>0.1003714286</v>
+      </c>
+      <c r="U70" s="12">
+        <f t="shared" si="14"/>
+        <v>0.1070714286</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3547,27 +3548,27 @@
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="B79" s="14"/>
+      <c r="B79" s="1"/>
       <c r="S79" s="12"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="B80" s="14"/>
+      <c r="B80" s="1"/>
       <c r="S80" s="12"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="14"/>
+      <c r="B81" s="1"/>
       <c r="S81" s="12"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="14"/>
+      <c r="B82" s="1"/>
       <c r="S82" s="12"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="14"/>
+      <c r="B83" s="1"/>
       <c r="S83" s="12"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="B84" s="14"/>
+      <c r="B84" s="1"/>
       <c r="S84" s="12"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.125</v>
+        <v>0.129</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2345</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.1045</v>
+        <v>0.1077</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.145925</v>
+        <v>0.146725</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.1053</v>
+        <v>0.1091</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.18605</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2334,7 +2334,7 @@
         <v>0.1667</v>
       </c>
       <c r="U38" s="13">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
@@ -2342,7 +2342,7 @@
       <c r="Y38" s="12"/>
       <c r="Z38" s="12">
         <f>average(R38:Y38)</f>
-        <v>0.201825</v>
+        <v>0.276825</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1070714286</v>
+        <v>0.1515</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.129</v>
+        <v>0.1333</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.235</v>
+        <v>0.2355375</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.069</v>
+        <v>0.0682</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.163175</v>
+        <v>0.162975</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.1077</v>
+        <v>0.1094</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.146725</v>
+        <v>0.14715</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -2560,7 +2560,7 @@
         <v>0.0263</v>
       </c>
       <c r="U46" s="13">
-        <v>0.0286</v>
+        <v>0.0263</v>
       </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
@@ -2568,7 +2568,7 @@
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.123025</v>
+        <v>0.12245</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1171</v>
+        <v>0.1111</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.181925</v>
+        <v>0.180425</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1515</v>
+        <v>0.1510571429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -173,8 +173,8 @@
     <xf borderId="2" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="10" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.1333</v>
+        <v>0.1452</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2355375</v>
+        <v>0.237025</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.0682</v>
+        <v>0.0698</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.162975</v>
+        <v>0.163375</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.1094</v>
+        <v>0.1129</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.14715</v>
+        <v>0.148025</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.1091</v>
+        <v>0.1034</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.187</v>
+        <v>0.185575</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1111</v>
+        <v>0.1215</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.180425</v>
+        <v>0.183025</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1510571429</v>
+        <v>0.1541571429</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.1452</v>
+        <v>0.1774</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.237025</v>
+        <v>0.24105</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.0698</v>
+        <v>0.069</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.163375</v>
+        <v>0.163175</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.1129</v>
+        <v>0.1148</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.148025</v>
+        <v>0.1485</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.1034</v>
+        <v>0.1207</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.185575</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2560,7 +2560,7 @@
         <v>0.0263</v>
       </c>
       <c r="U46" s="13">
-        <v>0.0263</v>
+        <v>0.027</v>
       </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
@@ -2568,7 +2568,7 @@
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.12245</v>
+        <v>0.122625</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1215</v>
+        <v>0.1226</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.183025</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f t="shared" si="14"/>
-        <v>0.1541571429</v>
+        <v>0.1616428571</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.1774</v>
+        <v>0.2203</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.24105</v>
+        <v>0.2464125</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.069</v>
+        <v>0.0482</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.163175</v>
+        <v>0.157975</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.1148</v>
+        <v>0.0882</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1485</v>
+        <v>0.14185</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.1207</v>
+        <v>0.129</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.1899</v>
+        <v>0.191975</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2560,7 +2560,7 @@
         <v>0.0263</v>
       </c>
       <c r="U46" s="13">
-        <v>0.027</v>
+        <v>0.0294</v>
       </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
@@ -2568,7 +2568,7 @@
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.122625</v>
+        <v>0.123225</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1226</v>
+        <v>0.1238</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.1833</v>
+        <v>0.1836</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3459,7 +3459,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="12">
-        <f t="shared" ref="B70:U70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
+        <f t="shared" ref="B70:T70" si="14">AVERAGE(B54,B46,B38,B30,B22,B14,B6)</f>
         <v>0.50445</v>
       </c>
       <c r="C70" s="12">
@@ -3535,8 +3535,8 @@
         <v>0.1003714286</v>
       </c>
       <c r="U70" s="12">
-        <f t="shared" si="14"/>
-        <v>0.1616428571</v>
+        <f>AVERAGE(U54,U46,U30,U22,U14,U6)</f>
+        <v>0.1064833333</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.2203</v>
+        <v>0.2241</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2464125</v>
+        <v>0.2468875</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.0482</v>
+        <v>0.0595</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.157975</v>
+        <v>0.1608</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.0882</v>
+        <v>0.0896</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.14185</v>
+        <v>0.1422</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.191975</v>
+        <v>0.191475</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1238</v>
+        <v>0.1346</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.1836</v>
+        <v>0.1863</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f>AVERAGE(U54,U46,U30,U22,U14,U6)</f>
-        <v>0.1064833333</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.2241</v>
+        <v>0.2281</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2468875</v>
+        <v>0.2473875</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.0595</v>
+        <v>0.0588</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.1608</v>
+        <v>0.160625</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.0896</v>
+        <v>0.0882</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1422</v>
+        <v>0.14185</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.127</v>
+        <v>0.125</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.191475</v>
+        <v>0.190975</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1346</v>
+        <v>0.1359</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.1863</v>
+        <v>0.186625</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f>AVERAGE(U54,U46,U30,U22,U14,U6)</f>
-        <v>0.1107</v>
+        <v>0.1109</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -775,7 +775,7 @@
         <v>0.127</v>
       </c>
       <c r="U6" s="13">
-        <v>0.2281</v>
+        <v>0.2143</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -783,7 +783,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2473875</v>
+        <v>0.2456625</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.0588</v>
+        <v>0.0471</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.160625</v>
+        <v>0.1577</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1549,7 +1549,7 @@
         <v>0.1029</v>
       </c>
       <c r="U22" s="13">
-        <v>0.0882</v>
+        <v>0.087</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
@@ -1557,7 +1557,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.14185</v>
+        <v>0.14155</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.125</v>
+        <v>0.1385</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.190975</v>
+        <v>0.19435</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2560,7 +2560,7 @@
         <v>0.0263</v>
       </c>
       <c r="U46" s="13">
-        <v>0.0294</v>
+        <v>0.0286</v>
       </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
@@ -2568,7 +2568,7 @@
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.123225</v>
+        <v>0.123025</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.1359</v>
+        <v>0.14</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.186625</v>
+        <v>0.18765</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f>AVERAGE(U54,U46,U30,U22,U14,U6)</f>
-        <v>0.1109</v>
+        <v>0.10925</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -1168,7 +1168,7 @@
         <v>0.0787</v>
       </c>
       <c r="U14" s="13">
-        <v>0.0471</v>
+        <v>0.0465</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -1176,7 +1176,7 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.1577</v>
+        <v>0.15755</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1941,7 +1941,7 @@
         <v>0.0784</v>
       </c>
       <c r="U30" s="13">
-        <v>0.1385</v>
+        <v>0.1613</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
@@ -1949,7 +1949,7 @@
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.19435</v>
+        <v>0.20005</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2560,7 +2560,7 @@
         <v>0.0263</v>
       </c>
       <c r="U46" s="13">
-        <v>0.0286</v>
+        <v>0.0606</v>
       </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
@@ -2568,7 +2568,7 @@
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.123025</v>
+        <v>0.131025</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2784,7 +2784,7 @@
         <v>0.1226</v>
       </c>
       <c r="U54" s="13">
-        <v>0.14</v>
+        <v>0.1515</v>
       </c>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
@@ -2792,7 +2792,7 @@
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.18765</v>
+        <v>0.190525</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="U70" s="12">
         <f>AVERAGE(U54,U46,U30,U22,U14,U6)</f>
-        <v>0.10925</v>
+        <v>0.1202</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -777,13 +777,15 @@
       <c r="U6" s="13">
         <v>0.2143</v>
       </c>
-      <c r="V6" s="12"/>
+      <c r="V6" s="13">
+        <v>0.2037</v>
+      </c>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2456625</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1170,13 +1172,15 @@
       <c r="U14" s="13">
         <v>0.0465</v>
       </c>
-      <c r="V14" s="12"/>
+      <c r="V14" s="13">
+        <v>0.0588</v>
+      </c>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.15755</v>
+        <v>0.1378</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1551,13 +1555,15 @@
       <c r="U22" s="13">
         <v>0.087</v>
       </c>
-      <c r="V22" s="12"/>
+      <c r="V22" s="13">
+        <v>0.0833</v>
+      </c>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.14155</v>
+        <v>0.1299</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1943,13 +1949,15 @@
       <c r="U30" s="13">
         <v>0.1613</v>
       </c>
-      <c r="V30" s="12"/>
+      <c r="V30" s="13">
+        <v>0.1613</v>
+      </c>
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.20005</v>
+        <v>0.1923</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2562,13 +2570,15 @@
       <c r="U46" s="13">
         <v>0.0606</v>
       </c>
-      <c r="V46" s="12"/>
+      <c r="V46" s="13">
+        <v>0.0606</v>
+      </c>
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.131025</v>
+        <v>0.11694</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2786,13 +2796,15 @@
       <c r="U54" s="13">
         <v>0.1515</v>
       </c>
-      <c r="V54" s="12"/>
+      <c r="V54" s="13">
+        <v>0.1616</v>
+      </c>
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.190525</v>
+        <v>0.18474</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3535,8 +3547,12 @@
         <v>0.1003714286</v>
       </c>
       <c r="U70" s="12">
-        <f>AVERAGE(U54,U46,U30,U22,U14,U6)</f>
+        <f t="shared" ref="U70:V70" si="15">AVERAGE(U54,U46,U30,U22,U14,U6)</f>
         <v>0.1202</v>
+      </c>
+      <c r="V70" s="12">
+        <f t="shared" si="15"/>
+        <v>0.12155</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
@@ -3602,67 +3618,67 @@
         <v>17</v>
       </c>
       <c r="C109" s="12" t="str">
-        <f t="shared" ref="C109:R109" si="15">average(C79:C84)</f>
+        <f t="shared" ref="C109:R109" si="16">average(C79:C84)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R109" s="12" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -778,14 +778,14 @@
         <v>0.2143</v>
       </c>
       <c r="V6" s="13">
-        <v>0.2037</v>
+        <v>0.1964</v>
       </c>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.241</v>
+        <v>0.2401888889</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1173,14 +1173,14 @@
         <v>0.0465</v>
       </c>
       <c r="V14" s="13">
-        <v>0.0588</v>
+        <v>0.0595</v>
       </c>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.1378</v>
+        <v>0.13794</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1556,14 +1556,14 @@
         <v>0.087</v>
       </c>
       <c r="V22" s="13">
-        <v>0.0833</v>
+        <v>0.0845</v>
       </c>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.1299</v>
+        <v>0.13014</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1950,14 +1950,14 @@
         <v>0.1613</v>
       </c>
       <c r="V30" s="13">
-        <v>0.1613</v>
+        <v>0.2063</v>
       </c>
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.1923</v>
+        <v>0.2013</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2571,14 +2571,14 @@
         <v>0.0606</v>
       </c>
       <c r="V46" s="13">
-        <v>0.0606</v>
+        <v>0.0645</v>
       </c>
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.11694</v>
+        <v>0.11772</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2797,14 +2797,14 @@
         <v>0.1515</v>
       </c>
       <c r="V54" s="13">
-        <v>0.1616</v>
+        <v>0.16</v>
       </c>
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.18474</v>
+        <v>0.18442</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="V70" s="12">
         <f t="shared" si="15"/>
-        <v>0.12155</v>
+        <v>0.1285333333</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -778,14 +778,14 @@
         <v>0.2143</v>
       </c>
       <c r="V6" s="13">
-        <v>0.1964</v>
+        <v>0.2</v>
       </c>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2401888889</v>
+        <v>0.2405888889</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1173,14 +1173,14 @@
         <v>0.0465</v>
       </c>
       <c r="V14" s="13">
-        <v>0.0595</v>
+        <v>0.0723</v>
       </c>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.13794</v>
+        <v>0.1405</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1556,14 +1556,14 @@
         <v>0.087</v>
       </c>
       <c r="V22" s="13">
-        <v>0.0845</v>
+        <v>0.0694</v>
       </c>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.13014</v>
+        <v>0.12712</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1950,14 +1950,14 @@
         <v>0.1613</v>
       </c>
       <c r="V30" s="13">
-        <v>0.2063</v>
+        <v>0.1884</v>
       </c>
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12">
         <f>average(R30:Y30)</f>
-        <v>0.2013</v>
+        <v>0.19772</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -2571,14 +2571,14 @@
         <v>0.0606</v>
       </c>
       <c r="V46" s="13">
-        <v>0.0645</v>
+        <v>0.0345</v>
       </c>
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.11772</v>
+        <v>0.11172</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2797,14 +2797,14 @@
         <v>0.1515</v>
       </c>
       <c r="V54" s="13">
-        <v>0.16</v>
+        <v>0.1939</v>
       </c>
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.18442</v>
+        <v>0.1912</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="V70" s="12">
         <f t="shared" si="15"/>
-        <v>0.1285333333</v>
+        <v>0.1264166667</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>

--- a/public/pm-contract-data.xlsx
+++ b/public/pm-contract-data.xlsx
@@ -778,14 +778,14 @@
         <v>0.2143</v>
       </c>
       <c r="V6" s="13">
-        <v>0.2</v>
+        <v>0.1887</v>
       </c>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12">
         <f t="shared" si="2"/>
-        <v>0.2405888889</v>
+        <v>0.2393333333</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>
@@ -1173,14 +1173,14 @@
         <v>0.0465</v>
       </c>
       <c r="V14" s="13">
-        <v>0.0723</v>
+        <v>0.0854</v>
       </c>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Y14" s="12"/>
       <c r="Z14" s="12">
         <f>average(R14:Y14)</f>
-        <v>0.1405</v>
+        <v>0.14312</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1556,14 +1556,14 @@
         <v>0.087</v>
       </c>
       <c r="V22" s="13">
-        <v>0.0694</v>
+        <v>0.0704</v>
       </c>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12">
         <f>average(R22:Y22)</f>
-        <v>0.12712</v>
+        <v>0.12732</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -2571,14 +2571,14 @@
         <v>0.0606</v>
       </c>
       <c r="V46" s="13">
-        <v>0.0345</v>
+        <v>0.0333</v>
       </c>
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
       <c r="Y46" s="12"/>
       <c r="Z46" s="12">
         <f>average(R46:Y46)</f>
-        <v>0.11172</v>
+        <v>0.11148</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
@@ -2797,14 +2797,14 @@
         <v>0.1515</v>
       </c>
       <c r="V54" s="13">
-        <v>0.1939</v>
+        <v>0.2062</v>
       </c>
       <c r="W54" s="12"/>
       <c r="X54" s="12"/>
       <c r="Y54" s="12"/>
       <c r="Z54" s="12">
         <f>average(R54:Y54)</f>
-        <v>0.1912</v>
+        <v>0.19366</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="V70" s="12">
         <f t="shared" si="15"/>
-        <v>0.1264166667</v>
+        <v>0.1287333333</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
